--- a/main/ig/StructureDefinition-fr-media-document.xlsx
+++ b/main/ig/StructureDefinition-fr-media-document.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-02-25T10:05:30+00:00</t>
+    <t>2026-03-13T14:11:35+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-media-document.xlsx
+++ b/main/ig/StructureDefinition-fr-media-document.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-13T14:11:35+00:00</t>
+    <t>2026-03-13T17:00:40+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-media-document.xlsx
+++ b/main/ig/StructureDefinition-fr-media-document.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-13T17:00:40+00:00</t>
+    <t>2026-03-13T17:26:39+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-media-document.xlsx
+++ b/main/ig/StructureDefinition-fr-media-document.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-13T17:26:39+00:00</t>
+    <t>2026-03-13T17:26:16+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-media-document.xlsx
+++ b/main/ig/StructureDefinition-fr-media-document.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-13T17:26:16+00:00</t>
+    <t>2026-03-13T22:26:12+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-media-document.xlsx
+++ b/main/ig/StructureDefinition-fr-media-document.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.1.0</t>
+    <t>0.1.0-snapsnot</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-13T22:26:12+00:00</t>
+    <t>2026-03-20T08:18:16+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-media-document.xlsx
+++ b/main/ig/StructureDefinition-fr-media-document.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-20T08:18:16+00:00</t>
+    <t>2026-03-23T13:14:10+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-media-document.xlsx
+++ b/main/ig/StructureDefinition-fr-media-document.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-23T13:14:10+00:00</t>
+    <t>2026-03-27T09:33:49+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-media-document.xlsx
+++ b/main/ig/StructureDefinition-fr-media-document.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-27T09:33:49+00:00</t>
+    <t>2026-03-30T15:11:58+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-media-document.xlsx
+++ b/main/ig/StructureDefinition-fr-media-document.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-30T15:11:58+00:00</t>
+    <t>2026-03-31T07:16:03+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-media-document.xlsx
+++ b/main/ig/StructureDefinition-fr-media-document.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-31T07:16:03+00:00</t>
+    <t>2026-04-01T07:43:12+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-media-document.xlsx
+++ b/main/ig/StructureDefinition-fr-media-document.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-01T07:43:12+00:00</t>
+    <t>2026-04-02T07:21:27+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-media-document.xlsx
+++ b/main/ig/StructureDefinition-fr-media-document.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-02T07:21:27+00:00</t>
+    <t>2026-04-02T12:41:19+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-media-document.xlsx
+++ b/main/ig/StructureDefinition-fr-media-document.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-02T12:41:19+00:00</t>
+    <t>2026-04-07T08:23:13+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-media-document.xlsx
+++ b/main/ig/StructureDefinition-fr-media-document.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.1.0-snapsnot</t>
+    <t>0.1.0-snapshot</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-07T08:23:13+00:00</t>
+    <t>2026-04-15T13:29:57+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-media-document.xlsx
+++ b/main/ig/StructureDefinition-fr-media-document.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-15T13:29:57+00:00</t>
+    <t>2026-04-15T15:41:19+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-media-document.xlsx
+++ b/main/ig/StructureDefinition-fr-media-document.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-15T15:41:19+00:00</t>
+    <t>2026-04-20T15:11:12+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-media-document.xlsx
+++ b/main/ig/StructureDefinition-fr-media-document.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-20T15:11:12+00:00</t>
+    <t>2026-04-23T15:25:59+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-media-document.xlsx
+++ b/main/ig/StructureDefinition-fr-media-document.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-23T15:25:59+00:00</t>
+    <t>2026-05-06T07:44:21+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-media-document.xlsx
+++ b/main/ig/StructureDefinition-fr-media-document.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-06T07:44:21+00:00</t>
+    <t>2026-05-13T14:53:03+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-media-document.xlsx
+++ b/main/ig/StructureDefinition-fr-media-document.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-13T14:53:03+00:00</t>
+    <t>2026-05-15T08:08:15+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-media-document.xlsx
+++ b/main/ig/StructureDefinition-fr-media-document.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-22T09:35:10+00:00</t>
+    <t>2026-06-29T12:53:00+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-media-document.xlsx
+++ b/main/ig/StructureDefinition-fr-media-document.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-29T12:53:00+00:00</t>
+    <t>2026-06-29T14:20:03+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-media-document.xlsx
+++ b/main/ig/StructureDefinition-fr-media-document.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-29T14:20:03+00:00</t>
+    <t>2026-06-29T15:28:29+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-media-document.xlsx
+++ b/main/ig/StructureDefinition-fr-media-document.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-29T15:28:29+00:00</t>
+    <t>2026-06-30T08:01:58+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-media-document.xlsx
+++ b/main/ig/StructureDefinition-fr-media-document.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4976" uniqueCount="541">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4974" uniqueCount="550">
   <si>
     <t>Property</t>
   </si>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-30T08:01:58+00:00</t>
+    <t>2026-06-30T09:01:37+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -434,38 +434,374 @@
     <t>Media.extension</t>
   </si>
   <si>
+    <t xml:space="preserve">Extension
+</t>
+  </si>
+  <si>
+    <t>Extension</t>
+  </si>
+  <si>
+    <t>An Extension</t>
+  </si>
+  <si>
+    <t xml:space="preserve">value:url}
+</t>
+  </si>
+  <si>
+    <t>open</t>
+  </si>
+  <si>
+    <t>DomainResource.extension</t>
+  </si>
+  <si>
+    <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
+ext-1:Must have either extensions or value[x], not both {extension.exists() != value.exists()}</t>
+  </si>
+  <si>
+    <t>Media.extension:author</t>
+  </si>
+  <si>
+    <t>author</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Extension {https://interop.esante.gouv.fr/ig/document/core/StructureDefinition/fr-actor-extension}
+</t>
+  </si>
+  <si>
+    <t>Auteur du média</t>
+  </si>
+  <si>
+    <t>Extension permettant de représenter un acteur impliqué dans le document avec son type et sa référence.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ele-1
+</t>
+  </si>
+  <si>
+    <t>Media.extension:author.id</t>
+  </si>
+  <si>
+    <t>Media.extension.id</t>
+  </si>
+  <si>
+    <t xml:space="preserve">string
+</t>
+  </si>
+  <si>
+    <t>Unique id for inter-element referencing</t>
+  </si>
+  <si>
+    <t>Unique id for the element within a resource (for internal references). This may be any string value that does not contain spaces.</t>
+  </si>
+  <si>
+    <t>Element.id</t>
+  </si>
+  <si>
+    <t>n/a</t>
+  </si>
+  <si>
+    <t>Media.extension:author.extension</t>
+  </si>
+  <si>
+    <t>Media.extension.extension</t>
+  </si>
+  <si>
+    <t>2</t>
+  </si>
+  <si>
+    <t>Extensions are always sliced by (at least) url</t>
+  </si>
+  <si>
+    <t>Element.extension</t>
+  </si>
+  <si>
+    <t>Media.extension:author.extension:type</t>
+  </si>
+  <si>
+    <t>type</t>
+  </si>
+  <si>
+    <t>Media.extension:author.extension:type.id</t>
+  </si>
+  <si>
+    <t>Media.extension.extension.id</t>
+  </si>
+  <si>
+    <t>Media.extension:author.extension:type.extension</t>
+  </si>
+  <si>
+    <t>Media.extension.extension.extension</t>
+  </si>
+  <si>
+    <t>Media.extension:author.extension:type.url</t>
+  </si>
+  <si>
+    <t>Media.extension.extension.url</t>
+  </si>
+  <si>
+    <t>identifies the meaning of the extension</t>
+  </si>
+  <si>
+    <t>Source of the definition for the extension code - a logical name or a URL.</t>
+  </si>
+  <si>
+    <t>The definition may point directly to a computable or human-readable definition of the extensibility codes, or it may be a logical URI as declared in some other specification. The definition SHALL be a URI for the Structure Definition defining the extension.</t>
+  </si>
+  <si>
+    <t>Extension.url</t>
+  </si>
+  <si>
+    <t>Media.extension:author.extension:type.value[x]</t>
+  </si>
+  <si>
+    <t>Media.extension.extension.value[x]</t>
+  </si>
+  <si>
+    <t>Value of extension</t>
+  </si>
+  <si>
+    <t>Value of extension - must be one of a constrained set of the data types (see [Extensibility](http://hl7.org/fhir/R4/extensibility.html) for a list).</t>
+  </si>
+  <si>
+    <t>AUT</t>
+  </si>
+  <si>
+    <t>required</t>
+  </si>
+  <si>
+    <t>https://interop.esante.gouv.fr/ig/document/core/ValueSet/fr-vs-actor-type-document</t>
+  </si>
+  <si>
+    <t>Extension.value[x]</t>
+  </si>
+  <si>
+    <t>Media.extension:author.extension:typeCode</t>
+  </si>
+  <si>
+    <t>typeCode</t>
+  </si>
+  <si>
+    <t>Type de participation</t>
+  </si>
+  <si>
+    <t>Media.extension:author.extension:typeCode.id</t>
+  </si>
+  <si>
+    <t>Media.extension:author.extension:typeCode.extension</t>
+  </si>
+  <si>
+    <t>Media.extension:author.extension:typeCode.url</t>
+  </si>
+  <si>
+    <t>Media.extension:author.extension:typeCode.value[x]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CodeableConcept
+</t>
+  </si>
+  <si>
+    <t>Media.extension:author.extension:actor</t>
+  </si>
+  <si>
+    <t>actor</t>
+  </si>
+  <si>
+    <t>Media.extension:author.extension:actor.id</t>
+  </si>
+  <si>
+    <t>Media.extension:author.extension:actor.extension</t>
+  </si>
+  <si>
+    <t>Media.extension:author.extension:actor.url</t>
+  </si>
+  <si>
+    <t>Media.extension:author.extension:actor.value[x]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Reference(https://interop.esante.gouv.fr/ig/document/core/StructureDefinition/fr-device-auteur-document|https://interop.esante.gouv.fr/ig/document/core/StructureDefinition/fr-practitionerRole-document)
+</t>
+  </si>
+  <si>
+    <t>Media.extension:author.url</t>
+  </si>
+  <si>
+    <t>Media.extension.url</t>
+  </si>
+  <si>
+    <t>https://interop.esante.gouv.fr/ig/document/core/StructureDefinition/fr-actor-extension</t>
+  </si>
+  <si>
+    <t>Media.extension:author.value[x]</t>
+  </si>
+  <si>
+    <t>Media.extension.value[x]</t>
+  </si>
+  <si>
+    <t>base64Binary
+booleancanonicalcodedatedateTimedecimalidinstantintegermarkdownoidpositiveIntstringtimeunsignedInturiurluuidAddressAgeAnnotationAttachmentCodeableConceptCodingContactPointCountDistanceDurationHumanNameIdentifierMoneyPeriodQuantityRangeRatioReferenceSampledDataSignatureTimingContactDetailContributorDataRequirementExpressionParameterDefinitionRelatedArtifactTriggerDefinitionUsageContextDosageMeta</t>
+  </si>
+  <si>
+    <t>Media.extension:informant</t>
+  </si>
+  <si>
+    <t>informant</t>
+  </si>
+  <si>
+    <t>Informateur</t>
+  </si>
+  <si>
+    <t>Media.extension:informant.id</t>
+  </si>
+  <si>
+    <t>Media.extension:informant.extension</t>
+  </si>
+  <si>
+    <t>Media.extension:informant.extension:type</t>
+  </si>
+  <si>
+    <t>Media.extension:informant.extension:type.id</t>
+  </si>
+  <si>
+    <t>Media.extension:informant.extension:type.extension</t>
+  </si>
+  <si>
+    <t>Media.extension:informant.extension:type.url</t>
+  </si>
+  <si>
+    <t>Media.extension:informant.extension:type.value[x]</t>
+  </si>
+  <si>
+    <t>INF</t>
+  </si>
+  <si>
+    <t>Media.extension:informant.extension:typeCode</t>
+  </si>
+  <si>
+    <t>Media.extension:informant.extension:typeCode.id</t>
+  </si>
+  <si>
+    <t>Media.extension:informant.extension:typeCode.extension</t>
+  </si>
+  <si>
+    <t>Media.extension:informant.extension:typeCode.url</t>
+  </si>
+  <si>
+    <t>Media.extension:informant.extension:typeCode.value[x]</t>
+  </si>
+  <si>
+    <t>Media.extension:informant.extension:actor</t>
+  </si>
+  <si>
+    <t>Media.extension:informant.extension:actor.id</t>
+  </si>
+  <si>
+    <t>Media.extension:informant.extension:actor.extension</t>
+  </si>
+  <si>
+    <t>Media.extension:informant.extension:actor.url</t>
+  </si>
+  <si>
+    <t>Media.extension:informant.extension:actor.value[x]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Reference(https://interop.esante.gouv.fr/ig/document/core/StructureDefinition/fr-practitionerRole-document|https://interop.esante.gouv.fr/ig/document/core/StructureDefinition/fr-related-person-document|https://interop.esante.gouv.fr/ig/document/core/StructureDefinition/fr-patient-ins-document|https://interop.esante.gouv.fr/ig/document/core/StructureDefinition/fr-patient-document)
+</t>
+  </si>
+  <si>
+    <t>Media.extension:informant.url</t>
+  </si>
+  <si>
+    <t>Media.extension:informant.value[x]</t>
+  </si>
+  <si>
+    <t>Media.extension:participant</t>
+  </si>
+  <si>
+    <t>participant</t>
+  </si>
+  <si>
+    <t>Participant : Personne ayant participé à l’acte</t>
+  </si>
+  <si>
+    <t>Media.extension:participant.id</t>
+  </si>
+  <si>
+    <t>Media.extension:participant.extension</t>
+  </si>
+  <si>
+    <t>Media.extension:participant.extension:type</t>
+  </si>
+  <si>
+    <t>Media.extension:participant.extension:type.id</t>
+  </si>
+  <si>
+    <t>Media.extension:participant.extension:type.extension</t>
+  </si>
+  <si>
+    <t>Media.extension:participant.extension:type.url</t>
+  </si>
+  <si>
+    <t>Media.extension:participant.extension:type.value[x]</t>
+  </si>
+  <si>
+    <t>PART</t>
+  </si>
+  <si>
+    <t>Media.extension:participant.extension:typeCode</t>
+  </si>
+  <si>
+    <t>Media.extension:participant.extension:typeCode.id</t>
+  </si>
+  <si>
+    <t>Media.extension:participant.extension:typeCode.extension</t>
+  </si>
+  <si>
+    <t>Media.extension:participant.extension:typeCode.url</t>
+  </si>
+  <si>
+    <t>Media.extension:participant.extension:typeCode.value[x]</t>
+  </si>
+  <si>
+    <t>Media.extension:participant.extension:actor</t>
+  </si>
+  <si>
+    <t>Media.extension:participant.extension:actor.id</t>
+  </si>
+  <si>
+    <t>Media.extension:participant.extension:actor.extension</t>
+  </si>
+  <si>
+    <t>Media.extension:participant.extension:actor.url</t>
+  </si>
+  <si>
+    <t>Media.extension:participant.extension:actor.value[x]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Reference(https://interop.esante.gouv.fr/ig/document/core/StructureDefinition/fr-practitionerRole-document|https://interop.esante.gouv.fr/ig/document/core/StructureDefinition/fr-related-person-document|https://interop.esante.gouv.fr/ig/document/core/StructureDefinition/fr-patient-ins-document|https://interop.esante.gouv.fr/ig/document/core/StructureDefinition/fr-patient-document|https://interop.esante.gouv.fr/ig/document/core/StructureDefinition/fr-device-auteur-document|https://interop.esante.gouv.fr/ig/document/core/StructureDefinition/fr-organization-document)
+</t>
+  </si>
+  <si>
+    <t>Media.extension:participant.url</t>
+  </si>
+  <si>
+    <t>Media.extension:participant.value[x]</t>
+  </si>
+  <si>
+    <t>Media.modifierExtension</t>
+  </si>
+  <si>
     <t>extensions
 user content</t>
   </si>
   <si>
-    <t xml:space="preserve">Extension
-</t>
-  </si>
-  <si>
-    <t>Additional content defined by implementations</t>
-  </si>
-  <si>
-    <t>May be used to represent additional information that is not part of the basic definition of the resource. To make the use of extensions safe and manageable, there is a strict set of governance  applied to the definition and use of extensions. Though any implementer can define an extension, there is a set of requirements that SHALL be met as part of the definition of the extension.</t>
-  </si>
-  <si>
-    <t>There can be no stigma associated with the use of extensions by any application, project, or standard - regardless of the institution or jurisdiction that uses or defines the extensions.  The use of extensions is what allows the FHIR specification to retain a core level of simplicity for everyone.</t>
-  </si>
-  <si>
-    <t>DomainResource.extension</t>
-  </si>
-  <si>
-    <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
-ext-1:Must have either extensions or value[x], not both {extension.exists() != value.exists()}</t>
-  </si>
-  <si>
-    <t>Media.modifierExtension</t>
-  </si>
-  <si>
     <t>Extensions that cannot be ignored</t>
   </si>
   <si>
     <t>May be used to represent additional information that is not part of the basic definition of the resource and that modifies the understanding of the element that contains it and/or the understanding of the containing element's descendants. Usually modifier elements provide negation or qualification. To make the use of extensions safe and manageable, there is a strict set of governance applied to the definition and use of extensions. Though any implementer is allowed to define an extension, there is a set of requirements that SHALL be met as part of the definition of the extension. Applications processing a resource are required to check for modifier extensions.
 Modifier extensions SHALL NOT change the meaning of any elements on Resource or DomainResource (including cannot change the meaning of modifierExtension itself).</t>
+  </si>
+  <si>
+    <t>There can be no stigma associated with the use of extensions by any application, project, or standard - regardless of the institution or jurisdiction that uses or defines the extensions.  The use of extensions is what allows the FHIR specification to retain a core level of simplicity for everyone.</t>
   </si>
   <si>
     <t>Modifier extensions allow for extensions that *cannot* be safely ignored to be clearly distinguished from the vast majority of extensions which can be safely ignored.  This promotes interoperability by eliminating the need for implementers to prohibit the presence of extensions. For further information, see the [definition of modifier extensions](http://hl7.org/fhir/R4/extensibility.html#modifierExtension).</t>
@@ -573,9 +909,6 @@
 Unknown does not represent "other" - one of the defined statuses must apply.  Unknown is used when the authoring system is not sure what the current status is.</t>
   </si>
   <si>
-    <t>required</t>
-  </si>
-  <si>
     <t>Codes identifying the lifecycle stage of an event.</t>
   </si>
   <si>
@@ -595,10 +928,6 @@
   </si>
   <si>
     <t>Media.type</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CodeableConcept
-</t>
   </si>
   <si>
     <t>Classification of media as image, video, or audio</t>
@@ -809,409 +1138,110 @@
     <t>Media.operator.id</t>
   </si>
   <si>
-    <t xml:space="preserve">string
+    <t>Media.operator.extension</t>
+  </si>
+  <si>
+    <t>Additional content defined by implementations</t>
+  </si>
+  <si>
+    <t>May be used to represent additional information that is not part of the basic definition of the element. To make the use of extensions safe and manageable, there is a strict set of governance  applied to the definition and use of extensions. Though any implementer can define an extension, there is a set of requirements that SHALL be met as part of the definition of the extension.</t>
+  </si>
+  <si>
+    <t>Media.operator.extension:performer</t>
+  </si>
+  <si>
+    <t>performer</t>
+  </si>
+  <si>
+    <t>Performer : Personne ayant réalisé l’acte</t>
+  </si>
+  <si>
+    <t>Media.operator.extension:performer.id</t>
+  </si>
+  <si>
+    <t>Media.operator.extension.id</t>
+  </si>
+  <si>
+    <t>Media.operator.extension:performer.extension</t>
+  </si>
+  <si>
+    <t>Media.operator.extension.extension</t>
+  </si>
+  <si>
+    <t>Media.operator.extension:performer.extension:type</t>
+  </si>
+  <si>
+    <t>Media.operator.extension:performer.extension:type.id</t>
+  </si>
+  <si>
+    <t>Media.operator.extension.extension.id</t>
+  </si>
+  <si>
+    <t>Media.operator.extension:performer.extension:type.extension</t>
+  </si>
+  <si>
+    <t>Media.operator.extension.extension.extension</t>
+  </si>
+  <si>
+    <t>Media.operator.extension:performer.extension:type.url</t>
+  </si>
+  <si>
+    <t>Media.operator.extension.extension.url</t>
+  </si>
+  <si>
+    <t>Media.operator.extension:performer.extension:type.value[x]</t>
+  </si>
+  <si>
+    <t>Media.operator.extension.extension.value[x]</t>
+  </si>
+  <si>
+    <t>PRF</t>
+  </si>
+  <si>
+    <t>Media.operator.extension:performer.extension:typeCode</t>
+  </si>
+  <si>
+    <t>Media.operator.extension:performer.extension:typeCode.id</t>
+  </si>
+  <si>
+    <t>Media.operator.extension:performer.extension:typeCode.extension</t>
+  </si>
+  <si>
+    <t>Media.operator.extension:performer.extension:typeCode.url</t>
+  </si>
+  <si>
+    <t>Media.operator.extension:performer.extension:typeCode.value[x]</t>
+  </si>
+  <si>
+    <t>Media.operator.extension:performer.extension:actor</t>
+  </si>
+  <si>
+    <t>Media.operator.extension:performer.extension:actor.id</t>
+  </si>
+  <si>
+    <t>Media.operator.extension:performer.extension:actor.extension</t>
+  </si>
+  <si>
+    <t>Media.operator.extension:performer.extension:actor.url</t>
+  </si>
+  <si>
+    <t>Media.operator.extension:performer.extension:actor.value[x]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Reference(https://interop.esante.gouv.fr/ig/document/core/StructureDefinition/fr-practitionerRole-document|https://interop.esante.gouv.fr/ig/document/core/StructureDefinition/fr-organization-document|https://interop.esante.gouv.fr/ig/document/core/StructureDefinition/fr-device-auteur-document)
 </t>
   </si>
   <si>
-    <t>Unique id for inter-element referencing</t>
-  </si>
-  <si>
-    <t>Unique id for the element within a resource (for internal references). This may be any string value that does not contain spaces.</t>
-  </si>
-  <si>
-    <t>Element.id</t>
-  </si>
-  <si>
-    <t>n/a</t>
-  </si>
-  <si>
-    <t>Media.operator.extension</t>
-  </si>
-  <si>
-    <t>May be used to represent additional information that is not part of the basic definition of the element. To make the use of extensions safe and manageable, there is a strict set of governance  applied to the definition and use of extensions. Though any implementer can define an extension, there is a set of requirements that SHALL be met as part of the definition of the extension.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">value:url}
-</t>
-  </si>
-  <si>
-    <t>Extensions are always sliced by (at least) url</t>
-  </si>
-  <si>
-    <t>open</t>
-  </si>
-  <si>
-    <t>Element.extension</t>
-  </si>
-  <si>
-    <t>Media.operator.extension:performer</t>
-  </si>
-  <si>
-    <t>performer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Extension {https://interop.esante.gouv.fr/ig/document/core/StructureDefinition/fr-actor-extension}
-</t>
-  </si>
-  <si>
-    <t>Performer : Personne ayant réalisé l’acte</t>
-  </si>
-  <si>
-    <t>Extension permettant de représenter un acteur impliqué dans le document avec son type et sa référence.</t>
-  </si>
-  <si>
-    <t>Media.operator.extension:performer.id</t>
-  </si>
-  <si>
-    <t>Media.operator.extension.id</t>
-  </si>
-  <si>
-    <t>Media.operator.extension:performer.extension</t>
-  </si>
-  <si>
-    <t>Media.operator.extension.extension</t>
-  </si>
-  <si>
-    <t>2</t>
-  </si>
-  <si>
-    <t>Extension</t>
-  </si>
-  <si>
-    <t>An Extension</t>
-  </si>
-  <si>
-    <t>Media.operator.extension:performer.extension:type</t>
-  </si>
-  <si>
-    <t>type</t>
-  </si>
-  <si>
-    <t>Media.operator.extension:performer.extension:type.id</t>
-  </si>
-  <si>
-    <t>Media.operator.extension.extension.id</t>
-  </si>
-  <si>
-    <t>Media.operator.extension:performer.extension:type.extension</t>
-  </si>
-  <si>
-    <t>Media.operator.extension.extension.extension</t>
-  </si>
-  <si>
-    <t>Media.operator.extension:performer.extension:type.url</t>
-  </si>
-  <si>
-    <t>Media.operator.extension.extension.url</t>
-  </si>
-  <si>
-    <t>identifies the meaning of the extension</t>
-  </si>
-  <si>
-    <t>Source of the definition for the extension code - a logical name or a URL.</t>
-  </si>
-  <si>
-    <t>The definition may point directly to a computable or human-readable definition of the extensibility codes, or it may be a logical URI as declared in some other specification. The definition SHALL be a URI for the Structure Definition defining the extension.</t>
-  </si>
-  <si>
-    <t>Extension.url</t>
-  </si>
-  <si>
-    <t>Media.operator.extension:performer.extension:type.value[x]</t>
-  </si>
-  <si>
-    <t>Media.operator.extension.extension.value[x]</t>
-  </si>
-  <si>
-    <t>Value of extension</t>
-  </si>
-  <si>
-    <t>Value of extension - must be one of a constrained set of the data types (see [Extensibility](http://hl7.org/fhir/R4/extensibility.html) for a list).</t>
-  </si>
-  <si>
-    <t>PRF</t>
-  </si>
-  <si>
-    <t>https://interop.esante.gouv.fr/ig/document/core/ValueSet/fr-vs-actor-type-document</t>
-  </si>
-  <si>
-    <t>Extension.value[x]</t>
-  </si>
-  <si>
-    <t>Media.operator.extension:performer.extension:typeCode</t>
-  </si>
-  <si>
-    <t>typeCode</t>
-  </si>
-  <si>
-    <t>Type de participation</t>
-  </si>
-  <si>
-    <t>Media.operator.extension:performer.extension:typeCode.id</t>
-  </si>
-  <si>
-    <t>Media.operator.extension:performer.extension:typeCode.extension</t>
-  </si>
-  <si>
-    <t>Media.operator.extension:performer.extension:typeCode.url</t>
-  </si>
-  <si>
-    <t>Media.operator.extension:performer.extension:typeCode.value[x]</t>
-  </si>
-  <si>
-    <t>Media.operator.extension:performer.extension:actor</t>
-  </si>
-  <si>
-    <t>actor</t>
-  </si>
-  <si>
-    <t>Référence vers le rôle du praticien dans le document</t>
-  </si>
-  <si>
-    <t>Media.operator.extension:performer.extension:actor.id</t>
-  </si>
-  <si>
-    <t>Media.operator.extension:performer.extension:actor.extension</t>
-  </si>
-  <si>
-    <t>Media.operator.extension:performer.extension:actor.url</t>
-  </si>
-  <si>
-    <t>Media.operator.extension:performer.extension:actor.value[x]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Reference(https://interop.esante.gouv.fr/ig/document/core/StructureDefinition/fr-practitionerRole-document|Device|https://interop.esante.gouv.fr/ig/document/core/StructureDefinition/fr-device-auteur-document|https://interop.esante.gouv.fr/ig/document/core/StructureDefinition/fr-organization-document|https://interop.esante.gouv.fr/ig/document/core/StructureDefinition/fr-related-person-document|https://interop.esante.gouv.fr/ig/document/core/StructureDefinition/fr-patient-ins-document|https://interop.esante.gouv.fr/ig/document/core/StructureDefinition/fr-patient-document)
-</t>
-  </si>
-  <si>
     <t>Media.operator.extension:performer.url</t>
   </si>
   <si>
     <t>Media.operator.extension.url</t>
   </si>
   <si>
-    <t>https://interop.esante.gouv.fr/ig/document/core/StructureDefinition/fr-actor-extension</t>
-  </si>
-  <si>
     <t>Media.operator.extension:performer.value[x]</t>
   </si>
   <si>
     <t>Media.operator.extension.value[x]</t>
-  </si>
-  <si>
-    <t>base64Binary
-booleancanonicalcodedatedateTimedecimalidinstantintegermarkdownoidpositiveIntstringtimeunsignedInturiurluuidAddressAgeAnnotationAttachmentCodeableConceptCodingContactPointCountDistanceDurationHumanNameIdentifierMoneyPeriodQuantityRangeRatioReferenceSampledDataSignatureTimingContactDetailContributorDataRequirementExpressionParameterDefinitionRelatedArtifactTriggerDefinitionUsageContextDosageMeta</t>
-  </si>
-  <si>
-    <t>Media.operator.extension:author</t>
-  </si>
-  <si>
-    <t>author</t>
-  </si>
-  <si>
-    <t>Auteur du média</t>
-  </si>
-  <si>
-    <t>Media.operator.extension:author.id</t>
-  </si>
-  <si>
-    <t>Media.operator.extension:author.extension</t>
-  </si>
-  <si>
-    <t>Media.operator.extension:author.extension:type</t>
-  </si>
-  <si>
-    <t>Media.operator.extension:author.extension:type.id</t>
-  </si>
-  <si>
-    <t>Media.operator.extension:author.extension:type.extension</t>
-  </si>
-  <si>
-    <t>Media.operator.extension:author.extension:type.url</t>
-  </si>
-  <si>
-    <t>Media.operator.extension:author.extension:type.value[x]</t>
-  </si>
-  <si>
-    <t>AUT</t>
-  </si>
-  <si>
-    <t>Media.operator.extension:author.extension:typeCode</t>
-  </si>
-  <si>
-    <t>Media.operator.extension:author.extension:typeCode.id</t>
-  </si>
-  <si>
-    <t>Media.operator.extension:author.extension:typeCode.extension</t>
-  </si>
-  <si>
-    <t>Media.operator.extension:author.extension:typeCode.url</t>
-  </si>
-  <si>
-    <t>Media.operator.extension:author.extension:typeCode.value[x]</t>
-  </si>
-  <si>
-    <t>Media.operator.extension:author.extension:actor</t>
-  </si>
-  <si>
-    <t>Media.operator.extension:author.extension:actor.id</t>
-  </si>
-  <si>
-    <t>Media.operator.extension:author.extension:actor.extension</t>
-  </si>
-  <si>
-    <t>Media.operator.extension:author.extension:actor.url</t>
-  </si>
-  <si>
-    <t>Media.operator.extension:author.extension:actor.value[x]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Reference(https://interop.esante.gouv.fr/ig/document/core/StructureDefinition/fr-device-auteur-document|https://interop.esante.gouv.fr/ig/document/core/StructureDefinition/fr-practitionerRole-document)
-</t>
-  </si>
-  <si>
-    <t>Media.operator.extension:author.url</t>
-  </si>
-  <si>
-    <t>Media.operator.extension:author.value[x]</t>
-  </si>
-  <si>
-    <t>Media.operator.extension:informant</t>
-  </si>
-  <si>
-    <t>informant</t>
-  </si>
-  <si>
-    <t>Informateur</t>
-  </si>
-  <si>
-    <t>Media.operator.extension:informant.id</t>
-  </si>
-  <si>
-    <t>Media.operator.extension:informant.extension</t>
-  </si>
-  <si>
-    <t>Media.operator.extension:informant.extension:type</t>
-  </si>
-  <si>
-    <t>Media.operator.extension:informant.extension:type.id</t>
-  </si>
-  <si>
-    <t>Media.operator.extension:informant.extension:type.extension</t>
-  </si>
-  <si>
-    <t>Media.operator.extension:informant.extension:type.url</t>
-  </si>
-  <si>
-    <t>Media.operator.extension:informant.extension:type.value[x]</t>
-  </si>
-  <si>
-    <t>INF</t>
-  </si>
-  <si>
-    <t>Media.operator.extension:informant.extension:typeCode</t>
-  </si>
-  <si>
-    <t>Media.operator.extension:informant.extension:typeCode.id</t>
-  </si>
-  <si>
-    <t>Media.operator.extension:informant.extension:typeCode.extension</t>
-  </si>
-  <si>
-    <t>Media.operator.extension:informant.extension:typeCode.url</t>
-  </si>
-  <si>
-    <t>Media.operator.extension:informant.extension:typeCode.value[x]</t>
-  </si>
-  <si>
-    <t>Media.operator.extension:informant.extension:actor</t>
-  </si>
-  <si>
-    <t>Media.operator.extension:informant.extension:actor.id</t>
-  </si>
-  <si>
-    <t>Media.operator.extension:informant.extension:actor.extension</t>
-  </si>
-  <si>
-    <t>Media.operator.extension:informant.extension:actor.url</t>
-  </si>
-  <si>
-    <t>Media.operator.extension:informant.extension:actor.value[x]</t>
-  </si>
-  <si>
-    <t>Media.operator.extension:informant.url</t>
-  </si>
-  <si>
-    <t>Media.operator.extension:informant.value[x]</t>
-  </si>
-  <si>
-    <t>Media.operator.extension:participant</t>
-  </si>
-  <si>
-    <t>participant</t>
-  </si>
-  <si>
-    <t>Participant : Personne ayant participé à l’acte</t>
-  </si>
-  <si>
-    <t>Media.operator.extension:participant.id</t>
-  </si>
-  <si>
-    <t>Media.operator.extension:participant.extension</t>
-  </si>
-  <si>
-    <t>Media.operator.extension:participant.extension:type</t>
-  </si>
-  <si>
-    <t>Media.operator.extension:participant.extension:type.id</t>
-  </si>
-  <si>
-    <t>Media.operator.extension:participant.extension:type.extension</t>
-  </si>
-  <si>
-    <t>Media.operator.extension:participant.extension:type.url</t>
-  </si>
-  <si>
-    <t>Media.operator.extension:participant.extension:type.value[x]</t>
-  </si>
-  <si>
-    <t>PART</t>
-  </si>
-  <si>
-    <t>Media.operator.extension:participant.extension:typeCode</t>
-  </si>
-  <si>
-    <t>Media.operator.extension:participant.extension:typeCode.id</t>
-  </si>
-  <si>
-    <t>Media.operator.extension:participant.extension:typeCode.extension</t>
-  </si>
-  <si>
-    <t>Media.operator.extension:participant.extension:typeCode.url</t>
-  </si>
-  <si>
-    <t>Media.operator.extension:participant.extension:typeCode.value[x]</t>
-  </si>
-  <si>
-    <t>Media.operator.extension:participant.extension:actor</t>
-  </si>
-  <si>
-    <t>Media.operator.extension:participant.extension:actor.id</t>
-  </si>
-  <si>
-    <t>Media.operator.extension:participant.extension:actor.extension</t>
-  </si>
-  <si>
-    <t>Media.operator.extension:participant.extension:actor.url</t>
-  </si>
-  <si>
-    <t>Media.operator.extension:participant.extension:actor.value[x]</t>
-  </si>
-  <si>
-    <t>Media.operator.extension:participant.url</t>
-  </si>
-  <si>
-    <t>Media.operator.extension:participant.value[x]</t>
   </si>
   <si>
     <t>Media.operator.reference</t>
@@ -2011,7 +2041,7 @@
   <dimension ref="A1:AQ128"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
-    <col min="1" max="1" width="54.5703125" customWidth="true" bestFit="true"/>
+    <col min="1" max="1" width="53.953125" customWidth="true" bestFit="true"/>
     <col min="2" max="2" width="37.4453125" customWidth="true" bestFit="true"/>
     <col min="3" max="3" width="10.8515625" customWidth="true" bestFit="true" hidden="true"/>
     <col min="4" max="4" width="34.21875" customWidth="true" bestFit="true" hidden="true"/>
@@ -3052,7 +3082,7 @@
       </c>
       <c r="C9" s="2"/>
       <c r="D9" t="s" s="2">
-        <v>135</v>
+        <v>80</v>
       </c>
       <c r="E9" s="2"/>
       <c r="F9" t="s" s="2">
@@ -3071,17 +3101,15 @@
         <v>80</v>
       </c>
       <c r="K9" t="s" s="2">
+        <v>135</v>
+      </c>
+      <c r="L9" t="s" s="2">
         <v>136</v>
       </c>
-      <c r="L9" t="s" s="2">
+      <c r="M9" t="s" s="2">
         <v>137</v>
       </c>
-      <c r="M9" t="s" s="2">
-        <v>138</v>
-      </c>
-      <c r="N9" t="s" s="2">
-        <v>139</v>
-      </c>
+      <c r="N9" s="2"/>
       <c r="O9" s="2"/>
       <c r="P9" t="s" s="2">
         <v>80</v>
@@ -3118,16 +3146,14 @@
         <v>80</v>
       </c>
       <c r="AB9" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AC9" t="s" s="2">
-        <v>80</v>
-      </c>
+        <v>138</v>
+      </c>
+      <c r="AC9" s="2"/>
       <c r="AD9" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AE9" t="s" s="2">
-        <v>80</v>
+        <v>139</v>
       </c>
       <c r="AF9" t="s" s="2">
         <v>140</v>
@@ -3148,7 +3174,7 @@
         <v>80</v>
       </c>
       <c r="AL9" t="s" s="2">
-        <v>133</v>
+        <v>80</v>
       </c>
       <c r="AM9" t="s" s="2">
         <v>80</v>
@@ -3171,11 +3197,13 @@
         <v>142</v>
       </c>
       <c r="B10" t="s" s="2">
-        <v>142</v>
-      </c>
-      <c r="C10" s="2"/>
+        <v>134</v>
+      </c>
+      <c r="C10" t="s" s="2">
+        <v>143</v>
+      </c>
       <c r="D10" t="s" s="2">
-        <v>135</v>
+        <v>80</v>
       </c>
       <c r="E10" s="2"/>
       <c r="F10" t="s" s="2">
@@ -3188,26 +3216,22 @@
         <v>80</v>
       </c>
       <c r="I10" t="s" s="2">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="J10" t="s" s="2">
         <v>80</v>
       </c>
       <c r="K10" t="s" s="2">
-        <v>136</v>
+        <v>144</v>
       </c>
       <c r="L10" t="s" s="2">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="M10" t="s" s="2">
-        <v>144</v>
-      </c>
-      <c r="N10" t="s" s="2">
-        <v>139</v>
-      </c>
-      <c r="O10" t="s" s="2">
-        <v>145</v>
-      </c>
+        <v>146</v>
+      </c>
+      <c r="N10" s="2"/>
+      <c r="O10" s="2"/>
       <c r="P10" t="s" s="2">
         <v>80</v>
       </c>
@@ -3255,7 +3279,7 @@
         <v>80</v>
       </c>
       <c r="AF10" t="s" s="2">
-        <v>146</v>
+        <v>140</v>
       </c>
       <c r="AG10" t="s" s="2">
         <v>81</v>
@@ -3264,7 +3288,7 @@
         <v>82</v>
       </c>
       <c r="AI10" t="s" s="2">
-        <v>80</v>
+        <v>147</v>
       </c>
       <c r="AJ10" t="s" s="2">
         <v>141</v>
@@ -3273,7 +3297,7 @@
         <v>80</v>
       </c>
       <c r="AL10" t="s" s="2">
-        <v>133</v>
+        <v>80</v>
       </c>
       <c r="AM10" t="s" s="2">
         <v>80</v>
@@ -3293,10 +3317,10 @@
     </row>
     <row r="11" hidden="true">
       <c r="A11" t="s" s="2">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="B11" t="s" s="2">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="C11" s="2"/>
       <c r="D11" t="s" s="2">
@@ -3307,7 +3331,7 @@
         <v>81</v>
       </c>
       <c r="G11" t="s" s="2">
-        <v>82</v>
+        <v>90</v>
       </c>
       <c r="H11" t="s" s="2">
         <v>80</v>
@@ -3316,20 +3340,18 @@
         <v>80</v>
       </c>
       <c r="J11" t="s" s="2">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="K11" t="s" s="2">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="L11" t="s" s="2">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="M11" t="s" s="2">
-        <v>150</v>
-      </c>
-      <c r="N11" t="s" s="2">
-        <v>151</v>
-      </c>
+        <v>152</v>
+      </c>
+      <c r="N11" s="2"/>
       <c r="O11" s="2"/>
       <c r="P11" t="s" s="2">
         <v>80</v>
@@ -3378,82 +3400,80 @@
         <v>80</v>
       </c>
       <c r="AF11" t="s" s="2">
-        <v>147</v>
+        <v>153</v>
       </c>
       <c r="AG11" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH11" t="s" s="2">
-        <v>82</v>
+        <v>90</v>
       </c>
       <c r="AI11" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AJ11" t="s" s="2">
-        <v>102</v>
+        <v>80</v>
       </c>
       <c r="AK11" t="s" s="2">
-        <v>152</v>
+        <v>80</v>
       </c>
       <c r="AL11" t="s" s="2">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="AM11" t="s" s="2">
-        <v>154</v>
+        <v>80</v>
       </c>
       <c r="AN11" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AO11" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AP11" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AQ11" t="s" s="2">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="12" hidden="true">
+      <c r="A12" t="s" s="2">
         <v>155</v>
-      </c>
-      <c r="AO11" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AP11" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AQ11" t="s" s="2">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="s" s="2">
-        <v>156</v>
       </c>
       <c r="B12" t="s" s="2">
         <v>156</v>
       </c>
       <c r="C12" s="2"/>
       <c r="D12" t="s" s="2">
-        <v>157</v>
+        <v>80</v>
       </c>
       <c r="E12" s="2"/>
       <c r="F12" t="s" s="2">
-        <v>81</v>
+        <v>157</v>
       </c>
       <c r="G12" t="s" s="2">
         <v>82</v>
       </c>
       <c r="H12" t="s" s="2">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="I12" t="s" s="2">
         <v>80</v>
       </c>
       <c r="J12" t="s" s="2">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="K12" t="s" s="2">
-        <v>158</v>
+        <v>135</v>
       </c>
       <c r="L12" t="s" s="2">
-        <v>159</v>
+        <v>136</v>
       </c>
       <c r="M12" t="s" s="2">
-        <v>160</v>
+        <v>137</v>
       </c>
       <c r="N12" s="2"/>
-      <c r="O12" t="s" s="2">
-        <v>161</v>
-      </c>
+      <c r="O12" s="2"/>
       <c r="P12" t="s" s="2">
         <v>80</v>
       </c>
@@ -3489,19 +3509,19 @@
         <v>80</v>
       </c>
       <c r="AB12" t="s" s="2">
-        <v>80</v>
+        <v>138</v>
       </c>
       <c r="AC12" t="s" s="2">
-        <v>80</v>
+        <v>158</v>
       </c>
       <c r="AD12" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AE12" t="s" s="2">
-        <v>80</v>
+        <v>139</v>
       </c>
       <c r="AF12" t="s" s="2">
-        <v>156</v>
+        <v>159</v>
       </c>
       <c r="AG12" t="s" s="2">
         <v>81</v>
@@ -3513,13 +3533,13 @@
         <v>80</v>
       </c>
       <c r="AJ12" t="s" s="2">
-        <v>102</v>
+        <v>141</v>
       </c>
       <c r="AK12" t="s" s="2">
-        <v>162</v>
+        <v>80</v>
       </c>
       <c r="AL12" t="s" s="2">
-        <v>163</v>
+        <v>80</v>
       </c>
       <c r="AM12" t="s" s="2">
         <v>80</v>
@@ -3537,48 +3557,46 @@
         <v>80</v>
       </c>
     </row>
-    <row r="13">
+    <row r="13" hidden="true">
       <c r="A13" t="s" s="2">
-        <v>164</v>
+        <v>160</v>
       </c>
       <c r="B13" t="s" s="2">
-        <v>164</v>
-      </c>
-      <c r="C13" s="2"/>
+        <v>156</v>
+      </c>
+      <c r="C13" t="s" s="2">
+        <v>161</v>
+      </c>
       <c r="D13" t="s" s="2">
-        <v>165</v>
+        <v>80</v>
       </c>
       <c r="E13" s="2"/>
       <c r="F13" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="G13" t="s" s="2">
-        <v>82</v>
+        <v>90</v>
       </c>
       <c r="H13" t="s" s="2">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="I13" t="s" s="2">
         <v>80</v>
       </c>
       <c r="J13" t="s" s="2">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="K13" t="s" s="2">
-        <v>166</v>
+        <v>135</v>
       </c>
       <c r="L13" t="s" s="2">
-        <v>167</v>
+        <v>136</v>
       </c>
       <c r="M13" t="s" s="2">
-        <v>168</v>
-      </c>
-      <c r="N13" t="s" s="2">
-        <v>169</v>
-      </c>
-      <c r="O13" t="s" s="2">
-        <v>170</v>
-      </c>
+        <v>137</v>
+      </c>
+      <c r="N13" s="2"/>
+      <c r="O13" s="2"/>
       <c r="P13" t="s" s="2">
         <v>80</v>
       </c>
@@ -3626,7 +3644,7 @@
         <v>80</v>
       </c>
       <c r="AF13" t="s" s="2">
-        <v>164</v>
+        <v>159</v>
       </c>
       <c r="AG13" t="s" s="2">
         <v>81</v>
@@ -3638,13 +3656,13 @@
         <v>80</v>
       </c>
       <c r="AJ13" t="s" s="2">
-        <v>102</v>
+        <v>141</v>
       </c>
       <c r="AK13" t="s" s="2">
-        <v>171</v>
+        <v>80</v>
       </c>
       <c r="AL13" t="s" s="2">
-        <v>172</v>
+        <v>80</v>
       </c>
       <c r="AM13" t="s" s="2">
         <v>80</v>
@@ -3664,10 +3682,10 @@
     </row>
     <row r="14" hidden="true">
       <c r="A14" t="s" s="2">
-        <v>173</v>
+        <v>162</v>
       </c>
       <c r="B14" t="s" s="2">
-        <v>173</v>
+        <v>163</v>
       </c>
       <c r="C14" s="2"/>
       <c r="D14" t="s" s="2">
@@ -3675,7 +3693,7 @@
       </c>
       <c r="E14" s="2"/>
       <c r="F14" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="G14" t="s" s="2">
         <v>90</v>
@@ -3684,23 +3702,21 @@
         <v>80</v>
       </c>
       <c r="I14" t="s" s="2">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="J14" t="s" s="2">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="K14" t="s" s="2">
-        <v>110</v>
+        <v>150</v>
       </c>
       <c r="L14" t="s" s="2">
-        <v>174</v>
+        <v>151</v>
       </c>
       <c r="M14" t="s" s="2">
-        <v>175</v>
-      </c>
-      <c r="N14" t="s" s="2">
-        <v>176</v>
-      </c>
+        <v>152</v>
+      </c>
+      <c r="N14" s="2"/>
       <c r="O14" s="2"/>
       <c r="P14" t="s" s="2">
         <v>80</v>
@@ -3725,13 +3741,13 @@
         <v>80</v>
       </c>
       <c r="X14" t="s" s="2">
-        <v>177</v>
+        <v>80</v>
       </c>
       <c r="Y14" t="s" s="2">
-        <v>178</v>
+        <v>80</v>
       </c>
       <c r="Z14" t="s" s="2">
-        <v>179</v>
+        <v>80</v>
       </c>
       <c r="AA14" t="s" s="2">
         <v>80</v>
@@ -3749,10 +3765,10 @@
         <v>80</v>
       </c>
       <c r="AF14" t="s" s="2">
-        <v>173</v>
+        <v>153</v>
       </c>
       <c r="AG14" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="AH14" t="s" s="2">
         <v>90</v>
@@ -3761,22 +3777,22 @@
         <v>80</v>
       </c>
       <c r="AJ14" t="s" s="2">
-        <v>102</v>
+        <v>80</v>
       </c>
       <c r="AK14" t="s" s="2">
-        <v>180</v>
+        <v>80</v>
       </c>
       <c r="AL14" t="s" s="2">
-        <v>181</v>
+        <v>154</v>
       </c>
       <c r="AM14" t="s" s="2">
-        <v>182</v>
+        <v>80</v>
       </c>
       <c r="AN14" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AO14" t="s" s="2">
-        <v>183</v>
+        <v>80</v>
       </c>
       <c r="AP14" t="s" s="2">
         <v>80</v>
@@ -3787,10 +3803,10 @@
     </row>
     <row r="15" hidden="true">
       <c r="A15" t="s" s="2">
-        <v>184</v>
+        <v>164</v>
       </c>
       <c r="B15" t="s" s="2">
-        <v>184</v>
+        <v>165</v>
       </c>
       <c r="C15" s="2"/>
       <c r="D15" t="s" s="2">
@@ -3801,7 +3817,7 @@
         <v>81</v>
       </c>
       <c r="G15" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="H15" t="s" s="2">
         <v>80</v>
@@ -3810,21 +3826,19 @@
         <v>80</v>
       </c>
       <c r="J15" t="s" s="2">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="K15" t="s" s="2">
-        <v>185</v>
+        <v>135</v>
       </c>
       <c r="L15" t="s" s="2">
-        <v>186</v>
+        <v>136</v>
       </c>
       <c r="M15" t="s" s="2">
-        <v>187</v>
+        <v>137</v>
       </c>
       <c r="N15" s="2"/>
-      <c r="O15" t="s" s="2">
-        <v>188</v>
-      </c>
+      <c r="O15" s="2"/>
       <c r="P15" t="s" s="2">
         <v>80</v>
       </c>
@@ -3848,52 +3862,52 @@
         <v>80</v>
       </c>
       <c r="X15" t="s" s="2">
-        <v>189</v>
+        <v>80</v>
       </c>
       <c r="Y15" t="s" s="2">
-        <v>190</v>
+        <v>80</v>
       </c>
       <c r="Z15" t="s" s="2">
-        <v>191</v>
+        <v>80</v>
       </c>
       <c r="AA15" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AB15" t="s" s="2">
-        <v>80</v>
+        <v>138</v>
       </c>
       <c r="AC15" t="s" s="2">
-        <v>80</v>
+        <v>158</v>
       </c>
       <c r="AD15" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AE15" t="s" s="2">
-        <v>80</v>
+        <v>139</v>
       </c>
       <c r="AF15" t="s" s="2">
-        <v>184</v>
+        <v>159</v>
       </c>
       <c r="AG15" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH15" t="s" s="2">
-        <v>90</v>
+        <v>82</v>
       </c>
       <c r="AI15" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AJ15" t="s" s="2">
-        <v>102</v>
+        <v>141</v>
       </c>
       <c r="AK15" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AL15" t="s" s="2">
-        <v>192</v>
+        <v>80</v>
       </c>
       <c r="AM15" t="s" s="2">
-        <v>193</v>
+        <v>80</v>
       </c>
       <c r="AN15" t="s" s="2">
         <v>80</v>
@@ -3910,10 +3924,10 @@
     </row>
     <row r="16" hidden="true">
       <c r="A16" t="s" s="2">
-        <v>194</v>
+        <v>166</v>
       </c>
       <c r="B16" t="s" s="2">
-        <v>194</v>
+        <v>167</v>
       </c>
       <c r="C16" s="2"/>
       <c r="D16" t="s" s="2">
@@ -3921,7 +3935,7 @@
       </c>
       <c r="E16" s="2"/>
       <c r="F16" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="G16" t="s" s="2">
         <v>90</v>
@@ -3933,25 +3947,27 @@
         <v>80</v>
       </c>
       <c r="J16" t="s" s="2">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="K16" t="s" s="2">
-        <v>185</v>
+        <v>104</v>
       </c>
       <c r="L16" t="s" s="2">
-        <v>195</v>
+        <v>168</v>
       </c>
       <c r="M16" t="s" s="2">
-        <v>196</v>
-      </c>
-      <c r="N16" s="2"/>
+        <v>169</v>
+      </c>
+      <c r="N16" t="s" s="2">
+        <v>170</v>
+      </c>
       <c r="O16" s="2"/>
       <c r="P16" t="s" s="2">
         <v>80</v>
       </c>
       <c r="Q16" s="2"/>
       <c r="R16" t="s" s="2">
-        <v>80</v>
+        <v>161</v>
       </c>
       <c r="S16" t="s" s="2">
         <v>80</v>
@@ -3969,13 +3985,13 @@
         <v>80</v>
       </c>
       <c r="X16" t="s" s="2">
-        <v>197</v>
+        <v>80</v>
       </c>
       <c r="Y16" t="s" s="2">
-        <v>198</v>
+        <v>80</v>
       </c>
       <c r="Z16" t="s" s="2">
-        <v>199</v>
+        <v>80</v>
       </c>
       <c r="AA16" t="s" s="2">
         <v>80</v>
@@ -3993,10 +4009,10 @@
         <v>80</v>
       </c>
       <c r="AF16" t="s" s="2">
-        <v>194</v>
+        <v>171</v>
       </c>
       <c r="AG16" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="AH16" t="s" s="2">
         <v>90</v>
@@ -4005,19 +4021,19 @@
         <v>80</v>
       </c>
       <c r="AJ16" t="s" s="2">
-        <v>102</v>
+        <v>80</v>
       </c>
       <c r="AK16" t="s" s="2">
-        <v>200</v>
+        <v>80</v>
       </c>
       <c r="AL16" t="s" s="2">
-        <v>201</v>
+        <v>133</v>
       </c>
       <c r="AM16" t="s" s="2">
-        <v>202</v>
+        <v>80</v>
       </c>
       <c r="AN16" t="s" s="2">
-        <v>203</v>
+        <v>80</v>
       </c>
       <c r="AO16" t="s" s="2">
         <v>80</v>
@@ -4031,10 +4047,10 @@
     </row>
     <row r="17" hidden="true">
       <c r="A17" t="s" s="2">
-        <v>204</v>
+        <v>172</v>
       </c>
       <c r="B17" t="s" s="2">
-        <v>204</v>
+        <v>173</v>
       </c>
       <c r="C17" s="2"/>
       <c r="D17" t="s" s="2">
@@ -4054,16 +4070,16 @@
         <v>80</v>
       </c>
       <c r="J17" t="s" s="2">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="K17" t="s" s="2">
-        <v>185</v>
+        <v>110</v>
       </c>
       <c r="L17" t="s" s="2">
-        <v>205</v>
+        <v>174</v>
       </c>
       <c r="M17" t="s" s="2">
-        <v>206</v>
+        <v>175</v>
       </c>
       <c r="N17" s="2"/>
       <c r="O17" s="2"/>
@@ -4075,7 +4091,7 @@
         <v>80</v>
       </c>
       <c r="S17" t="s" s="2">
-        <v>80</v>
+        <v>176</v>
       </c>
       <c r="T17" t="s" s="2">
         <v>80</v>
@@ -4090,13 +4106,11 @@
         <v>80</v>
       </c>
       <c r="X17" t="s" s="2">
-        <v>197</v>
-      </c>
-      <c r="Y17" t="s" s="2">
-        <v>207</v>
-      </c>
+        <v>177</v>
+      </c>
+      <c r="Y17" s="2"/>
       <c r="Z17" t="s" s="2">
-        <v>208</v>
+        <v>178</v>
       </c>
       <c r="AA17" t="s" s="2">
         <v>80</v>
@@ -4114,7 +4128,7 @@
         <v>80</v>
       </c>
       <c r="AF17" t="s" s="2">
-        <v>204</v>
+        <v>179</v>
       </c>
       <c r="AG17" t="s" s="2">
         <v>81</v>
@@ -4132,7 +4146,7 @@
         <v>80</v>
       </c>
       <c r="AL17" t="s" s="2">
-        <v>209</v>
+        <v>133</v>
       </c>
       <c r="AM17" t="s" s="2">
         <v>80</v>
@@ -4150,14 +4164,16 @@
         <v>80</v>
       </c>
     </row>
-    <row r="18">
+    <row r="18" hidden="true">
       <c r="A18" t="s" s="2">
-        <v>210</v>
+        <v>180</v>
       </c>
       <c r="B18" t="s" s="2">
-        <v>210</v>
-      </c>
-      <c r="C18" s="2"/>
+        <v>156</v>
+      </c>
+      <c r="C18" t="s" s="2">
+        <v>181</v>
+      </c>
       <c r="D18" t="s" s="2">
         <v>80</v>
       </c>
@@ -4169,22 +4185,22 @@
         <v>90</v>
       </c>
       <c r="H18" t="s" s="2">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="I18" t="s" s="2">
         <v>80</v>
       </c>
       <c r="J18" t="s" s="2">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="K18" t="s" s="2">
-        <v>211</v>
+        <v>135</v>
       </c>
       <c r="L18" t="s" s="2">
-        <v>212</v>
+        <v>182</v>
       </c>
       <c r="M18" t="s" s="2">
-        <v>213</v>
+        <v>137</v>
       </c>
       <c r="N18" s="2"/>
       <c r="O18" s="2"/>
@@ -4235,31 +4251,31 @@
         <v>80</v>
       </c>
       <c r="AF18" t="s" s="2">
-        <v>210</v>
+        <v>159</v>
       </c>
       <c r="AG18" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH18" t="s" s="2">
-        <v>90</v>
+        <v>82</v>
       </c>
       <c r="AI18" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AJ18" t="s" s="2">
-        <v>102</v>
+        <v>141</v>
       </c>
       <c r="AK18" t="s" s="2">
-        <v>214</v>
+        <v>80</v>
       </c>
       <c r="AL18" t="s" s="2">
-        <v>215</v>
+        <v>80</v>
       </c>
       <c r="AM18" t="s" s="2">
-        <v>216</v>
+        <v>80</v>
       </c>
       <c r="AN18" t="s" s="2">
-        <v>217</v>
+        <v>80</v>
       </c>
       <c r="AO18" t="s" s="2">
         <v>80</v>
@@ -4273,14 +4289,14 @@
     </row>
     <row r="19" hidden="true">
       <c r="A19" t="s" s="2">
-        <v>218</v>
+        <v>183</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>218</v>
+        <v>163</v>
       </c>
       <c r="C19" s="2"/>
       <c r="D19" t="s" s="2">
-        <v>219</v>
+        <v>80</v>
       </c>
       <c r="E19" s="2"/>
       <c r="F19" t="s" s="2">
@@ -4296,23 +4312,19 @@
         <v>80</v>
       </c>
       <c r="J19" t="s" s="2">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="K19" t="s" s="2">
-        <v>220</v>
+        <v>150</v>
       </c>
       <c r="L19" t="s" s="2">
-        <v>221</v>
+        <v>151</v>
       </c>
       <c r="M19" t="s" s="2">
-        <v>222</v>
-      </c>
-      <c r="N19" t="s" s="2">
-        <v>223</v>
-      </c>
-      <c r="O19" t="s" s="2">
-        <v>224</v>
-      </c>
+        <v>152</v>
+      </c>
+      <c r="N19" s="2"/>
+      <c r="O19" s="2"/>
       <c r="P19" t="s" s="2">
         <v>80</v>
       </c>
@@ -4360,7 +4372,7 @@
         <v>80</v>
       </c>
       <c r="AF19" t="s" s="2">
-        <v>218</v>
+        <v>153</v>
       </c>
       <c r="AG19" t="s" s="2">
         <v>81</v>
@@ -4372,16 +4384,16 @@
         <v>80</v>
       </c>
       <c r="AJ19" t="s" s="2">
-        <v>102</v>
+        <v>80</v>
       </c>
       <c r="AK19" t="s" s="2">
-        <v>225</v>
+        <v>80</v>
       </c>
       <c r="AL19" t="s" s="2">
-        <v>226</v>
+        <v>154</v>
       </c>
       <c r="AM19" t="s" s="2">
-        <v>227</v>
+        <v>80</v>
       </c>
       <c r="AN19" t="s" s="2">
         <v>80</v>
@@ -4398,21 +4410,21 @@
     </row>
     <row r="20" hidden="true">
       <c r="A20" t="s" s="2">
-        <v>228</v>
+        <v>184</v>
       </c>
       <c r="B20" t="s" s="2">
-        <v>228</v>
+        <v>165</v>
       </c>
       <c r="C20" s="2"/>
       <c r="D20" t="s" s="2">
-        <v>229</v>
+        <v>80</v>
       </c>
       <c r="E20" s="2"/>
       <c r="F20" t="s" s="2">
         <v>81</v>
       </c>
       <c r="G20" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="H20" t="s" s="2">
         <v>80</v>
@@ -4421,16 +4433,16 @@
         <v>80</v>
       </c>
       <c r="J20" t="s" s="2">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="K20" t="s" s="2">
-        <v>230</v>
+        <v>135</v>
       </c>
       <c r="L20" t="s" s="2">
-        <v>231</v>
+        <v>136</v>
       </c>
       <c r="M20" t="s" s="2">
-        <v>232</v>
+        <v>137</v>
       </c>
       <c r="N20" s="2"/>
       <c r="O20" s="2"/>
@@ -4469,40 +4481,40 @@
         <v>80</v>
       </c>
       <c r="AB20" t="s" s="2">
-        <v>80</v>
+        <v>138</v>
       </c>
       <c r="AC20" t="s" s="2">
-        <v>80</v>
+        <v>158</v>
       </c>
       <c r="AD20" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AE20" t="s" s="2">
-        <v>80</v>
+        <v>139</v>
       </c>
       <c r="AF20" t="s" s="2">
-        <v>228</v>
+        <v>159</v>
       </c>
       <c r="AG20" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH20" t="s" s="2">
-        <v>90</v>
+        <v>82</v>
       </c>
       <c r="AI20" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AJ20" t="s" s="2">
-        <v>102</v>
+        <v>141</v>
       </c>
       <c r="AK20" t="s" s="2">
-        <v>233</v>
+        <v>80</v>
       </c>
       <c r="AL20" t="s" s="2">
-        <v>234</v>
+        <v>80</v>
       </c>
       <c r="AM20" t="s" s="2">
-        <v>235</v>
+        <v>80</v>
       </c>
       <c r="AN20" t="s" s="2">
         <v>80</v>
@@ -4519,10 +4531,10 @@
     </row>
     <row r="21" hidden="true">
       <c r="A21" t="s" s="2">
-        <v>236</v>
+        <v>185</v>
       </c>
       <c r="B21" t="s" s="2">
-        <v>236</v>
+        <v>167</v>
       </c>
       <c r="C21" s="2"/>
       <c r="D21" t="s" s="2">
@@ -4530,7 +4542,7 @@
       </c>
       <c r="E21" s="2"/>
       <c r="F21" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="G21" t="s" s="2">
         <v>90</v>
@@ -4542,19 +4554,19 @@
         <v>80</v>
       </c>
       <c r="J21" t="s" s="2">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="K21" t="s" s="2">
-        <v>237</v>
+        <v>104</v>
       </c>
       <c r="L21" t="s" s="2">
-        <v>238</v>
+        <v>168</v>
       </c>
       <c r="M21" t="s" s="2">
-        <v>239</v>
+        <v>169</v>
       </c>
       <c r="N21" t="s" s="2">
-        <v>240</v>
+        <v>170</v>
       </c>
       <c r="O21" s="2"/>
       <c r="P21" t="s" s="2">
@@ -4562,7 +4574,7 @@
       </c>
       <c r="Q21" s="2"/>
       <c r="R21" t="s" s="2">
-        <v>80</v>
+        <v>181</v>
       </c>
       <c r="S21" t="s" s="2">
         <v>80</v>
@@ -4604,10 +4616,10 @@
         <v>80</v>
       </c>
       <c r="AF21" t="s" s="2">
-        <v>236</v>
+        <v>171</v>
       </c>
       <c r="AG21" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="AH21" t="s" s="2">
         <v>90</v>
@@ -4616,22 +4628,22 @@
         <v>80</v>
       </c>
       <c r="AJ21" t="s" s="2">
-        <v>102</v>
+        <v>80</v>
       </c>
       <c r="AK21" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AL21" t="s" s="2">
-        <v>241</v>
+        <v>133</v>
       </c>
       <c r="AM21" t="s" s="2">
-        <v>242</v>
+        <v>80</v>
       </c>
       <c r="AN21" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AO21" t="s" s="2">
-        <v>243</v>
+        <v>80</v>
       </c>
       <c r="AP21" t="s" s="2">
         <v>80</v>
@@ -4640,12 +4652,12 @@
         <v>80</v>
       </c>
     </row>
-    <row r="22">
+    <row r="22" hidden="true">
       <c r="A22" t="s" s="2">
-        <v>244</v>
+        <v>186</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>244</v>
+        <v>173</v>
       </c>
       <c r="C22" s="2"/>
       <c r="D22" t="s" s="2">
@@ -4659,22 +4671,22 @@
         <v>90</v>
       </c>
       <c r="H22" t="s" s="2">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="I22" t="s" s="2">
         <v>80</v>
       </c>
       <c r="J22" t="s" s="2">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="K22" t="s" s="2">
-        <v>245</v>
+        <v>187</v>
       </c>
       <c r="L22" t="s" s="2">
-        <v>246</v>
+        <v>174</v>
       </c>
       <c r="M22" t="s" s="2">
-        <v>247</v>
+        <v>175</v>
       </c>
       <c r="N22" s="2"/>
       <c r="O22" s="2"/>
@@ -4725,7 +4737,7 @@
         <v>80</v>
       </c>
       <c r="AF22" t="s" s="2">
-        <v>244</v>
+        <v>179</v>
       </c>
       <c r="AG22" t="s" s="2">
         <v>81</v>
@@ -4740,16 +4752,16 @@
         <v>102</v>
       </c>
       <c r="AK22" t="s" s="2">
-        <v>248</v>
+        <v>80</v>
       </c>
       <c r="AL22" t="s" s="2">
-        <v>249</v>
+        <v>133</v>
       </c>
       <c r="AM22" t="s" s="2">
-        <v>250</v>
+        <v>80</v>
       </c>
       <c r="AN22" t="s" s="2">
-        <v>251</v>
+        <v>80</v>
       </c>
       <c r="AO22" t="s" s="2">
         <v>80</v>
@@ -4763,18 +4775,20 @@
     </row>
     <row r="23" hidden="true">
       <c r="A23" t="s" s="2">
-        <v>252</v>
+        <v>188</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>252</v>
-      </c>
-      <c r="C23" s="2"/>
+        <v>156</v>
+      </c>
+      <c r="C23" t="s" s="2">
+        <v>189</v>
+      </c>
       <c r="D23" t="s" s="2">
         <v>80</v>
       </c>
       <c r="E23" s="2"/>
       <c r="F23" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="G23" t="s" s="2">
         <v>90</v>
@@ -4789,13 +4803,13 @@
         <v>80</v>
       </c>
       <c r="K23" t="s" s="2">
-        <v>253</v>
+        <v>135</v>
       </c>
       <c r="L23" t="s" s="2">
-        <v>254</v>
+        <v>136</v>
       </c>
       <c r="M23" t="s" s="2">
-        <v>255</v>
+        <v>137</v>
       </c>
       <c r="N23" s="2"/>
       <c r="O23" s="2"/>
@@ -4846,25 +4860,25 @@
         <v>80</v>
       </c>
       <c r="AF23" t="s" s="2">
-        <v>256</v>
+        <v>159</v>
       </c>
       <c r="AG23" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH23" t="s" s="2">
-        <v>90</v>
+        <v>82</v>
       </c>
       <c r="AI23" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AJ23" t="s" s="2">
-        <v>80</v>
+        <v>141</v>
       </c>
       <c r="AK23" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AL23" t="s" s="2">
-        <v>257</v>
+        <v>80</v>
       </c>
       <c r="AM23" t="s" s="2">
         <v>80</v>
@@ -4884,21 +4898,21 @@
     </row>
     <row r="24" hidden="true">
       <c r="A24" t="s" s="2">
-        <v>258</v>
+        <v>190</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>258</v>
+        <v>163</v>
       </c>
       <c r="C24" s="2"/>
       <c r="D24" t="s" s="2">
-        <v>135</v>
+        <v>80</v>
       </c>
       <c r="E24" s="2"/>
       <c r="F24" t="s" s="2">
         <v>81</v>
       </c>
       <c r="G24" t="s" s="2">
-        <v>82</v>
+        <v>90</v>
       </c>
       <c r="H24" t="s" s="2">
         <v>80</v>
@@ -4910,17 +4924,15 @@
         <v>80</v>
       </c>
       <c r="K24" t="s" s="2">
-        <v>136</v>
+        <v>150</v>
       </c>
       <c r="L24" t="s" s="2">
-        <v>137</v>
+        <v>151</v>
       </c>
       <c r="M24" t="s" s="2">
-        <v>259</v>
-      </c>
-      <c r="N24" t="s" s="2">
-        <v>139</v>
-      </c>
+        <v>152</v>
+      </c>
+      <c r="N24" s="2"/>
       <c r="O24" s="2"/>
       <c r="P24" t="s" s="2">
         <v>80</v>
@@ -4957,37 +4969,37 @@
         <v>80</v>
       </c>
       <c r="AB24" t="s" s="2">
-        <v>260</v>
+        <v>80</v>
       </c>
       <c r="AC24" t="s" s="2">
-        <v>261</v>
+        <v>80</v>
       </c>
       <c r="AD24" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AE24" t="s" s="2">
-        <v>262</v>
+        <v>80</v>
       </c>
       <c r="AF24" t="s" s="2">
-        <v>263</v>
+        <v>153</v>
       </c>
       <c r="AG24" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH24" t="s" s="2">
-        <v>82</v>
+        <v>90</v>
       </c>
       <c r="AI24" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AJ24" t="s" s="2">
-        <v>141</v>
+        <v>80</v>
       </c>
       <c r="AK24" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AL24" t="s" s="2">
-        <v>257</v>
+        <v>154</v>
       </c>
       <c r="AM24" t="s" s="2">
         <v>80</v>
@@ -5007,14 +5019,12 @@
     </row>
     <row r="25" hidden="true">
       <c r="A25" t="s" s="2">
-        <v>264</v>
+        <v>191</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>258</v>
-      </c>
-      <c r="C25" t="s" s="2">
-        <v>265</v>
-      </c>
+        <v>165</v>
+      </c>
+      <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
         <v>80</v>
       </c>
@@ -5023,7 +5033,7 @@
         <v>81</v>
       </c>
       <c r="G25" t="s" s="2">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="H25" t="s" s="2">
         <v>80</v>
@@ -5035,13 +5045,13 @@
         <v>80</v>
       </c>
       <c r="K25" t="s" s="2">
-        <v>266</v>
+        <v>135</v>
       </c>
       <c r="L25" t="s" s="2">
-        <v>267</v>
+        <v>136</v>
       </c>
       <c r="M25" t="s" s="2">
-        <v>268</v>
+        <v>137</v>
       </c>
       <c r="N25" s="2"/>
       <c r="O25" s="2"/>
@@ -5080,19 +5090,19 @@
         <v>80</v>
       </c>
       <c r="AB25" t="s" s="2">
-        <v>80</v>
+        <v>138</v>
       </c>
       <c r="AC25" t="s" s="2">
-        <v>80</v>
+        <v>158</v>
       </c>
       <c r="AD25" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AE25" t="s" s="2">
-        <v>80</v>
+        <v>139</v>
       </c>
       <c r="AF25" t="s" s="2">
-        <v>263</v>
+        <v>159</v>
       </c>
       <c r="AG25" t="s" s="2">
         <v>81</v>
@@ -5130,10 +5140,10 @@
     </row>
     <row r="26" hidden="true">
       <c r="A26" t="s" s="2">
-        <v>269</v>
+        <v>192</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>270</v>
+        <v>167</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
@@ -5141,7 +5151,7 @@
       </c>
       <c r="E26" s="2"/>
       <c r="F26" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="G26" t="s" s="2">
         <v>90</v>
@@ -5156,22 +5166,24 @@
         <v>80</v>
       </c>
       <c r="K26" t="s" s="2">
-        <v>253</v>
+        <v>104</v>
       </c>
       <c r="L26" t="s" s="2">
-        <v>254</v>
+        <v>168</v>
       </c>
       <c r="M26" t="s" s="2">
-        <v>255</v>
-      </c>
-      <c r="N26" s="2"/>
+        <v>169</v>
+      </c>
+      <c r="N26" t="s" s="2">
+        <v>170</v>
+      </c>
       <c r="O26" s="2"/>
       <c r="P26" t="s" s="2">
         <v>80</v>
       </c>
       <c r="Q26" s="2"/>
       <c r="R26" t="s" s="2">
-        <v>80</v>
+        <v>189</v>
       </c>
       <c r="S26" t="s" s="2">
         <v>80</v>
@@ -5213,10 +5225,10 @@
         <v>80</v>
       </c>
       <c r="AF26" t="s" s="2">
-        <v>256</v>
+        <v>171</v>
       </c>
       <c r="AG26" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="AH26" t="s" s="2">
         <v>90</v>
@@ -5231,7 +5243,7 @@
         <v>80</v>
       </c>
       <c r="AL26" t="s" s="2">
-        <v>257</v>
+        <v>133</v>
       </c>
       <c r="AM26" t="s" s="2">
         <v>80</v>
@@ -5251,10 +5263,10 @@
     </row>
     <row r="27" hidden="true">
       <c r="A27" t="s" s="2">
-        <v>271</v>
+        <v>193</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>272</v>
+        <v>173</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
@@ -5262,10 +5274,10 @@
       </c>
       <c r="E27" s="2"/>
       <c r="F27" t="s" s="2">
-        <v>273</v>
+        <v>81</v>
       </c>
       <c r="G27" t="s" s="2">
-        <v>82</v>
+        <v>90</v>
       </c>
       <c r="H27" t="s" s="2">
         <v>80</v>
@@ -5277,13 +5289,13 @@
         <v>80</v>
       </c>
       <c r="K27" t="s" s="2">
-        <v>136</v>
+        <v>194</v>
       </c>
       <c r="L27" t="s" s="2">
-        <v>274</v>
+        <v>174</v>
       </c>
       <c r="M27" t="s" s="2">
-        <v>275</v>
+        <v>175</v>
       </c>
       <c r="N27" s="2"/>
       <c r="O27" s="2"/>
@@ -5322,37 +5334,37 @@
         <v>80</v>
       </c>
       <c r="AB27" t="s" s="2">
-        <v>260</v>
+        <v>80</v>
       </c>
       <c r="AC27" t="s" s="2">
-        <v>261</v>
+        <v>80</v>
       </c>
       <c r="AD27" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AE27" t="s" s="2">
-        <v>262</v>
+        <v>80</v>
       </c>
       <c r="AF27" t="s" s="2">
-        <v>263</v>
+        <v>179</v>
       </c>
       <c r="AG27" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH27" t="s" s="2">
-        <v>82</v>
+        <v>90</v>
       </c>
       <c r="AI27" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AJ27" t="s" s="2">
-        <v>141</v>
+        <v>102</v>
       </c>
       <c r="AK27" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AL27" t="s" s="2">
-        <v>80</v>
+        <v>133</v>
       </c>
       <c r="AM27" t="s" s="2">
         <v>80</v>
@@ -5372,14 +5384,12 @@
     </row>
     <row r="28" hidden="true">
       <c r="A28" t="s" s="2">
-        <v>276</v>
+        <v>195</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>272</v>
-      </c>
-      <c r="C28" t="s" s="2">
-        <v>277</v>
-      </c>
+        <v>196</v>
+      </c>
+      <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
         <v>80</v>
       </c>
@@ -5400,22 +5410,24 @@
         <v>80</v>
       </c>
       <c r="K28" t="s" s="2">
-        <v>136</v>
+        <v>104</v>
       </c>
       <c r="L28" t="s" s="2">
-        <v>274</v>
+        <v>168</v>
       </c>
       <c r="M28" t="s" s="2">
-        <v>275</v>
-      </c>
-      <c r="N28" s="2"/>
+        <v>169</v>
+      </c>
+      <c r="N28" t="s" s="2">
+        <v>170</v>
+      </c>
       <c r="O28" s="2"/>
       <c r="P28" t="s" s="2">
         <v>80</v>
       </c>
       <c r="Q28" s="2"/>
       <c r="R28" t="s" s="2">
-        <v>80</v>
+        <v>197</v>
       </c>
       <c r="S28" t="s" s="2">
         <v>80</v>
@@ -5457,25 +5469,25 @@
         <v>80</v>
       </c>
       <c r="AF28" t="s" s="2">
-        <v>263</v>
+        <v>171</v>
       </c>
       <c r="AG28" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="AH28" t="s" s="2">
-        <v>82</v>
+        <v>90</v>
       </c>
       <c r="AI28" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AJ28" t="s" s="2">
-        <v>141</v>
+        <v>80</v>
       </c>
       <c r="AK28" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AL28" t="s" s="2">
-        <v>80</v>
+        <v>133</v>
       </c>
       <c r="AM28" t="s" s="2">
         <v>80</v>
@@ -5495,10 +5507,10 @@
     </row>
     <row r="29" hidden="true">
       <c r="A29" t="s" s="2">
-        <v>278</v>
+        <v>198</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>279</v>
+        <v>199</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
@@ -5509,7 +5521,7 @@
         <v>81</v>
       </c>
       <c r="G29" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="H29" t="s" s="2">
         <v>80</v>
@@ -5521,13 +5533,13 @@
         <v>80</v>
       </c>
       <c r="K29" t="s" s="2">
-        <v>253</v>
+        <v>200</v>
       </c>
       <c r="L29" t="s" s="2">
-        <v>254</v>
+        <v>174</v>
       </c>
       <c r="M29" t="s" s="2">
-        <v>255</v>
+        <v>175</v>
       </c>
       <c r="N29" s="2"/>
       <c r="O29" s="2"/>
@@ -5578,7 +5590,7 @@
         <v>80</v>
       </c>
       <c r="AF29" t="s" s="2">
-        <v>256</v>
+        <v>179</v>
       </c>
       <c r="AG29" t="s" s="2">
         <v>81</v>
@@ -5590,13 +5602,13 @@
         <v>80</v>
       </c>
       <c r="AJ29" t="s" s="2">
-        <v>80</v>
+        <v>102</v>
       </c>
       <c r="AK29" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AL29" t="s" s="2">
-        <v>257</v>
+        <v>133</v>
       </c>
       <c r="AM29" t="s" s="2">
         <v>80</v>
@@ -5616,12 +5628,14 @@
     </row>
     <row r="30" hidden="true">
       <c r="A30" t="s" s="2">
-        <v>280</v>
+        <v>201</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>281</v>
-      </c>
-      <c r="C30" s="2"/>
+        <v>134</v>
+      </c>
+      <c r="C30" t="s" s="2">
+        <v>202</v>
+      </c>
       <c r="D30" t="s" s="2">
         <v>80</v>
       </c>
@@ -5630,7 +5644,7 @@
         <v>81</v>
       </c>
       <c r="G30" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="H30" t="s" s="2">
         <v>80</v>
@@ -5642,13 +5656,13 @@
         <v>80</v>
       </c>
       <c r="K30" t="s" s="2">
-        <v>136</v>
+        <v>144</v>
       </c>
       <c r="L30" t="s" s="2">
-        <v>274</v>
+        <v>203</v>
       </c>
       <c r="M30" t="s" s="2">
-        <v>275</v>
+        <v>146</v>
       </c>
       <c r="N30" s="2"/>
       <c r="O30" s="2"/>
@@ -5687,19 +5701,19 @@
         <v>80</v>
       </c>
       <c r="AB30" t="s" s="2">
-        <v>260</v>
+        <v>80</v>
       </c>
       <c r="AC30" t="s" s="2">
-        <v>261</v>
+        <v>80</v>
       </c>
       <c r="AD30" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AE30" t="s" s="2">
-        <v>262</v>
+        <v>80</v>
       </c>
       <c r="AF30" t="s" s="2">
-        <v>263</v>
+        <v>140</v>
       </c>
       <c r="AG30" t="s" s="2">
         <v>81</v>
@@ -5708,7 +5722,7 @@
         <v>82</v>
       </c>
       <c r="AI30" t="s" s="2">
-        <v>80</v>
+        <v>147</v>
       </c>
       <c r="AJ30" t="s" s="2">
         <v>141</v>
@@ -5737,10 +5751,10 @@
     </row>
     <row r="31" hidden="true">
       <c r="A31" t="s" s="2">
-        <v>282</v>
+        <v>204</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>283</v>
+        <v>149</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
@@ -5748,7 +5762,7 @@
       </c>
       <c r="E31" s="2"/>
       <c r="F31" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="G31" t="s" s="2">
         <v>90</v>
@@ -5763,24 +5777,22 @@
         <v>80</v>
       </c>
       <c r="K31" t="s" s="2">
-        <v>104</v>
+        <v>150</v>
       </c>
       <c r="L31" t="s" s="2">
-        <v>284</v>
+        <v>151</v>
       </c>
       <c r="M31" t="s" s="2">
-        <v>285</v>
-      </c>
-      <c r="N31" t="s" s="2">
-        <v>286</v>
-      </c>
+        <v>152</v>
+      </c>
+      <c r="N31" s="2"/>
       <c r="O31" s="2"/>
       <c r="P31" t="s" s="2">
         <v>80</v>
       </c>
       <c r="Q31" s="2"/>
       <c r="R31" t="s" s="2">
-        <v>277</v>
+        <v>80</v>
       </c>
       <c r="S31" t="s" s="2">
         <v>80</v>
@@ -5822,10 +5834,10 @@
         <v>80</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>287</v>
+        <v>153</v>
       </c>
       <c r="AG31" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="AH31" t="s" s="2">
         <v>90</v>
@@ -5840,7 +5852,7 @@
         <v>80</v>
       </c>
       <c r="AL31" t="s" s="2">
-        <v>133</v>
+        <v>154</v>
       </c>
       <c r="AM31" t="s" s="2">
         <v>80</v>
@@ -5860,10 +5872,10 @@
     </row>
     <row r="32" hidden="true">
       <c r="A32" t="s" s="2">
-        <v>288</v>
+        <v>205</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>289</v>
+        <v>156</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
@@ -5871,10 +5883,10 @@
       </c>
       <c r="E32" s="2"/>
       <c r="F32" t="s" s="2">
-        <v>81</v>
+        <v>157</v>
       </c>
       <c r="G32" t="s" s="2">
-        <v>90</v>
+        <v>82</v>
       </c>
       <c r="H32" t="s" s="2">
         <v>80</v>
@@ -5886,13 +5898,13 @@
         <v>80</v>
       </c>
       <c r="K32" t="s" s="2">
-        <v>110</v>
+        <v>135</v>
       </c>
       <c r="L32" t="s" s="2">
-        <v>290</v>
+        <v>136</v>
       </c>
       <c r="M32" t="s" s="2">
-        <v>291</v>
+        <v>137</v>
       </c>
       <c r="N32" s="2"/>
       <c r="O32" s="2"/>
@@ -5904,7 +5916,7 @@
         <v>80</v>
       </c>
       <c r="S32" t="s" s="2">
-        <v>292</v>
+        <v>80</v>
       </c>
       <c r="T32" t="s" s="2">
         <v>80</v>
@@ -5919,47 +5931,49 @@
         <v>80</v>
       </c>
       <c r="X32" t="s" s="2">
-        <v>177</v>
-      </c>
-      <c r="Y32" s="2"/>
+        <v>80</v>
+      </c>
+      <c r="Y32" t="s" s="2">
+        <v>80</v>
+      </c>
       <c r="Z32" t="s" s="2">
-        <v>293</v>
+        <v>80</v>
       </c>
       <c r="AA32" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AB32" t="s" s="2">
-        <v>80</v>
+        <v>138</v>
       </c>
       <c r="AC32" t="s" s="2">
-        <v>80</v>
+        <v>158</v>
       </c>
       <c r="AD32" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AE32" t="s" s="2">
-        <v>80</v>
+        <v>139</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>294</v>
+        <v>159</v>
       </c>
       <c r="AG32" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH32" t="s" s="2">
-        <v>90</v>
+        <v>82</v>
       </c>
       <c r="AI32" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AJ32" t="s" s="2">
-        <v>102</v>
+        <v>141</v>
       </c>
       <c r="AK32" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AL32" t="s" s="2">
-        <v>133</v>
+        <v>80</v>
       </c>
       <c r="AM32" t="s" s="2">
         <v>80</v>
@@ -5979,20 +5993,20 @@
     </row>
     <row r="33" hidden="true">
       <c r="A33" t="s" s="2">
-        <v>295</v>
+        <v>206</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>272</v>
+        <v>156</v>
       </c>
       <c r="C33" t="s" s="2">
-        <v>296</v>
+        <v>161</v>
       </c>
       <c r="D33" t="s" s="2">
         <v>80</v>
       </c>
       <c r="E33" s="2"/>
       <c r="F33" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="G33" t="s" s="2">
         <v>90</v>
@@ -6007,13 +6021,13 @@
         <v>80</v>
       </c>
       <c r="K33" t="s" s="2">
+        <v>135</v>
+      </c>
+      <c r="L33" t="s" s="2">
         <v>136</v>
       </c>
-      <c r="L33" t="s" s="2">
-        <v>297</v>
-      </c>
       <c r="M33" t="s" s="2">
-        <v>275</v>
+        <v>137</v>
       </c>
       <c r="N33" s="2"/>
       <c r="O33" s="2"/>
@@ -6064,7 +6078,7 @@
         <v>80</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>263</v>
+        <v>159</v>
       </c>
       <c r="AG33" t="s" s="2">
         <v>81</v>
@@ -6102,10 +6116,10 @@
     </row>
     <row r="34" hidden="true">
       <c r="A34" t="s" s="2">
-        <v>298</v>
+        <v>207</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>279</v>
+        <v>163</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
@@ -6128,13 +6142,13 @@
         <v>80</v>
       </c>
       <c r="K34" t="s" s="2">
-        <v>253</v>
+        <v>150</v>
       </c>
       <c r="L34" t="s" s="2">
-        <v>254</v>
+        <v>151</v>
       </c>
       <c r="M34" t="s" s="2">
-        <v>255</v>
+        <v>152</v>
       </c>
       <c r="N34" s="2"/>
       <c r="O34" s="2"/>
@@ -6185,7 +6199,7 @@
         <v>80</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>256</v>
+        <v>153</v>
       </c>
       <c r="AG34" t="s" s="2">
         <v>81</v>
@@ -6203,7 +6217,7 @@
         <v>80</v>
       </c>
       <c r="AL34" t="s" s="2">
-        <v>257</v>
+        <v>154</v>
       </c>
       <c r="AM34" t="s" s="2">
         <v>80</v>
@@ -6223,10 +6237,10 @@
     </row>
     <row r="35" hidden="true">
       <c r="A35" t="s" s="2">
-        <v>299</v>
+        <v>208</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>281</v>
+        <v>165</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
@@ -6249,13 +6263,13 @@
         <v>80</v>
       </c>
       <c r="K35" t="s" s="2">
+        <v>135</v>
+      </c>
+      <c r="L35" t="s" s="2">
         <v>136</v>
       </c>
-      <c r="L35" t="s" s="2">
-        <v>274</v>
-      </c>
       <c r="M35" t="s" s="2">
-        <v>275</v>
+        <v>137</v>
       </c>
       <c r="N35" s="2"/>
       <c r="O35" s="2"/>
@@ -6294,19 +6308,19 @@
         <v>80</v>
       </c>
       <c r="AB35" t="s" s="2">
-        <v>260</v>
+        <v>138</v>
       </c>
       <c r="AC35" t="s" s="2">
-        <v>261</v>
+        <v>158</v>
       </c>
       <c r="AD35" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AE35" t="s" s="2">
-        <v>262</v>
+        <v>139</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>263</v>
+        <v>159</v>
       </c>
       <c r="AG35" t="s" s="2">
         <v>81</v>
@@ -6344,10 +6358,10 @@
     </row>
     <row r="36" hidden="true">
       <c r="A36" t="s" s="2">
-        <v>300</v>
+        <v>209</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>283</v>
+        <v>167</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
@@ -6373,13 +6387,13 @@
         <v>104</v>
       </c>
       <c r="L36" t="s" s="2">
-        <v>284</v>
+        <v>168</v>
       </c>
       <c r="M36" t="s" s="2">
-        <v>285</v>
+        <v>169</v>
       </c>
       <c r="N36" t="s" s="2">
-        <v>286</v>
+        <v>170</v>
       </c>
       <c r="O36" s="2"/>
       <c r="P36" t="s" s="2">
@@ -6387,7 +6401,7 @@
       </c>
       <c r="Q36" s="2"/>
       <c r="R36" t="s" s="2">
-        <v>296</v>
+        <v>161</v>
       </c>
       <c r="S36" t="s" s="2">
         <v>80</v>
@@ -6429,7 +6443,7 @@
         <v>80</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>287</v>
+        <v>171</v>
       </c>
       <c r="AG36" t="s" s="2">
         <v>90</v>
@@ -6467,10 +6481,10 @@
     </row>
     <row r="37" hidden="true">
       <c r="A37" t="s" s="2">
-        <v>301</v>
+        <v>210</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>289</v>
+        <v>173</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
@@ -6493,13 +6507,13 @@
         <v>80</v>
       </c>
       <c r="K37" t="s" s="2">
-        <v>185</v>
+        <v>110</v>
       </c>
       <c r="L37" t="s" s="2">
-        <v>290</v>
+        <v>174</v>
       </c>
       <c r="M37" t="s" s="2">
-        <v>291</v>
+        <v>175</v>
       </c>
       <c r="N37" s="2"/>
       <c r="O37" s="2"/>
@@ -6511,7 +6525,7 @@
         <v>80</v>
       </c>
       <c r="S37" t="s" s="2">
-        <v>80</v>
+        <v>211</v>
       </c>
       <c r="T37" t="s" s="2">
         <v>80</v>
@@ -6526,13 +6540,11 @@
         <v>80</v>
       </c>
       <c r="X37" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="Y37" t="s" s="2">
-        <v>80</v>
-      </c>
+        <v>177</v>
+      </c>
+      <c r="Y37" s="2"/>
       <c r="Z37" t="s" s="2">
-        <v>80</v>
+        <v>178</v>
       </c>
       <c r="AA37" t="s" s="2">
         <v>80</v>
@@ -6550,7 +6562,7 @@
         <v>80</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>294</v>
+        <v>179</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>81</v>
@@ -6588,20 +6600,20 @@
     </row>
     <row r="38" hidden="true">
       <c r="A38" t="s" s="2">
-        <v>302</v>
+        <v>212</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>272</v>
+        <v>156</v>
       </c>
       <c r="C38" t="s" s="2">
-        <v>303</v>
+        <v>181</v>
       </c>
       <c r="D38" t="s" s="2">
         <v>80</v>
       </c>
       <c r="E38" s="2"/>
       <c r="F38" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="G38" t="s" s="2">
         <v>90</v>
@@ -6616,13 +6628,13 @@
         <v>80</v>
       </c>
       <c r="K38" t="s" s="2">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="L38" t="s" s="2">
-        <v>304</v>
+        <v>182</v>
       </c>
       <c r="M38" t="s" s="2">
-        <v>275</v>
+        <v>137</v>
       </c>
       <c r="N38" s="2"/>
       <c r="O38" s="2"/>
@@ -6673,7 +6685,7 @@
         <v>80</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>263</v>
+        <v>159</v>
       </c>
       <c r="AG38" t="s" s="2">
         <v>81</v>
@@ -6711,10 +6723,10 @@
     </row>
     <row r="39" hidden="true">
       <c r="A39" t="s" s="2">
-        <v>305</v>
+        <v>213</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>279</v>
+        <v>163</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
@@ -6737,13 +6749,13 @@
         <v>80</v>
       </c>
       <c r="K39" t="s" s="2">
-        <v>253</v>
+        <v>150</v>
       </c>
       <c r="L39" t="s" s="2">
-        <v>254</v>
+        <v>151</v>
       </c>
       <c r="M39" t="s" s="2">
-        <v>255</v>
+        <v>152</v>
       </c>
       <c r="N39" s="2"/>
       <c r="O39" s="2"/>
@@ -6794,7 +6806,7 @@
         <v>80</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>256</v>
+        <v>153</v>
       </c>
       <c r="AG39" t="s" s="2">
         <v>81</v>
@@ -6812,7 +6824,7 @@
         <v>80</v>
       </c>
       <c r="AL39" t="s" s="2">
-        <v>257</v>
+        <v>154</v>
       </c>
       <c r="AM39" t="s" s="2">
         <v>80</v>
@@ -6832,10 +6844,10 @@
     </row>
     <row r="40" hidden="true">
       <c r="A40" t="s" s="2">
-        <v>306</v>
+        <v>214</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>281</v>
+        <v>165</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
@@ -6858,13 +6870,13 @@
         <v>80</v>
       </c>
       <c r="K40" t="s" s="2">
+        <v>135</v>
+      </c>
+      <c r="L40" t="s" s="2">
         <v>136</v>
       </c>
-      <c r="L40" t="s" s="2">
-        <v>274</v>
-      </c>
       <c r="M40" t="s" s="2">
-        <v>275</v>
+        <v>137</v>
       </c>
       <c r="N40" s="2"/>
       <c r="O40" s="2"/>
@@ -6903,19 +6915,19 @@
         <v>80</v>
       </c>
       <c r="AB40" t="s" s="2">
-        <v>260</v>
+        <v>138</v>
       </c>
       <c r="AC40" t="s" s="2">
-        <v>261</v>
+        <v>158</v>
       </c>
       <c r="AD40" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AE40" t="s" s="2">
-        <v>262</v>
+        <v>139</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>263</v>
+        <v>159</v>
       </c>
       <c r="AG40" t="s" s="2">
         <v>81</v>
@@ -6953,10 +6965,10 @@
     </row>
     <row r="41" hidden="true">
       <c r="A41" t="s" s="2">
-        <v>307</v>
+        <v>215</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>283</v>
+        <v>167</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
@@ -6982,13 +6994,13 @@
         <v>104</v>
       </c>
       <c r="L41" t="s" s="2">
-        <v>284</v>
+        <v>168</v>
       </c>
       <c r="M41" t="s" s="2">
-        <v>285</v>
+        <v>169</v>
       </c>
       <c r="N41" t="s" s="2">
-        <v>286</v>
+        <v>170</v>
       </c>
       <c r="O41" s="2"/>
       <c r="P41" t="s" s="2">
@@ -6996,7 +7008,7 @@
       </c>
       <c r="Q41" s="2"/>
       <c r="R41" t="s" s="2">
-        <v>303</v>
+        <v>181</v>
       </c>
       <c r="S41" t="s" s="2">
         <v>80</v>
@@ -7038,7 +7050,7 @@
         <v>80</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>287</v>
+        <v>171</v>
       </c>
       <c r="AG41" t="s" s="2">
         <v>90</v>
@@ -7076,10 +7088,10 @@
     </row>
     <row r="42" hidden="true">
       <c r="A42" t="s" s="2">
-        <v>308</v>
+        <v>216</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>289</v>
+        <v>173</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
@@ -7102,13 +7114,13 @@
         <v>80</v>
       </c>
       <c r="K42" t="s" s="2">
-        <v>309</v>
+        <v>187</v>
       </c>
       <c r="L42" t="s" s="2">
-        <v>290</v>
+        <v>174</v>
       </c>
       <c r="M42" t="s" s="2">
-        <v>291</v>
+        <v>175</v>
       </c>
       <c r="N42" s="2"/>
       <c r="O42" s="2"/>
@@ -7159,7 +7171,7 @@
         <v>80</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>294</v>
+        <v>179</v>
       </c>
       <c r="AG42" t="s" s="2">
         <v>81</v>
@@ -7197,12 +7209,14 @@
     </row>
     <row r="43" hidden="true">
       <c r="A43" t="s" s="2">
-        <v>310</v>
+        <v>217</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>311</v>
-      </c>
-      <c r="C43" s="2"/>
+        <v>156</v>
+      </c>
+      <c r="C43" t="s" s="2">
+        <v>189</v>
+      </c>
       <c r="D43" t="s" s="2">
         <v>80</v>
       </c>
@@ -7223,24 +7237,22 @@
         <v>80</v>
       </c>
       <c r="K43" t="s" s="2">
-        <v>104</v>
+        <v>135</v>
       </c>
       <c r="L43" t="s" s="2">
-        <v>284</v>
+        <v>136</v>
       </c>
       <c r="M43" t="s" s="2">
-        <v>285</v>
-      </c>
-      <c r="N43" t="s" s="2">
-        <v>286</v>
-      </c>
+        <v>137</v>
+      </c>
+      <c r="N43" s="2"/>
       <c r="O43" s="2"/>
       <c r="P43" t="s" s="2">
         <v>80</v>
       </c>
       <c r="Q43" s="2"/>
       <c r="R43" t="s" s="2">
-        <v>312</v>
+        <v>80</v>
       </c>
       <c r="S43" t="s" s="2">
         <v>80</v>
@@ -7282,25 +7294,25 @@
         <v>80</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>287</v>
+        <v>159</v>
       </c>
       <c r="AG43" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="AH43" t="s" s="2">
-        <v>90</v>
+        <v>82</v>
       </c>
       <c r="AI43" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AJ43" t="s" s="2">
-        <v>80</v>
+        <v>141</v>
       </c>
       <c r="AK43" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AL43" t="s" s="2">
-        <v>133</v>
+        <v>80</v>
       </c>
       <c r="AM43" t="s" s="2">
         <v>80</v>
@@ -7320,10 +7332,10 @@
     </row>
     <row r="44" hidden="true">
       <c r="A44" t="s" s="2">
-        <v>313</v>
+        <v>218</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>314</v>
+        <v>163</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
@@ -7334,7 +7346,7 @@
         <v>81</v>
       </c>
       <c r="G44" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="H44" t="s" s="2">
         <v>80</v>
@@ -7346,13 +7358,13 @@
         <v>80</v>
       </c>
       <c r="K44" t="s" s="2">
-        <v>315</v>
+        <v>150</v>
       </c>
       <c r="L44" t="s" s="2">
-        <v>290</v>
+        <v>151</v>
       </c>
       <c r="M44" t="s" s="2">
-        <v>291</v>
+        <v>152</v>
       </c>
       <c r="N44" s="2"/>
       <c r="O44" s="2"/>
@@ -7403,7 +7415,7 @@
         <v>80</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>294</v>
+        <v>153</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>81</v>
@@ -7415,13 +7427,13 @@
         <v>80</v>
       </c>
       <c r="AJ44" t="s" s="2">
-        <v>102</v>
+        <v>80</v>
       </c>
       <c r="AK44" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AL44" t="s" s="2">
-        <v>133</v>
+        <v>154</v>
       </c>
       <c r="AM44" t="s" s="2">
         <v>80</v>
@@ -7441,14 +7453,12 @@
     </row>
     <row r="45" hidden="true">
       <c r="A45" t="s" s="2">
-        <v>316</v>
+        <v>219</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>258</v>
-      </c>
-      <c r="C45" t="s" s="2">
-        <v>317</v>
-      </c>
+        <v>165</v>
+      </c>
+      <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
         <v>80</v>
       </c>
@@ -7457,7 +7467,7 @@
         <v>81</v>
       </c>
       <c r="G45" t="s" s="2">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="H45" t="s" s="2">
         <v>80</v>
@@ -7469,13 +7479,13 @@
         <v>80</v>
       </c>
       <c r="K45" t="s" s="2">
-        <v>266</v>
+        <v>135</v>
       </c>
       <c r="L45" t="s" s="2">
-        <v>318</v>
+        <v>136</v>
       </c>
       <c r="M45" t="s" s="2">
-        <v>268</v>
+        <v>137</v>
       </c>
       <c r="N45" s="2"/>
       <c r="O45" s="2"/>
@@ -7514,19 +7524,19 @@
         <v>80</v>
       </c>
       <c r="AB45" t="s" s="2">
-        <v>80</v>
+        <v>138</v>
       </c>
       <c r="AC45" t="s" s="2">
-        <v>80</v>
+        <v>158</v>
       </c>
       <c r="AD45" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AE45" t="s" s="2">
-        <v>80</v>
+        <v>139</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>263</v>
+        <v>159</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>81</v>
@@ -7564,10 +7574,10 @@
     </row>
     <row r="46" hidden="true">
       <c r="A46" t="s" s="2">
-        <v>319</v>
+        <v>220</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>270</v>
+        <v>167</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
@@ -7575,7 +7585,7 @@
       </c>
       <c r="E46" s="2"/>
       <c r="F46" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="G46" t="s" s="2">
         <v>90</v>
@@ -7590,22 +7600,24 @@
         <v>80</v>
       </c>
       <c r="K46" t="s" s="2">
-        <v>253</v>
+        <v>104</v>
       </c>
       <c r="L46" t="s" s="2">
-        <v>254</v>
+        <v>168</v>
       </c>
       <c r="M46" t="s" s="2">
-        <v>255</v>
-      </c>
-      <c r="N46" s="2"/>
+        <v>169</v>
+      </c>
+      <c r="N46" t="s" s="2">
+        <v>170</v>
+      </c>
       <c r="O46" s="2"/>
       <c r="P46" t="s" s="2">
         <v>80</v>
       </c>
       <c r="Q46" s="2"/>
       <c r="R46" t="s" s="2">
-        <v>80</v>
+        <v>189</v>
       </c>
       <c r="S46" t="s" s="2">
         <v>80</v>
@@ -7647,10 +7659,10 @@
         <v>80</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>256</v>
+        <v>171</v>
       </c>
       <c r="AG46" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="AH46" t="s" s="2">
         <v>90</v>
@@ -7665,7 +7677,7 @@
         <v>80</v>
       </c>
       <c r="AL46" t="s" s="2">
-        <v>257</v>
+        <v>133</v>
       </c>
       <c r="AM46" t="s" s="2">
         <v>80</v>
@@ -7685,10 +7697,10 @@
     </row>
     <row r="47" hidden="true">
       <c r="A47" t="s" s="2">
-        <v>320</v>
+        <v>221</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>272</v>
+        <v>173</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
@@ -7696,10 +7708,10 @@
       </c>
       <c r="E47" s="2"/>
       <c r="F47" t="s" s="2">
-        <v>273</v>
+        <v>81</v>
       </c>
       <c r="G47" t="s" s="2">
-        <v>82</v>
+        <v>90</v>
       </c>
       <c r="H47" t="s" s="2">
         <v>80</v>
@@ -7711,13 +7723,13 @@
         <v>80</v>
       </c>
       <c r="K47" t="s" s="2">
-        <v>136</v>
+        <v>222</v>
       </c>
       <c r="L47" t="s" s="2">
-        <v>274</v>
+        <v>174</v>
       </c>
       <c r="M47" t="s" s="2">
-        <v>275</v>
+        <v>175</v>
       </c>
       <c r="N47" s="2"/>
       <c r="O47" s="2"/>
@@ -7756,37 +7768,37 @@
         <v>80</v>
       </c>
       <c r="AB47" t="s" s="2">
-        <v>260</v>
+        <v>80</v>
       </c>
       <c r="AC47" t="s" s="2">
-        <v>261</v>
+        <v>80</v>
       </c>
       <c r="AD47" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AE47" t="s" s="2">
-        <v>262</v>
+        <v>80</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>263</v>
+        <v>179</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH47" t="s" s="2">
-        <v>82</v>
+        <v>90</v>
       </c>
       <c r="AI47" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AJ47" t="s" s="2">
-        <v>141</v>
+        <v>102</v>
       </c>
       <c r="AK47" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AL47" t="s" s="2">
-        <v>80</v>
+        <v>133</v>
       </c>
       <c r="AM47" t="s" s="2">
         <v>80</v>
@@ -7806,14 +7818,12 @@
     </row>
     <row r="48" hidden="true">
       <c r="A48" t="s" s="2">
-        <v>321</v>
+        <v>223</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>272</v>
-      </c>
-      <c r="C48" t="s" s="2">
-        <v>277</v>
-      </c>
+        <v>196</v>
+      </c>
+      <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
         <v>80</v>
       </c>
@@ -7834,22 +7844,24 @@
         <v>80</v>
       </c>
       <c r="K48" t="s" s="2">
-        <v>136</v>
+        <v>104</v>
       </c>
       <c r="L48" t="s" s="2">
-        <v>274</v>
+        <v>168</v>
       </c>
       <c r="M48" t="s" s="2">
-        <v>275</v>
-      </c>
-      <c r="N48" s="2"/>
+        <v>169</v>
+      </c>
+      <c r="N48" t="s" s="2">
+        <v>170</v>
+      </c>
       <c r="O48" s="2"/>
       <c r="P48" t="s" s="2">
         <v>80</v>
       </c>
       <c r="Q48" s="2"/>
       <c r="R48" t="s" s="2">
-        <v>80</v>
+        <v>197</v>
       </c>
       <c r="S48" t="s" s="2">
         <v>80</v>
@@ -7891,25 +7903,25 @@
         <v>80</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>263</v>
+        <v>171</v>
       </c>
       <c r="AG48" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="AH48" t="s" s="2">
-        <v>82</v>
+        <v>90</v>
       </c>
       <c r="AI48" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AJ48" t="s" s="2">
-        <v>141</v>
+        <v>80</v>
       </c>
       <c r="AK48" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AL48" t="s" s="2">
-        <v>80</v>
+        <v>133</v>
       </c>
       <c r="AM48" t="s" s="2">
         <v>80</v>
@@ -7929,10 +7941,10 @@
     </row>
     <row r="49" hidden="true">
       <c r="A49" t="s" s="2">
-        <v>322</v>
+        <v>224</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>279</v>
+        <v>199</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
@@ -7943,7 +7955,7 @@
         <v>81</v>
       </c>
       <c r="G49" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="H49" t="s" s="2">
         <v>80</v>
@@ -7955,13 +7967,13 @@
         <v>80</v>
       </c>
       <c r="K49" t="s" s="2">
-        <v>253</v>
+        <v>200</v>
       </c>
       <c r="L49" t="s" s="2">
-        <v>254</v>
+        <v>174</v>
       </c>
       <c r="M49" t="s" s="2">
-        <v>255</v>
+        <v>175</v>
       </c>
       <c r="N49" s="2"/>
       <c r="O49" s="2"/>
@@ -8012,7 +8024,7 @@
         <v>80</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>256</v>
+        <v>179</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>81</v>
@@ -8024,13 +8036,13 @@
         <v>80</v>
       </c>
       <c r="AJ49" t="s" s="2">
-        <v>80</v>
+        <v>102</v>
       </c>
       <c r="AK49" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AL49" t="s" s="2">
-        <v>257</v>
+        <v>133</v>
       </c>
       <c r="AM49" t="s" s="2">
         <v>80</v>
@@ -8050,12 +8062,14 @@
     </row>
     <row r="50" hidden="true">
       <c r="A50" t="s" s="2">
-        <v>323</v>
+        <v>225</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>281</v>
-      </c>
-      <c r="C50" s="2"/>
+        <v>134</v>
+      </c>
+      <c r="C50" t="s" s="2">
+        <v>226</v>
+      </c>
       <c r="D50" t="s" s="2">
         <v>80</v>
       </c>
@@ -8064,7 +8078,7 @@
         <v>81</v>
       </c>
       <c r="G50" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="H50" t="s" s="2">
         <v>80</v>
@@ -8076,13 +8090,13 @@
         <v>80</v>
       </c>
       <c r="K50" t="s" s="2">
-        <v>136</v>
+        <v>144</v>
       </c>
       <c r="L50" t="s" s="2">
-        <v>274</v>
+        <v>227</v>
       </c>
       <c r="M50" t="s" s="2">
-        <v>275</v>
+        <v>146</v>
       </c>
       <c r="N50" s="2"/>
       <c r="O50" s="2"/>
@@ -8121,19 +8135,19 @@
         <v>80</v>
       </c>
       <c r="AB50" t="s" s="2">
-        <v>260</v>
+        <v>80</v>
       </c>
       <c r="AC50" t="s" s="2">
-        <v>261</v>
+        <v>80</v>
       </c>
       <c r="AD50" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AE50" t="s" s="2">
-        <v>262</v>
+        <v>80</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>263</v>
+        <v>140</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>81</v>
@@ -8142,7 +8156,7 @@
         <v>82</v>
       </c>
       <c r="AI50" t="s" s="2">
-        <v>80</v>
+        <v>147</v>
       </c>
       <c r="AJ50" t="s" s="2">
         <v>141</v>
@@ -8171,10 +8185,10 @@
     </row>
     <row r="51" hidden="true">
       <c r="A51" t="s" s="2">
-        <v>324</v>
+        <v>228</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>283</v>
+        <v>149</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
@@ -8182,7 +8196,7 @@
       </c>
       <c r="E51" s="2"/>
       <c r="F51" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="G51" t="s" s="2">
         <v>90</v>
@@ -8197,24 +8211,22 @@
         <v>80</v>
       </c>
       <c r="K51" t="s" s="2">
-        <v>104</v>
+        <v>150</v>
       </c>
       <c r="L51" t="s" s="2">
-        <v>284</v>
+        <v>151</v>
       </c>
       <c r="M51" t="s" s="2">
-        <v>285</v>
-      </c>
-      <c r="N51" t="s" s="2">
-        <v>286</v>
-      </c>
+        <v>152</v>
+      </c>
+      <c r="N51" s="2"/>
       <c r="O51" s="2"/>
       <c r="P51" t="s" s="2">
         <v>80</v>
       </c>
       <c r="Q51" s="2"/>
       <c r="R51" t="s" s="2">
-        <v>277</v>
+        <v>80</v>
       </c>
       <c r="S51" t="s" s="2">
         <v>80</v>
@@ -8256,10 +8268,10 @@
         <v>80</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>287</v>
+        <v>153</v>
       </c>
       <c r="AG51" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="AH51" t="s" s="2">
         <v>90</v>
@@ -8274,7 +8286,7 @@
         <v>80</v>
       </c>
       <c r="AL51" t="s" s="2">
-        <v>133</v>
+        <v>154</v>
       </c>
       <c r="AM51" t="s" s="2">
         <v>80</v>
@@ -8294,10 +8306,10 @@
     </row>
     <row r="52" hidden="true">
       <c r="A52" t="s" s="2">
-        <v>325</v>
+        <v>229</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>289</v>
+        <v>156</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
@@ -8305,10 +8317,10 @@
       </c>
       <c r="E52" s="2"/>
       <c r="F52" t="s" s="2">
-        <v>81</v>
+        <v>157</v>
       </c>
       <c r="G52" t="s" s="2">
-        <v>90</v>
+        <v>82</v>
       </c>
       <c r="H52" t="s" s="2">
         <v>80</v>
@@ -8320,13 +8332,13 @@
         <v>80</v>
       </c>
       <c r="K52" t="s" s="2">
-        <v>110</v>
+        <v>135</v>
       </c>
       <c r="L52" t="s" s="2">
-        <v>290</v>
+        <v>136</v>
       </c>
       <c r="M52" t="s" s="2">
-        <v>291</v>
+        <v>137</v>
       </c>
       <c r="N52" s="2"/>
       <c r="O52" s="2"/>
@@ -8338,7 +8350,7 @@
         <v>80</v>
       </c>
       <c r="S52" t="s" s="2">
-        <v>326</v>
+        <v>80</v>
       </c>
       <c r="T52" t="s" s="2">
         <v>80</v>
@@ -8353,47 +8365,49 @@
         <v>80</v>
       </c>
       <c r="X52" t="s" s="2">
-        <v>177</v>
-      </c>
-      <c r="Y52" s="2"/>
+        <v>80</v>
+      </c>
+      <c r="Y52" t="s" s="2">
+        <v>80</v>
+      </c>
       <c r="Z52" t="s" s="2">
-        <v>293</v>
+        <v>80</v>
       </c>
       <c r="AA52" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AB52" t="s" s="2">
-        <v>80</v>
+        <v>138</v>
       </c>
       <c r="AC52" t="s" s="2">
-        <v>80</v>
+        <v>158</v>
       </c>
       <c r="AD52" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AE52" t="s" s="2">
-        <v>80</v>
+        <v>139</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>294</v>
+        <v>159</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH52" t="s" s="2">
-        <v>90</v>
+        <v>82</v>
       </c>
       <c r="AI52" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AJ52" t="s" s="2">
-        <v>102</v>
+        <v>141</v>
       </c>
       <c r="AK52" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AL52" t="s" s="2">
-        <v>133</v>
+        <v>80</v>
       </c>
       <c r="AM52" t="s" s="2">
         <v>80</v>
@@ -8413,20 +8427,20 @@
     </row>
     <row r="53" hidden="true">
       <c r="A53" t="s" s="2">
-        <v>327</v>
+        <v>230</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>272</v>
+        <v>156</v>
       </c>
       <c r="C53" t="s" s="2">
-        <v>296</v>
+        <v>161</v>
       </c>
       <c r="D53" t="s" s="2">
         <v>80</v>
       </c>
       <c r="E53" s="2"/>
       <c r="F53" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="G53" t="s" s="2">
         <v>90</v>
@@ -8441,13 +8455,13 @@
         <v>80</v>
       </c>
       <c r="K53" t="s" s="2">
+        <v>135</v>
+      </c>
+      <c r="L53" t="s" s="2">
         <v>136</v>
       </c>
-      <c r="L53" t="s" s="2">
-        <v>297</v>
-      </c>
       <c r="M53" t="s" s="2">
-        <v>275</v>
+        <v>137</v>
       </c>
       <c r="N53" s="2"/>
       <c r="O53" s="2"/>
@@ -8498,7 +8512,7 @@
         <v>80</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>263</v>
+        <v>159</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>81</v>
@@ -8536,10 +8550,10 @@
     </row>
     <row r="54" hidden="true">
       <c r="A54" t="s" s="2">
-        <v>328</v>
+        <v>231</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>279</v>
+        <v>163</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
@@ -8562,13 +8576,13 @@
         <v>80</v>
       </c>
       <c r="K54" t="s" s="2">
-        <v>253</v>
+        <v>150</v>
       </c>
       <c r="L54" t="s" s="2">
-        <v>254</v>
+        <v>151</v>
       </c>
       <c r="M54" t="s" s="2">
-        <v>255</v>
+        <v>152</v>
       </c>
       <c r="N54" s="2"/>
       <c r="O54" s="2"/>
@@ -8619,7 +8633,7 @@
         <v>80</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>256</v>
+        <v>153</v>
       </c>
       <c r="AG54" t="s" s="2">
         <v>81</v>
@@ -8637,7 +8651,7 @@
         <v>80</v>
       </c>
       <c r="AL54" t="s" s="2">
-        <v>257</v>
+        <v>154</v>
       </c>
       <c r="AM54" t="s" s="2">
         <v>80</v>
@@ -8657,10 +8671,10 @@
     </row>
     <row r="55" hidden="true">
       <c r="A55" t="s" s="2">
-        <v>329</v>
+        <v>232</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>281</v>
+        <v>165</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
@@ -8683,13 +8697,13 @@
         <v>80</v>
       </c>
       <c r="K55" t="s" s="2">
+        <v>135</v>
+      </c>
+      <c r="L55" t="s" s="2">
         <v>136</v>
       </c>
-      <c r="L55" t="s" s="2">
-        <v>274</v>
-      </c>
       <c r="M55" t="s" s="2">
-        <v>275</v>
+        <v>137</v>
       </c>
       <c r="N55" s="2"/>
       <c r="O55" s="2"/>
@@ -8728,19 +8742,19 @@
         <v>80</v>
       </c>
       <c r="AB55" t="s" s="2">
-        <v>260</v>
+        <v>138</v>
       </c>
       <c r="AC55" t="s" s="2">
-        <v>261</v>
+        <v>158</v>
       </c>
       <c r="AD55" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AE55" t="s" s="2">
-        <v>262</v>
+        <v>139</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>263</v>
+        <v>159</v>
       </c>
       <c r="AG55" t="s" s="2">
         <v>81</v>
@@ -8778,10 +8792,10 @@
     </row>
     <row r="56" hidden="true">
       <c r="A56" t="s" s="2">
-        <v>330</v>
+        <v>233</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>283</v>
+        <v>167</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
@@ -8807,13 +8821,13 @@
         <v>104</v>
       </c>
       <c r="L56" t="s" s="2">
-        <v>284</v>
+        <v>168</v>
       </c>
       <c r="M56" t="s" s="2">
-        <v>285</v>
+        <v>169</v>
       </c>
       <c r="N56" t="s" s="2">
-        <v>286</v>
+        <v>170</v>
       </c>
       <c r="O56" s="2"/>
       <c r="P56" t="s" s="2">
@@ -8821,7 +8835,7 @@
       </c>
       <c r="Q56" s="2"/>
       <c r="R56" t="s" s="2">
-        <v>296</v>
+        <v>161</v>
       </c>
       <c r="S56" t="s" s="2">
         <v>80</v>
@@ -8863,7 +8877,7 @@
         <v>80</v>
       </c>
       <c r="AF56" t="s" s="2">
-        <v>287</v>
+        <v>171</v>
       </c>
       <c r="AG56" t="s" s="2">
         <v>90</v>
@@ -8901,10 +8915,10 @@
     </row>
     <row r="57" hidden="true">
       <c r="A57" t="s" s="2">
-        <v>331</v>
+        <v>234</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>289</v>
+        <v>173</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
@@ -8927,13 +8941,13 @@
         <v>80</v>
       </c>
       <c r="K57" t="s" s="2">
-        <v>185</v>
+        <v>110</v>
       </c>
       <c r="L57" t="s" s="2">
-        <v>290</v>
+        <v>174</v>
       </c>
       <c r="M57" t="s" s="2">
-        <v>291</v>
+        <v>175</v>
       </c>
       <c r="N57" s="2"/>
       <c r="O57" s="2"/>
@@ -8945,7 +8959,7 @@
         <v>80</v>
       </c>
       <c r="S57" t="s" s="2">
-        <v>80</v>
+        <v>235</v>
       </c>
       <c r="T57" t="s" s="2">
         <v>80</v>
@@ -8960,13 +8974,11 @@
         <v>80</v>
       </c>
       <c r="X57" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="Y57" t="s" s="2">
-        <v>80</v>
-      </c>
+        <v>177</v>
+      </c>
+      <c r="Y57" s="2"/>
       <c r="Z57" t="s" s="2">
-        <v>80</v>
+        <v>178</v>
       </c>
       <c r="AA57" t="s" s="2">
         <v>80</v>
@@ -8984,7 +8996,7 @@
         <v>80</v>
       </c>
       <c r="AF57" t="s" s="2">
-        <v>294</v>
+        <v>179</v>
       </c>
       <c r="AG57" t="s" s="2">
         <v>81</v>
@@ -9022,20 +9034,20 @@
     </row>
     <row r="58" hidden="true">
       <c r="A58" t="s" s="2">
-        <v>332</v>
+        <v>236</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>272</v>
+        <v>156</v>
       </c>
       <c r="C58" t="s" s="2">
-        <v>303</v>
+        <v>181</v>
       </c>
       <c r="D58" t="s" s="2">
         <v>80</v>
       </c>
       <c r="E58" s="2"/>
       <c r="F58" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="G58" t="s" s="2">
         <v>90</v>
@@ -9050,13 +9062,13 @@
         <v>80</v>
       </c>
       <c r="K58" t="s" s="2">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="L58" t="s" s="2">
-        <v>274</v>
+        <v>182</v>
       </c>
       <c r="M58" t="s" s="2">
-        <v>275</v>
+        <v>137</v>
       </c>
       <c r="N58" s="2"/>
       <c r="O58" s="2"/>
@@ -9107,7 +9119,7 @@
         <v>80</v>
       </c>
       <c r="AF58" t="s" s="2">
-        <v>263</v>
+        <v>159</v>
       </c>
       <c r="AG58" t="s" s="2">
         <v>81</v>
@@ -9145,10 +9157,10 @@
     </row>
     <row r="59" hidden="true">
       <c r="A59" t="s" s="2">
-        <v>333</v>
+        <v>237</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>279</v>
+        <v>163</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
@@ -9171,13 +9183,13 @@
         <v>80</v>
       </c>
       <c r="K59" t="s" s="2">
-        <v>253</v>
+        <v>150</v>
       </c>
       <c r="L59" t="s" s="2">
-        <v>254</v>
+        <v>151</v>
       </c>
       <c r="M59" t="s" s="2">
-        <v>255</v>
+        <v>152</v>
       </c>
       <c r="N59" s="2"/>
       <c r="O59" s="2"/>
@@ -9228,7 +9240,7 @@
         <v>80</v>
       </c>
       <c r="AF59" t="s" s="2">
-        <v>256</v>
+        <v>153</v>
       </c>
       <c r="AG59" t="s" s="2">
         <v>81</v>
@@ -9246,7 +9258,7 @@
         <v>80</v>
       </c>
       <c r="AL59" t="s" s="2">
-        <v>257</v>
+        <v>154</v>
       </c>
       <c r="AM59" t="s" s="2">
         <v>80</v>
@@ -9266,10 +9278,10 @@
     </row>
     <row r="60" hidden="true">
       <c r="A60" t="s" s="2">
-        <v>334</v>
+        <v>238</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>281</v>
+        <v>165</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
@@ -9292,13 +9304,13 @@
         <v>80</v>
       </c>
       <c r="K60" t="s" s="2">
+        <v>135</v>
+      </c>
+      <c r="L60" t="s" s="2">
         <v>136</v>
       </c>
-      <c r="L60" t="s" s="2">
-        <v>274</v>
-      </c>
       <c r="M60" t="s" s="2">
-        <v>275</v>
+        <v>137</v>
       </c>
       <c r="N60" s="2"/>
       <c r="O60" s="2"/>
@@ -9337,19 +9349,19 @@
         <v>80</v>
       </c>
       <c r="AB60" t="s" s="2">
-        <v>260</v>
+        <v>138</v>
       </c>
       <c r="AC60" t="s" s="2">
-        <v>261</v>
+        <v>158</v>
       </c>
       <c r="AD60" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AE60" t="s" s="2">
-        <v>262</v>
+        <v>139</v>
       </c>
       <c r="AF60" t="s" s="2">
-        <v>263</v>
+        <v>159</v>
       </c>
       <c r="AG60" t="s" s="2">
         <v>81</v>
@@ -9387,10 +9399,10 @@
     </row>
     <row r="61" hidden="true">
       <c r="A61" t="s" s="2">
-        <v>335</v>
+        <v>239</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>283</v>
+        <v>167</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
@@ -9416,13 +9428,13 @@
         <v>104</v>
       </c>
       <c r="L61" t="s" s="2">
-        <v>284</v>
+        <v>168</v>
       </c>
       <c r="M61" t="s" s="2">
-        <v>285</v>
+        <v>169</v>
       </c>
       <c r="N61" t="s" s="2">
-        <v>286</v>
+        <v>170</v>
       </c>
       <c r="O61" s="2"/>
       <c r="P61" t="s" s="2">
@@ -9430,7 +9442,7 @@
       </c>
       <c r="Q61" s="2"/>
       <c r="R61" t="s" s="2">
-        <v>303</v>
+        <v>181</v>
       </c>
       <c r="S61" t="s" s="2">
         <v>80</v>
@@ -9472,7 +9484,7 @@
         <v>80</v>
       </c>
       <c r="AF61" t="s" s="2">
-        <v>287</v>
+        <v>171</v>
       </c>
       <c r="AG61" t="s" s="2">
         <v>90</v>
@@ -9510,10 +9522,10 @@
     </row>
     <row r="62" hidden="true">
       <c r="A62" t="s" s="2">
-        <v>336</v>
+        <v>240</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>289</v>
+        <v>173</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
@@ -9536,13 +9548,13 @@
         <v>80</v>
       </c>
       <c r="K62" t="s" s="2">
-        <v>337</v>
+        <v>187</v>
       </c>
       <c r="L62" t="s" s="2">
-        <v>290</v>
+        <v>174</v>
       </c>
       <c r="M62" t="s" s="2">
-        <v>291</v>
+        <v>175</v>
       </c>
       <c r="N62" s="2"/>
       <c r="O62" s="2"/>
@@ -9593,7 +9605,7 @@
         <v>80</v>
       </c>
       <c r="AF62" t="s" s="2">
-        <v>294</v>
+        <v>179</v>
       </c>
       <c r="AG62" t="s" s="2">
         <v>81</v>
@@ -9631,12 +9643,14 @@
     </row>
     <row r="63" hidden="true">
       <c r="A63" t="s" s="2">
-        <v>338</v>
+        <v>241</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>311</v>
-      </c>
-      <c r="C63" s="2"/>
+        <v>156</v>
+      </c>
+      <c r="C63" t="s" s="2">
+        <v>189</v>
+      </c>
       <c r="D63" t="s" s="2">
         <v>80</v>
       </c>
@@ -9657,24 +9671,22 @@
         <v>80</v>
       </c>
       <c r="K63" t="s" s="2">
-        <v>104</v>
+        <v>135</v>
       </c>
       <c r="L63" t="s" s="2">
-        <v>284</v>
+        <v>136</v>
       </c>
       <c r="M63" t="s" s="2">
-        <v>285</v>
-      </c>
-      <c r="N63" t="s" s="2">
-        <v>286</v>
-      </c>
+        <v>137</v>
+      </c>
+      <c r="N63" s="2"/>
       <c r="O63" s="2"/>
       <c r="P63" t="s" s="2">
         <v>80</v>
       </c>
       <c r="Q63" s="2"/>
       <c r="R63" t="s" s="2">
-        <v>312</v>
+        <v>80</v>
       </c>
       <c r="S63" t="s" s="2">
         <v>80</v>
@@ -9716,25 +9728,25 @@
         <v>80</v>
       </c>
       <c r="AF63" t="s" s="2">
-        <v>287</v>
+        <v>159</v>
       </c>
       <c r="AG63" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="AH63" t="s" s="2">
-        <v>90</v>
+        <v>82</v>
       </c>
       <c r="AI63" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AJ63" t="s" s="2">
-        <v>80</v>
+        <v>141</v>
       </c>
       <c r="AK63" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AL63" t="s" s="2">
-        <v>133</v>
+        <v>80</v>
       </c>
       <c r="AM63" t="s" s="2">
         <v>80</v>
@@ -9754,10 +9766,10 @@
     </row>
     <row r="64" hidden="true">
       <c r="A64" t="s" s="2">
-        <v>339</v>
+        <v>242</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>314</v>
+        <v>163</v>
       </c>
       <c r="C64" s="2"/>
       <c r="D64" t="s" s="2">
@@ -9768,7 +9780,7 @@
         <v>81</v>
       </c>
       <c r="G64" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="H64" t="s" s="2">
         <v>80</v>
@@ -9780,13 +9792,13 @@
         <v>80</v>
       </c>
       <c r="K64" t="s" s="2">
-        <v>315</v>
+        <v>150</v>
       </c>
       <c r="L64" t="s" s="2">
-        <v>290</v>
+        <v>151</v>
       </c>
       <c r="M64" t="s" s="2">
-        <v>291</v>
+        <v>152</v>
       </c>
       <c r="N64" s="2"/>
       <c r="O64" s="2"/>
@@ -9837,7 +9849,7 @@
         <v>80</v>
       </c>
       <c r="AF64" t="s" s="2">
-        <v>294</v>
+        <v>153</v>
       </c>
       <c r="AG64" t="s" s="2">
         <v>81</v>
@@ -9849,13 +9861,13 @@
         <v>80</v>
       </c>
       <c r="AJ64" t="s" s="2">
-        <v>102</v>
+        <v>80</v>
       </c>
       <c r="AK64" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AL64" t="s" s="2">
-        <v>133</v>
+        <v>154</v>
       </c>
       <c r="AM64" t="s" s="2">
         <v>80</v>
@@ -9875,14 +9887,12 @@
     </row>
     <row r="65" hidden="true">
       <c r="A65" t="s" s="2">
-        <v>340</v>
+        <v>243</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>258</v>
-      </c>
-      <c r="C65" t="s" s="2">
-        <v>341</v>
-      </c>
+        <v>165</v>
+      </c>
+      <c r="C65" s="2"/>
       <c r="D65" t="s" s="2">
         <v>80</v>
       </c>
@@ -9891,7 +9901,7 @@
         <v>81</v>
       </c>
       <c r="G65" t="s" s="2">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="H65" t="s" s="2">
         <v>80</v>
@@ -9903,13 +9913,13 @@
         <v>80</v>
       </c>
       <c r="K65" t="s" s="2">
-        <v>266</v>
+        <v>135</v>
       </c>
       <c r="L65" t="s" s="2">
-        <v>342</v>
+        <v>136</v>
       </c>
       <c r="M65" t="s" s="2">
-        <v>268</v>
+        <v>137</v>
       </c>
       <c r="N65" s="2"/>
       <c r="O65" s="2"/>
@@ -9948,19 +9958,19 @@
         <v>80</v>
       </c>
       <c r="AB65" t="s" s="2">
-        <v>80</v>
+        <v>138</v>
       </c>
       <c r="AC65" t="s" s="2">
-        <v>80</v>
+        <v>158</v>
       </c>
       <c r="AD65" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AE65" t="s" s="2">
-        <v>80</v>
+        <v>139</v>
       </c>
       <c r="AF65" t="s" s="2">
-        <v>263</v>
+        <v>159</v>
       </c>
       <c r="AG65" t="s" s="2">
         <v>81</v>
@@ -9998,10 +10008,10 @@
     </row>
     <row r="66" hidden="true">
       <c r="A66" t="s" s="2">
-        <v>343</v>
+        <v>244</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>270</v>
+        <v>167</v>
       </c>
       <c r="C66" s="2"/>
       <c r="D66" t="s" s="2">
@@ -10009,7 +10019,7 @@
       </c>
       <c r="E66" s="2"/>
       <c r="F66" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="G66" t="s" s="2">
         <v>90</v>
@@ -10024,22 +10034,24 @@
         <v>80</v>
       </c>
       <c r="K66" t="s" s="2">
-        <v>253</v>
+        <v>104</v>
       </c>
       <c r="L66" t="s" s="2">
-        <v>254</v>
+        <v>168</v>
       </c>
       <c r="M66" t="s" s="2">
-        <v>255</v>
-      </c>
-      <c r="N66" s="2"/>
+        <v>169</v>
+      </c>
+      <c r="N66" t="s" s="2">
+        <v>170</v>
+      </c>
       <c r="O66" s="2"/>
       <c r="P66" t="s" s="2">
         <v>80</v>
       </c>
       <c r="Q66" s="2"/>
       <c r="R66" t="s" s="2">
-        <v>80</v>
+        <v>189</v>
       </c>
       <c r="S66" t="s" s="2">
         <v>80</v>
@@ -10081,10 +10093,10 @@
         <v>80</v>
       </c>
       <c r="AF66" t="s" s="2">
-        <v>256</v>
+        <v>171</v>
       </c>
       <c r="AG66" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="AH66" t="s" s="2">
         <v>90</v>
@@ -10099,7 +10111,7 @@
         <v>80</v>
       </c>
       <c r="AL66" t="s" s="2">
-        <v>257</v>
+        <v>133</v>
       </c>
       <c r="AM66" t="s" s="2">
         <v>80</v>
@@ -10119,10 +10131,10 @@
     </row>
     <row r="67" hidden="true">
       <c r="A67" t="s" s="2">
-        <v>344</v>
+        <v>245</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>272</v>
+        <v>173</v>
       </c>
       <c r="C67" s="2"/>
       <c r="D67" t="s" s="2">
@@ -10130,10 +10142,10 @@
       </c>
       <c r="E67" s="2"/>
       <c r="F67" t="s" s="2">
-        <v>273</v>
+        <v>81</v>
       </c>
       <c r="G67" t="s" s="2">
-        <v>82</v>
+        <v>90</v>
       </c>
       <c r="H67" t="s" s="2">
         <v>80</v>
@@ -10145,13 +10157,13 @@
         <v>80</v>
       </c>
       <c r="K67" t="s" s="2">
-        <v>136</v>
+        <v>246</v>
       </c>
       <c r="L67" t="s" s="2">
-        <v>274</v>
+        <v>174</v>
       </c>
       <c r="M67" t="s" s="2">
-        <v>275</v>
+        <v>175</v>
       </c>
       <c r="N67" s="2"/>
       <c r="O67" s="2"/>
@@ -10190,37 +10202,37 @@
         <v>80</v>
       </c>
       <c r="AB67" t="s" s="2">
-        <v>260</v>
+        <v>80</v>
       </c>
       <c r="AC67" t="s" s="2">
-        <v>261</v>
+        <v>80</v>
       </c>
       <c r="AD67" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AE67" t="s" s="2">
-        <v>262</v>
+        <v>80</v>
       </c>
       <c r="AF67" t="s" s="2">
-        <v>263</v>
+        <v>179</v>
       </c>
       <c r="AG67" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH67" t="s" s="2">
-        <v>82</v>
+        <v>90</v>
       </c>
       <c r="AI67" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AJ67" t="s" s="2">
-        <v>141</v>
+        <v>102</v>
       </c>
       <c r="AK67" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AL67" t="s" s="2">
-        <v>80</v>
+        <v>133</v>
       </c>
       <c r="AM67" t="s" s="2">
         <v>80</v>
@@ -10240,14 +10252,12 @@
     </row>
     <row r="68" hidden="true">
       <c r="A68" t="s" s="2">
-        <v>345</v>
+        <v>247</v>
       </c>
       <c r="B68" t="s" s="2">
-        <v>272</v>
-      </c>
-      <c r="C68" t="s" s="2">
-        <v>277</v>
-      </c>
+        <v>196</v>
+      </c>
+      <c r="C68" s="2"/>
       <c r="D68" t="s" s="2">
         <v>80</v>
       </c>
@@ -10268,22 +10278,24 @@
         <v>80</v>
       </c>
       <c r="K68" t="s" s="2">
-        <v>136</v>
+        <v>104</v>
       </c>
       <c r="L68" t="s" s="2">
-        <v>274</v>
+        <v>168</v>
       </c>
       <c r="M68" t="s" s="2">
-        <v>275</v>
-      </c>
-      <c r="N68" s="2"/>
+        <v>169</v>
+      </c>
+      <c r="N68" t="s" s="2">
+        <v>170</v>
+      </c>
       <c r="O68" s="2"/>
       <c r="P68" t="s" s="2">
         <v>80</v>
       </c>
       <c r="Q68" s="2"/>
       <c r="R68" t="s" s="2">
-        <v>80</v>
+        <v>197</v>
       </c>
       <c r="S68" t="s" s="2">
         <v>80</v>
@@ -10325,25 +10337,25 @@
         <v>80</v>
       </c>
       <c r="AF68" t="s" s="2">
-        <v>263</v>
+        <v>171</v>
       </c>
       <c r="AG68" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="AH68" t="s" s="2">
-        <v>82</v>
+        <v>90</v>
       </c>
       <c r="AI68" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AJ68" t="s" s="2">
-        <v>141</v>
+        <v>80</v>
       </c>
       <c r="AK68" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AL68" t="s" s="2">
-        <v>80</v>
+        <v>133</v>
       </c>
       <c r="AM68" t="s" s="2">
         <v>80</v>
@@ -10363,10 +10375,10 @@
     </row>
     <row r="69" hidden="true">
       <c r="A69" t="s" s="2">
-        <v>346</v>
+        <v>248</v>
       </c>
       <c r="B69" t="s" s="2">
-        <v>279</v>
+        <v>199</v>
       </c>
       <c r="C69" s="2"/>
       <c r="D69" t="s" s="2">
@@ -10377,7 +10389,7 @@
         <v>81</v>
       </c>
       <c r="G69" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="H69" t="s" s="2">
         <v>80</v>
@@ -10389,13 +10401,13 @@
         <v>80</v>
       </c>
       <c r="K69" t="s" s="2">
-        <v>253</v>
+        <v>200</v>
       </c>
       <c r="L69" t="s" s="2">
-        <v>254</v>
+        <v>174</v>
       </c>
       <c r="M69" t="s" s="2">
-        <v>255</v>
+        <v>175</v>
       </c>
       <c r="N69" s="2"/>
       <c r="O69" s="2"/>
@@ -10446,7 +10458,7 @@
         <v>80</v>
       </c>
       <c r="AF69" t="s" s="2">
-        <v>256</v>
+        <v>179</v>
       </c>
       <c r="AG69" t="s" s="2">
         <v>81</v>
@@ -10458,13 +10470,13 @@
         <v>80</v>
       </c>
       <c r="AJ69" t="s" s="2">
-        <v>80</v>
+        <v>102</v>
       </c>
       <c r="AK69" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AL69" t="s" s="2">
-        <v>257</v>
+        <v>133</v>
       </c>
       <c r="AM69" t="s" s="2">
         <v>80</v>
@@ -10484,42 +10496,46 @@
     </row>
     <row r="70" hidden="true">
       <c r="A70" t="s" s="2">
-        <v>347</v>
+        <v>249</v>
       </c>
       <c r="B70" t="s" s="2">
-        <v>281</v>
+        <v>249</v>
       </c>
       <c r="C70" s="2"/>
       <c r="D70" t="s" s="2">
-        <v>80</v>
+        <v>250</v>
       </c>
       <c r="E70" s="2"/>
       <c r="F70" t="s" s="2">
         <v>81</v>
       </c>
       <c r="G70" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="H70" t="s" s="2">
         <v>80</v>
       </c>
       <c r="I70" t="s" s="2">
-        <v>80</v>
+        <v>91</v>
       </c>
       <c r="J70" t="s" s="2">
         <v>80</v>
       </c>
       <c r="K70" t="s" s="2">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="L70" t="s" s="2">
-        <v>274</v>
+        <v>251</v>
       </c>
       <c r="M70" t="s" s="2">
-        <v>275</v>
-      </c>
-      <c r="N70" s="2"/>
-      <c r="O70" s="2"/>
+        <v>252</v>
+      </c>
+      <c r="N70" t="s" s="2">
+        <v>253</v>
+      </c>
+      <c r="O70" t="s" s="2">
+        <v>254</v>
+      </c>
       <c r="P70" t="s" s="2">
         <v>80</v>
       </c>
@@ -10555,19 +10571,19 @@
         <v>80</v>
       </c>
       <c r="AB70" t="s" s="2">
-        <v>260</v>
+        <v>80</v>
       </c>
       <c r="AC70" t="s" s="2">
-        <v>261</v>
+        <v>80</v>
       </c>
       <c r="AD70" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AE70" t="s" s="2">
-        <v>262</v>
+        <v>80</v>
       </c>
       <c r="AF70" t="s" s="2">
-        <v>263</v>
+        <v>255</v>
       </c>
       <c r="AG70" t="s" s="2">
         <v>81</v>
@@ -10585,7 +10601,7 @@
         <v>80</v>
       </c>
       <c r="AL70" t="s" s="2">
-        <v>80</v>
+        <v>133</v>
       </c>
       <c r="AM70" t="s" s="2">
         <v>80</v>
@@ -10605,10 +10621,10 @@
     </row>
     <row r="71" hidden="true">
       <c r="A71" t="s" s="2">
-        <v>348</v>
+        <v>256</v>
       </c>
       <c r="B71" t="s" s="2">
-        <v>283</v>
+        <v>256</v>
       </c>
       <c r="C71" s="2"/>
       <c r="D71" t="s" s="2">
@@ -10616,10 +10632,10 @@
       </c>
       <c r="E71" s="2"/>
       <c r="F71" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="G71" t="s" s="2">
-        <v>90</v>
+        <v>82</v>
       </c>
       <c r="H71" t="s" s="2">
         <v>80</v>
@@ -10628,19 +10644,19 @@
         <v>80</v>
       </c>
       <c r="J71" t="s" s="2">
-        <v>80</v>
+        <v>91</v>
       </c>
       <c r="K71" t="s" s="2">
-        <v>104</v>
+        <v>257</v>
       </c>
       <c r="L71" t="s" s="2">
-        <v>284</v>
+        <v>258</v>
       </c>
       <c r="M71" t="s" s="2">
-        <v>285</v>
+        <v>259</v>
       </c>
       <c r="N71" t="s" s="2">
-        <v>286</v>
+        <v>260</v>
       </c>
       <c r="O71" s="2"/>
       <c r="P71" t="s" s="2">
@@ -10648,7 +10664,7 @@
       </c>
       <c r="Q71" s="2"/>
       <c r="R71" t="s" s="2">
-        <v>277</v>
+        <v>80</v>
       </c>
       <c r="S71" t="s" s="2">
         <v>80</v>
@@ -10690,31 +10706,31 @@
         <v>80</v>
       </c>
       <c r="AF71" t="s" s="2">
-        <v>287</v>
+        <v>256</v>
       </c>
       <c r="AG71" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="AH71" t="s" s="2">
-        <v>90</v>
+        <v>82</v>
       </c>
       <c r="AI71" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AJ71" t="s" s="2">
-        <v>80</v>
+        <v>102</v>
       </c>
       <c r="AK71" t="s" s="2">
-        <v>80</v>
+        <v>261</v>
       </c>
       <c r="AL71" t="s" s="2">
-        <v>133</v>
+        <v>262</v>
       </c>
       <c r="AM71" t="s" s="2">
-        <v>80</v>
+        <v>263</v>
       </c>
       <c r="AN71" t="s" s="2">
-        <v>80</v>
+        <v>264</v>
       </c>
       <c r="AO71" t="s" s="2">
         <v>80</v>
@@ -10726,44 +10742,46 @@
         <v>80</v>
       </c>
     </row>
-    <row r="72" hidden="true">
+    <row r="72">
       <c r="A72" t="s" s="2">
-        <v>349</v>
+        <v>265</v>
       </c>
       <c r="B72" t="s" s="2">
-        <v>289</v>
+        <v>265</v>
       </c>
       <c r="C72" s="2"/>
       <c r="D72" t="s" s="2">
-        <v>80</v>
+        <v>266</v>
       </c>
       <c r="E72" s="2"/>
       <c r="F72" t="s" s="2">
         <v>81</v>
       </c>
       <c r="G72" t="s" s="2">
-        <v>90</v>
+        <v>82</v>
       </c>
       <c r="H72" t="s" s="2">
-        <v>80</v>
+        <v>91</v>
       </c>
       <c r="I72" t="s" s="2">
         <v>80</v>
       </c>
       <c r="J72" t="s" s="2">
-        <v>80</v>
+        <v>91</v>
       </c>
       <c r="K72" t="s" s="2">
-        <v>110</v>
+        <v>267</v>
       </c>
       <c r="L72" t="s" s="2">
-        <v>290</v>
+        <v>268</v>
       </c>
       <c r="M72" t="s" s="2">
-        <v>291</v>
+        <v>269</v>
       </c>
       <c r="N72" s="2"/>
-      <c r="O72" s="2"/>
+      <c r="O72" t="s" s="2">
+        <v>270</v>
+      </c>
       <c r="P72" t="s" s="2">
         <v>80</v>
       </c>
@@ -10772,7 +10790,7 @@
         <v>80</v>
       </c>
       <c r="S72" t="s" s="2">
-        <v>350</v>
+        <v>80</v>
       </c>
       <c r="T72" t="s" s="2">
         <v>80</v>
@@ -10787,11 +10805,13 @@
         <v>80</v>
       </c>
       <c r="X72" t="s" s="2">
-        <v>177</v>
-      </c>
-      <c r="Y72" s="2"/>
+        <v>80</v>
+      </c>
+      <c r="Y72" t="s" s="2">
+        <v>80</v>
+      </c>
       <c r="Z72" t="s" s="2">
-        <v>293</v>
+        <v>80</v>
       </c>
       <c r="AA72" t="s" s="2">
         <v>80</v>
@@ -10809,13 +10829,13 @@
         <v>80</v>
       </c>
       <c r="AF72" t="s" s="2">
-        <v>294</v>
+        <v>265</v>
       </c>
       <c r="AG72" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH72" t="s" s="2">
-        <v>90</v>
+        <v>82</v>
       </c>
       <c r="AI72" t="s" s="2">
         <v>80</v>
@@ -10824,10 +10844,10 @@
         <v>102</v>
       </c>
       <c r="AK72" t="s" s="2">
-        <v>80</v>
+        <v>271</v>
       </c>
       <c r="AL72" t="s" s="2">
-        <v>133</v>
+        <v>272</v>
       </c>
       <c r="AM72" t="s" s="2">
         <v>80</v>
@@ -10845,46 +10865,48 @@
         <v>80</v>
       </c>
     </row>
-    <row r="73" hidden="true">
+    <row r="73">
       <c r="A73" t="s" s="2">
-        <v>351</v>
+        <v>273</v>
       </c>
       <c r="B73" t="s" s="2">
-        <v>272</v>
-      </c>
-      <c r="C73" t="s" s="2">
-        <v>296</v>
-      </c>
+        <v>273</v>
+      </c>
+      <c r="C73" s="2"/>
       <c r="D73" t="s" s="2">
-        <v>80</v>
+        <v>274</v>
       </c>
       <c r="E73" s="2"/>
       <c r="F73" t="s" s="2">
         <v>81</v>
       </c>
       <c r="G73" t="s" s="2">
-        <v>90</v>
+        <v>82</v>
       </c>
       <c r="H73" t="s" s="2">
-        <v>80</v>
+        <v>91</v>
       </c>
       <c r="I73" t="s" s="2">
         <v>80</v>
       </c>
       <c r="J73" t="s" s="2">
-        <v>80</v>
+        <v>91</v>
       </c>
       <c r="K73" t="s" s="2">
-        <v>136</v>
+        <v>275</v>
       </c>
       <c r="L73" t="s" s="2">
-        <v>297</v>
+        <v>276</v>
       </c>
       <c r="M73" t="s" s="2">
-        <v>275</v>
-      </c>
-      <c r="N73" s="2"/>
-      <c r="O73" s="2"/>
+        <v>277</v>
+      </c>
+      <c r="N73" t="s" s="2">
+        <v>278</v>
+      </c>
+      <c r="O73" t="s" s="2">
+        <v>279</v>
+      </c>
       <c r="P73" t="s" s="2">
         <v>80</v>
       </c>
@@ -10932,7 +10954,7 @@
         <v>80</v>
       </c>
       <c r="AF73" t="s" s="2">
-        <v>263</v>
+        <v>273</v>
       </c>
       <c r="AG73" t="s" s="2">
         <v>81</v>
@@ -10944,13 +10966,13 @@
         <v>80</v>
       </c>
       <c r="AJ73" t="s" s="2">
-        <v>141</v>
+        <v>102</v>
       </c>
       <c r="AK73" t="s" s="2">
-        <v>80</v>
+        <v>280</v>
       </c>
       <c r="AL73" t="s" s="2">
-        <v>80</v>
+        <v>281</v>
       </c>
       <c r="AM73" t="s" s="2">
         <v>80</v>
@@ -10970,10 +10992,10 @@
     </row>
     <row r="74" hidden="true">
       <c r="A74" t="s" s="2">
-        <v>352</v>
+        <v>282</v>
       </c>
       <c r="B74" t="s" s="2">
-        <v>279</v>
+        <v>282</v>
       </c>
       <c r="C74" s="2"/>
       <c r="D74" t="s" s="2">
@@ -10981,7 +11003,7 @@
       </c>
       <c r="E74" s="2"/>
       <c r="F74" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="G74" t="s" s="2">
         <v>90</v>
@@ -10990,21 +11012,23 @@
         <v>80</v>
       </c>
       <c r="I74" t="s" s="2">
-        <v>80</v>
+        <v>91</v>
       </c>
       <c r="J74" t="s" s="2">
-        <v>80</v>
+        <v>91</v>
       </c>
       <c r="K74" t="s" s="2">
-        <v>253</v>
+        <v>110</v>
       </c>
       <c r="L74" t="s" s="2">
-        <v>254</v>
+        <v>283</v>
       </c>
       <c r="M74" t="s" s="2">
-        <v>255</v>
-      </c>
-      <c r="N74" s="2"/>
+        <v>284</v>
+      </c>
+      <c r="N74" t="s" s="2">
+        <v>285</v>
+      </c>
       <c r="O74" s="2"/>
       <c r="P74" t="s" s="2">
         <v>80</v>
@@ -11029,13 +11053,13 @@
         <v>80</v>
       </c>
       <c r="X74" t="s" s="2">
-        <v>80</v>
+        <v>177</v>
       </c>
       <c r="Y74" t="s" s="2">
-        <v>80</v>
+        <v>286</v>
       </c>
       <c r="Z74" t="s" s="2">
-        <v>80</v>
+        <v>287</v>
       </c>
       <c r="AA74" t="s" s="2">
         <v>80</v>
@@ -11053,10 +11077,10 @@
         <v>80</v>
       </c>
       <c r="AF74" t="s" s="2">
-        <v>256</v>
+        <v>282</v>
       </c>
       <c r="AG74" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="AH74" t="s" s="2">
         <v>90</v>
@@ -11065,22 +11089,22 @@
         <v>80</v>
       </c>
       <c r="AJ74" t="s" s="2">
-        <v>80</v>
+        <v>102</v>
       </c>
       <c r="AK74" t="s" s="2">
-        <v>80</v>
+        <v>288</v>
       </c>
       <c r="AL74" t="s" s="2">
-        <v>257</v>
+        <v>289</v>
       </c>
       <c r="AM74" t="s" s="2">
-        <v>80</v>
+        <v>290</v>
       </c>
       <c r="AN74" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AO74" t="s" s="2">
-        <v>80</v>
+        <v>291</v>
       </c>
       <c r="AP74" t="s" s="2">
         <v>80</v>
@@ -11091,10 +11115,10 @@
     </row>
     <row r="75" hidden="true">
       <c r="A75" t="s" s="2">
-        <v>353</v>
+        <v>292</v>
       </c>
       <c r="B75" t="s" s="2">
-        <v>281</v>
+        <v>292</v>
       </c>
       <c r="C75" s="2"/>
       <c r="D75" t="s" s="2">
@@ -11105,7 +11129,7 @@
         <v>81</v>
       </c>
       <c r="G75" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="H75" t="s" s="2">
         <v>80</v>
@@ -11114,19 +11138,21 @@
         <v>80</v>
       </c>
       <c r="J75" t="s" s="2">
-        <v>80</v>
+        <v>91</v>
       </c>
       <c r="K75" t="s" s="2">
-        <v>136</v>
+        <v>187</v>
       </c>
       <c r="L75" t="s" s="2">
-        <v>274</v>
+        <v>293</v>
       </c>
       <c r="M75" t="s" s="2">
-        <v>275</v>
+        <v>294</v>
       </c>
       <c r="N75" s="2"/>
-      <c r="O75" s="2"/>
+      <c r="O75" t="s" s="2">
+        <v>295</v>
+      </c>
       <c r="P75" t="s" s="2">
         <v>80</v>
       </c>
@@ -11150,52 +11176,52 @@
         <v>80</v>
       </c>
       <c r="X75" t="s" s="2">
-        <v>80</v>
+        <v>296</v>
       </c>
       <c r="Y75" t="s" s="2">
-        <v>80</v>
+        <v>297</v>
       </c>
       <c r="Z75" t="s" s="2">
-        <v>80</v>
+        <v>298</v>
       </c>
       <c r="AA75" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AB75" t="s" s="2">
-        <v>260</v>
+        <v>80</v>
       </c>
       <c r="AC75" t="s" s="2">
-        <v>261</v>
+        <v>80</v>
       </c>
       <c r="AD75" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AE75" t="s" s="2">
-        <v>262</v>
+        <v>80</v>
       </c>
       <c r="AF75" t="s" s="2">
-        <v>263</v>
+        <v>292</v>
       </c>
       <c r="AG75" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH75" t="s" s="2">
-        <v>82</v>
+        <v>90</v>
       </c>
       <c r="AI75" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AJ75" t="s" s="2">
-        <v>141</v>
+        <v>102</v>
       </c>
       <c r="AK75" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AL75" t="s" s="2">
-        <v>80</v>
+        <v>299</v>
       </c>
       <c r="AM75" t="s" s="2">
-        <v>80</v>
+        <v>300</v>
       </c>
       <c r="AN75" t="s" s="2">
         <v>80</v>
@@ -11212,10 +11238,10 @@
     </row>
     <row r="76" hidden="true">
       <c r="A76" t="s" s="2">
-        <v>354</v>
+        <v>301</v>
       </c>
       <c r="B76" t="s" s="2">
-        <v>283</v>
+        <v>301</v>
       </c>
       <c r="C76" s="2"/>
       <c r="D76" t="s" s="2">
@@ -11223,7 +11249,7 @@
       </c>
       <c r="E76" s="2"/>
       <c r="F76" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="G76" t="s" s="2">
         <v>90</v>
@@ -11235,27 +11261,25 @@
         <v>80</v>
       </c>
       <c r="J76" t="s" s="2">
-        <v>80</v>
+        <v>91</v>
       </c>
       <c r="K76" t="s" s="2">
-        <v>104</v>
+        <v>187</v>
       </c>
       <c r="L76" t="s" s="2">
-        <v>284</v>
+        <v>302</v>
       </c>
       <c r="M76" t="s" s="2">
-        <v>285</v>
-      </c>
-      <c r="N76" t="s" s="2">
-        <v>286</v>
-      </c>
+        <v>303</v>
+      </c>
+      <c r="N76" s="2"/>
       <c r="O76" s="2"/>
       <c r="P76" t="s" s="2">
         <v>80</v>
       </c>
       <c r="Q76" s="2"/>
       <c r="R76" t="s" s="2">
-        <v>296</v>
+        <v>80</v>
       </c>
       <c r="S76" t="s" s="2">
         <v>80</v>
@@ -11273,13 +11297,13 @@
         <v>80</v>
       </c>
       <c r="X76" t="s" s="2">
-        <v>80</v>
+        <v>304</v>
       </c>
       <c r="Y76" t="s" s="2">
-        <v>80</v>
+        <v>305</v>
       </c>
       <c r="Z76" t="s" s="2">
-        <v>80</v>
+        <v>306</v>
       </c>
       <c r="AA76" t="s" s="2">
         <v>80</v>
@@ -11297,10 +11321,10 @@
         <v>80</v>
       </c>
       <c r="AF76" t="s" s="2">
-        <v>287</v>
+        <v>301</v>
       </c>
       <c r="AG76" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="AH76" t="s" s="2">
         <v>90</v>
@@ -11309,19 +11333,19 @@
         <v>80</v>
       </c>
       <c r="AJ76" t="s" s="2">
-        <v>80</v>
+        <v>102</v>
       </c>
       <c r="AK76" t="s" s="2">
-        <v>80</v>
+        <v>307</v>
       </c>
       <c r="AL76" t="s" s="2">
-        <v>133</v>
+        <v>308</v>
       </c>
       <c r="AM76" t="s" s="2">
-        <v>80</v>
+        <v>309</v>
       </c>
       <c r="AN76" t="s" s="2">
-        <v>80</v>
+        <v>310</v>
       </c>
       <c r="AO76" t="s" s="2">
         <v>80</v>
@@ -11335,10 +11359,10 @@
     </row>
     <row r="77" hidden="true">
       <c r="A77" t="s" s="2">
-        <v>355</v>
+        <v>311</v>
       </c>
       <c r="B77" t="s" s="2">
-        <v>289</v>
+        <v>311</v>
       </c>
       <c r="C77" s="2"/>
       <c r="D77" t="s" s="2">
@@ -11358,16 +11382,16 @@
         <v>80</v>
       </c>
       <c r="J77" t="s" s="2">
-        <v>80</v>
+        <v>91</v>
       </c>
       <c r="K77" t="s" s="2">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="L77" t="s" s="2">
-        <v>290</v>
+        <v>312</v>
       </c>
       <c r="M77" t="s" s="2">
-        <v>291</v>
+        <v>313</v>
       </c>
       <c r="N77" s="2"/>
       <c r="O77" s="2"/>
@@ -11394,13 +11418,13 @@
         <v>80</v>
       </c>
       <c r="X77" t="s" s="2">
-        <v>80</v>
+        <v>304</v>
       </c>
       <c r="Y77" t="s" s="2">
-        <v>80</v>
+        <v>314</v>
       </c>
       <c r="Z77" t="s" s="2">
-        <v>80</v>
+        <v>315</v>
       </c>
       <c r="AA77" t="s" s="2">
         <v>80</v>
@@ -11418,7 +11442,7 @@
         <v>80</v>
       </c>
       <c r="AF77" t="s" s="2">
-        <v>294</v>
+        <v>311</v>
       </c>
       <c r="AG77" t="s" s="2">
         <v>81</v>
@@ -11436,7 +11460,7 @@
         <v>80</v>
       </c>
       <c r="AL77" t="s" s="2">
-        <v>133</v>
+        <v>316</v>
       </c>
       <c r="AM77" t="s" s="2">
         <v>80</v>
@@ -11454,43 +11478,41 @@
         <v>80</v>
       </c>
     </row>
-    <row r="78" hidden="true">
+    <row r="78">
       <c r="A78" t="s" s="2">
-        <v>356</v>
+        <v>317</v>
       </c>
       <c r="B78" t="s" s="2">
-        <v>272</v>
-      </c>
-      <c r="C78" t="s" s="2">
-        <v>303</v>
-      </c>
+        <v>317</v>
+      </c>
+      <c r="C78" s="2"/>
       <c r="D78" t="s" s="2">
         <v>80</v>
       </c>
       <c r="E78" s="2"/>
       <c r="F78" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="G78" t="s" s="2">
         <v>90</v>
       </c>
       <c r="H78" t="s" s="2">
-        <v>80</v>
+        <v>91</v>
       </c>
       <c r="I78" t="s" s="2">
         <v>80</v>
       </c>
       <c r="J78" t="s" s="2">
-        <v>80</v>
+        <v>91</v>
       </c>
       <c r="K78" t="s" s="2">
-        <v>136</v>
+        <v>318</v>
       </c>
       <c r="L78" t="s" s="2">
-        <v>304</v>
+        <v>319</v>
       </c>
       <c r="M78" t="s" s="2">
-        <v>275</v>
+        <v>320</v>
       </c>
       <c r="N78" s="2"/>
       <c r="O78" s="2"/>
@@ -11541,31 +11563,31 @@
         <v>80</v>
       </c>
       <c r="AF78" t="s" s="2">
-        <v>263</v>
+        <v>317</v>
       </c>
       <c r="AG78" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH78" t="s" s="2">
-        <v>82</v>
+        <v>90</v>
       </c>
       <c r="AI78" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AJ78" t="s" s="2">
-        <v>141</v>
+        <v>102</v>
       </c>
       <c r="AK78" t="s" s="2">
-        <v>80</v>
+        <v>321</v>
       </c>
       <c r="AL78" t="s" s="2">
-        <v>80</v>
+        <v>322</v>
       </c>
       <c r="AM78" t="s" s="2">
-        <v>80</v>
+        <v>323</v>
       </c>
       <c r="AN78" t="s" s="2">
-        <v>80</v>
+        <v>324</v>
       </c>
       <c r="AO78" t="s" s="2">
         <v>80</v>
@@ -11579,14 +11601,14 @@
     </row>
     <row r="79" hidden="true">
       <c r="A79" t="s" s="2">
-        <v>357</v>
+        <v>325</v>
       </c>
       <c r="B79" t="s" s="2">
-        <v>279</v>
+        <v>325</v>
       </c>
       <c r="C79" s="2"/>
       <c r="D79" t="s" s="2">
-        <v>80</v>
+        <v>326</v>
       </c>
       <c r="E79" s="2"/>
       <c r="F79" t="s" s="2">
@@ -11602,19 +11624,23 @@
         <v>80</v>
       </c>
       <c r="J79" t="s" s="2">
-        <v>80</v>
+        <v>91</v>
       </c>
       <c r="K79" t="s" s="2">
-        <v>253</v>
+        <v>327</v>
       </c>
       <c r="L79" t="s" s="2">
-        <v>254</v>
+        <v>328</v>
       </c>
       <c r="M79" t="s" s="2">
-        <v>255</v>
-      </c>
-      <c r="N79" s="2"/>
-      <c r="O79" s="2"/>
+        <v>329</v>
+      </c>
+      <c r="N79" t="s" s="2">
+        <v>330</v>
+      </c>
+      <c r="O79" t="s" s="2">
+        <v>331</v>
+      </c>
       <c r="P79" t="s" s="2">
         <v>80</v>
       </c>
@@ -11662,7 +11688,7 @@
         <v>80</v>
       </c>
       <c r="AF79" t="s" s="2">
-        <v>256</v>
+        <v>325</v>
       </c>
       <c r="AG79" t="s" s="2">
         <v>81</v>
@@ -11674,16 +11700,16 @@
         <v>80</v>
       </c>
       <c r="AJ79" t="s" s="2">
-        <v>80</v>
+        <v>102</v>
       </c>
       <c r="AK79" t="s" s="2">
-        <v>80</v>
+        <v>332</v>
       </c>
       <c r="AL79" t="s" s="2">
-        <v>257</v>
+        <v>333</v>
       </c>
       <c r="AM79" t="s" s="2">
-        <v>80</v>
+        <v>334</v>
       </c>
       <c r="AN79" t="s" s="2">
         <v>80</v>
@@ -11700,21 +11726,21 @@
     </row>
     <row r="80" hidden="true">
       <c r="A80" t="s" s="2">
-        <v>358</v>
+        <v>335</v>
       </c>
       <c r="B80" t="s" s="2">
-        <v>281</v>
+        <v>335</v>
       </c>
       <c r="C80" s="2"/>
       <c r="D80" t="s" s="2">
-        <v>80</v>
+        <v>336</v>
       </c>
       <c r="E80" s="2"/>
       <c r="F80" t="s" s="2">
         <v>81</v>
       </c>
       <c r="G80" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="H80" t="s" s="2">
         <v>80</v>
@@ -11723,16 +11749,16 @@
         <v>80</v>
       </c>
       <c r="J80" t="s" s="2">
-        <v>80</v>
+        <v>91</v>
       </c>
       <c r="K80" t="s" s="2">
-        <v>136</v>
+        <v>337</v>
       </c>
       <c r="L80" t="s" s="2">
-        <v>274</v>
+        <v>338</v>
       </c>
       <c r="M80" t="s" s="2">
-        <v>275</v>
+        <v>339</v>
       </c>
       <c r="N80" s="2"/>
       <c r="O80" s="2"/>
@@ -11771,40 +11797,40 @@
         <v>80</v>
       </c>
       <c r="AB80" t="s" s="2">
-        <v>260</v>
+        <v>80</v>
       </c>
       <c r="AC80" t="s" s="2">
-        <v>261</v>
+        <v>80</v>
       </c>
       <c r="AD80" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AE80" t="s" s="2">
-        <v>262</v>
+        <v>80</v>
       </c>
       <c r="AF80" t="s" s="2">
-        <v>263</v>
+        <v>335</v>
       </c>
       <c r="AG80" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH80" t="s" s="2">
-        <v>82</v>
+        <v>90</v>
       </c>
       <c r="AI80" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AJ80" t="s" s="2">
-        <v>141</v>
+        <v>102</v>
       </c>
       <c r="AK80" t="s" s="2">
-        <v>80</v>
+        <v>340</v>
       </c>
       <c r="AL80" t="s" s="2">
-        <v>80</v>
+        <v>341</v>
       </c>
       <c r="AM80" t="s" s="2">
-        <v>80</v>
+        <v>342</v>
       </c>
       <c r="AN80" t="s" s="2">
         <v>80</v>
@@ -11821,10 +11847,10 @@
     </row>
     <row r="81" hidden="true">
       <c r="A81" t="s" s="2">
-        <v>359</v>
+        <v>343</v>
       </c>
       <c r="B81" t="s" s="2">
-        <v>283</v>
+        <v>343</v>
       </c>
       <c r="C81" s="2"/>
       <c r="D81" t="s" s="2">
@@ -11832,7 +11858,7 @@
       </c>
       <c r="E81" s="2"/>
       <c r="F81" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="G81" t="s" s="2">
         <v>90</v>
@@ -11844,19 +11870,19 @@
         <v>80</v>
       </c>
       <c r="J81" t="s" s="2">
-        <v>80</v>
+        <v>91</v>
       </c>
       <c r="K81" t="s" s="2">
-        <v>104</v>
+        <v>344</v>
       </c>
       <c r="L81" t="s" s="2">
-        <v>284</v>
+        <v>345</v>
       </c>
       <c r="M81" t="s" s="2">
-        <v>285</v>
+        <v>346</v>
       </c>
       <c r="N81" t="s" s="2">
-        <v>286</v>
+        <v>347</v>
       </c>
       <c r="O81" s="2"/>
       <c r="P81" t="s" s="2">
@@ -11864,7 +11890,7 @@
       </c>
       <c r="Q81" s="2"/>
       <c r="R81" t="s" s="2">
-        <v>303</v>
+        <v>80</v>
       </c>
       <c r="S81" t="s" s="2">
         <v>80</v>
@@ -11906,10 +11932,10 @@
         <v>80</v>
       </c>
       <c r="AF81" t="s" s="2">
-        <v>287</v>
+        <v>343</v>
       </c>
       <c r="AG81" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="AH81" t="s" s="2">
         <v>90</v>
@@ -11918,22 +11944,22 @@
         <v>80</v>
       </c>
       <c r="AJ81" t="s" s="2">
-        <v>80</v>
+        <v>102</v>
       </c>
       <c r="AK81" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AL81" t="s" s="2">
-        <v>133</v>
+        <v>348</v>
       </c>
       <c r="AM81" t="s" s="2">
-        <v>80</v>
+        <v>349</v>
       </c>
       <c r="AN81" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AO81" t="s" s="2">
-        <v>80</v>
+        <v>350</v>
       </c>
       <c r="AP81" t="s" s="2">
         <v>80</v>
@@ -11942,12 +11968,12 @@
         <v>80</v>
       </c>
     </row>
-    <row r="82" hidden="true">
+    <row r="82">
       <c r="A82" t="s" s="2">
-        <v>360</v>
+        <v>351</v>
       </c>
       <c r="B82" t="s" s="2">
-        <v>289</v>
+        <v>351</v>
       </c>
       <c r="C82" s="2"/>
       <c r="D82" t="s" s="2">
@@ -11961,22 +11987,22 @@
         <v>90</v>
       </c>
       <c r="H82" t="s" s="2">
-        <v>80</v>
+        <v>91</v>
       </c>
       <c r="I82" t="s" s="2">
         <v>80</v>
       </c>
       <c r="J82" t="s" s="2">
-        <v>80</v>
+        <v>91</v>
       </c>
       <c r="K82" t="s" s="2">
-        <v>309</v>
+        <v>352</v>
       </c>
       <c r="L82" t="s" s="2">
-        <v>290</v>
+        <v>353</v>
       </c>
       <c r="M82" t="s" s="2">
-        <v>291</v>
+        <v>354</v>
       </c>
       <c r="N82" s="2"/>
       <c r="O82" s="2"/>
@@ -12027,7 +12053,7 @@
         <v>80</v>
       </c>
       <c r="AF82" t="s" s="2">
-        <v>294</v>
+        <v>351</v>
       </c>
       <c r="AG82" t="s" s="2">
         <v>81</v>
@@ -12042,16 +12068,16 @@
         <v>102</v>
       </c>
       <c r="AK82" t="s" s="2">
-        <v>80</v>
+        <v>355</v>
       </c>
       <c r="AL82" t="s" s="2">
-        <v>133</v>
+        <v>356</v>
       </c>
       <c r="AM82" t="s" s="2">
-        <v>80</v>
+        <v>357</v>
       </c>
       <c r="AN82" t="s" s="2">
-        <v>80</v>
+        <v>358</v>
       </c>
       <c r="AO82" t="s" s="2">
         <v>80</v>
@@ -12065,10 +12091,10 @@
     </row>
     <row r="83" hidden="true">
       <c r="A83" t="s" s="2">
-        <v>361</v>
+        <v>359</v>
       </c>
       <c r="B83" t="s" s="2">
-        <v>311</v>
+        <v>359</v>
       </c>
       <c r="C83" s="2"/>
       <c r="D83" t="s" s="2">
@@ -12076,7 +12102,7 @@
       </c>
       <c r="E83" s="2"/>
       <c r="F83" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="G83" t="s" s="2">
         <v>90</v>
@@ -12091,24 +12117,22 @@
         <v>80</v>
       </c>
       <c r="K83" t="s" s="2">
-        <v>104</v>
+        <v>150</v>
       </c>
       <c r="L83" t="s" s="2">
-        <v>284</v>
+        <v>151</v>
       </c>
       <c r="M83" t="s" s="2">
-        <v>285</v>
-      </c>
-      <c r="N83" t="s" s="2">
-        <v>286</v>
-      </c>
+        <v>152</v>
+      </c>
+      <c r="N83" s="2"/>
       <c r="O83" s="2"/>
       <c r="P83" t="s" s="2">
         <v>80</v>
       </c>
       <c r="Q83" s="2"/>
       <c r="R83" t="s" s="2">
-        <v>312</v>
+        <v>80</v>
       </c>
       <c r="S83" t="s" s="2">
         <v>80</v>
@@ -12150,10 +12174,10 @@
         <v>80</v>
       </c>
       <c r="AF83" t="s" s="2">
-        <v>287</v>
+        <v>153</v>
       </c>
       <c r="AG83" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="AH83" t="s" s="2">
         <v>90</v>
@@ -12168,7 +12192,7 @@
         <v>80</v>
       </c>
       <c r="AL83" t="s" s="2">
-        <v>133</v>
+        <v>154</v>
       </c>
       <c r="AM83" t="s" s="2">
         <v>80</v>
@@ -12188,21 +12212,21 @@
     </row>
     <row r="84" hidden="true">
       <c r="A84" t="s" s="2">
-        <v>362</v>
+        <v>360</v>
       </c>
       <c r="B84" t="s" s="2">
-        <v>314</v>
+        <v>360</v>
       </c>
       <c r="C84" s="2"/>
       <c r="D84" t="s" s="2">
-        <v>80</v>
+        <v>250</v>
       </c>
       <c r="E84" s="2"/>
       <c r="F84" t="s" s="2">
         <v>81</v>
       </c>
       <c r="G84" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="H84" t="s" s="2">
         <v>80</v>
@@ -12214,15 +12238,17 @@
         <v>80</v>
       </c>
       <c r="K84" t="s" s="2">
-        <v>315</v>
+        <v>135</v>
       </c>
       <c r="L84" t="s" s="2">
-        <v>290</v>
+        <v>361</v>
       </c>
       <c r="M84" t="s" s="2">
-        <v>291</v>
-      </c>
-      <c r="N84" s="2"/>
+        <v>362</v>
+      </c>
+      <c r="N84" t="s" s="2">
+        <v>253</v>
+      </c>
       <c r="O84" s="2"/>
       <c r="P84" t="s" s="2">
         <v>80</v>
@@ -12259,37 +12285,37 @@
         <v>80</v>
       </c>
       <c r="AB84" t="s" s="2">
-        <v>80</v>
+        <v>138</v>
       </c>
       <c r="AC84" t="s" s="2">
-        <v>80</v>
+        <v>158</v>
       </c>
       <c r="AD84" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AE84" t="s" s="2">
-        <v>80</v>
+        <v>139</v>
       </c>
       <c r="AF84" t="s" s="2">
-        <v>294</v>
+        <v>159</v>
       </c>
       <c r="AG84" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH84" t="s" s="2">
-        <v>90</v>
+        <v>82</v>
       </c>
       <c r="AI84" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AJ84" t="s" s="2">
-        <v>102</v>
+        <v>141</v>
       </c>
       <c r="AK84" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AL84" t="s" s="2">
-        <v>133</v>
+        <v>154</v>
       </c>
       <c r="AM84" t="s" s="2">
         <v>80</v>
@@ -12312,7 +12338,7 @@
         <v>363</v>
       </c>
       <c r="B85" t="s" s="2">
-        <v>258</v>
+        <v>360</v>
       </c>
       <c r="C85" t="s" s="2">
         <v>364</v>
@@ -12337,13 +12363,13 @@
         <v>80</v>
       </c>
       <c r="K85" t="s" s="2">
-        <v>266</v>
+        <v>144</v>
       </c>
       <c r="L85" t="s" s="2">
         <v>365</v>
       </c>
       <c r="M85" t="s" s="2">
-        <v>268</v>
+        <v>146</v>
       </c>
       <c r="N85" s="2"/>
       <c r="O85" s="2"/>
@@ -12394,7 +12420,7 @@
         <v>80</v>
       </c>
       <c r="AF85" t="s" s="2">
-        <v>263</v>
+        <v>159</v>
       </c>
       <c r="AG85" t="s" s="2">
         <v>81</v>
@@ -12435,7 +12461,7 @@
         <v>366</v>
       </c>
       <c r="B86" t="s" s="2">
-        <v>270</v>
+        <v>367</v>
       </c>
       <c r="C86" s="2"/>
       <c r="D86" t="s" s="2">
@@ -12458,13 +12484,13 @@
         <v>80</v>
       </c>
       <c r="K86" t="s" s="2">
-        <v>253</v>
+        <v>150</v>
       </c>
       <c r="L86" t="s" s="2">
-        <v>254</v>
+        <v>151</v>
       </c>
       <c r="M86" t="s" s="2">
-        <v>255</v>
+        <v>152</v>
       </c>
       <c r="N86" s="2"/>
       <c r="O86" s="2"/>
@@ -12515,7 +12541,7 @@
         <v>80</v>
       </c>
       <c r="AF86" t="s" s="2">
-        <v>256</v>
+        <v>153</v>
       </c>
       <c r="AG86" t="s" s="2">
         <v>81</v>
@@ -12533,7 +12559,7 @@
         <v>80</v>
       </c>
       <c r="AL86" t="s" s="2">
-        <v>257</v>
+        <v>154</v>
       </c>
       <c r="AM86" t="s" s="2">
         <v>80</v>
@@ -12553,10 +12579,10 @@
     </row>
     <row r="87" hidden="true">
       <c r="A87" t="s" s="2">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="B87" t="s" s="2">
-        <v>272</v>
+        <v>369</v>
       </c>
       <c r="C87" s="2"/>
       <c r="D87" t="s" s="2">
@@ -12564,7 +12590,7 @@
       </c>
       <c r="E87" s="2"/>
       <c r="F87" t="s" s="2">
-        <v>273</v>
+        <v>157</v>
       </c>
       <c r="G87" t="s" s="2">
         <v>82</v>
@@ -12579,13 +12605,13 @@
         <v>80</v>
       </c>
       <c r="K87" t="s" s="2">
+        <v>135</v>
+      </c>
+      <c r="L87" t="s" s="2">
         <v>136</v>
       </c>
-      <c r="L87" t="s" s="2">
-        <v>274</v>
-      </c>
       <c r="M87" t="s" s="2">
-        <v>275</v>
+        <v>137</v>
       </c>
       <c r="N87" s="2"/>
       <c r="O87" s="2"/>
@@ -12624,19 +12650,19 @@
         <v>80</v>
       </c>
       <c r="AB87" t="s" s="2">
-        <v>260</v>
+        <v>138</v>
       </c>
       <c r="AC87" t="s" s="2">
-        <v>261</v>
+        <v>158</v>
       </c>
       <c r="AD87" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AE87" t="s" s="2">
-        <v>262</v>
+        <v>139</v>
       </c>
       <c r="AF87" t="s" s="2">
-        <v>263</v>
+        <v>159</v>
       </c>
       <c r="AG87" t="s" s="2">
         <v>81</v>
@@ -12674,13 +12700,13 @@
     </row>
     <row r="88" hidden="true">
       <c r="A88" t="s" s="2">
-        <v>368</v>
+        <v>370</v>
       </c>
       <c r="B88" t="s" s="2">
-        <v>272</v>
+        <v>369</v>
       </c>
       <c r="C88" t="s" s="2">
-        <v>277</v>
+        <v>161</v>
       </c>
       <c r="D88" t="s" s="2">
         <v>80</v>
@@ -12702,13 +12728,13 @@
         <v>80</v>
       </c>
       <c r="K88" t="s" s="2">
+        <v>135</v>
+      </c>
+      <c r="L88" t="s" s="2">
         <v>136</v>
       </c>
-      <c r="L88" t="s" s="2">
-        <v>274</v>
-      </c>
       <c r="M88" t="s" s="2">
-        <v>275</v>
+        <v>137</v>
       </c>
       <c r="N88" s="2"/>
       <c r="O88" s="2"/>
@@ -12759,7 +12785,7 @@
         <v>80</v>
       </c>
       <c r="AF88" t="s" s="2">
-        <v>263</v>
+        <v>159</v>
       </c>
       <c r="AG88" t="s" s="2">
         <v>81</v>
@@ -12797,10 +12823,10 @@
     </row>
     <row r="89" hidden="true">
       <c r="A89" t="s" s="2">
-        <v>369</v>
+        <v>371</v>
       </c>
       <c r="B89" t="s" s="2">
-        <v>279</v>
+        <v>372</v>
       </c>
       <c r="C89" s="2"/>
       <c r="D89" t="s" s="2">
@@ -12823,13 +12849,13 @@
         <v>80</v>
       </c>
       <c r="K89" t="s" s="2">
-        <v>253</v>
+        <v>150</v>
       </c>
       <c r="L89" t="s" s="2">
-        <v>254</v>
+        <v>151</v>
       </c>
       <c r="M89" t="s" s="2">
-        <v>255</v>
+        <v>152</v>
       </c>
       <c r="N89" s="2"/>
       <c r="O89" s="2"/>
@@ -12880,7 +12906,7 @@
         <v>80</v>
       </c>
       <c r="AF89" t="s" s="2">
-        <v>256</v>
+        <v>153</v>
       </c>
       <c r="AG89" t="s" s="2">
         <v>81</v>
@@ -12898,7 +12924,7 @@
         <v>80</v>
       </c>
       <c r="AL89" t="s" s="2">
-        <v>257</v>
+        <v>154</v>
       </c>
       <c r="AM89" t="s" s="2">
         <v>80</v>
@@ -12918,10 +12944,10 @@
     </row>
     <row r="90" hidden="true">
       <c r="A90" t="s" s="2">
-        <v>370</v>
+        <v>373</v>
       </c>
       <c r="B90" t="s" s="2">
-        <v>281</v>
+        <v>374</v>
       </c>
       <c r="C90" s="2"/>
       <c r="D90" t="s" s="2">
@@ -12944,13 +12970,13 @@
         <v>80</v>
       </c>
       <c r="K90" t="s" s="2">
+        <v>135</v>
+      </c>
+      <c r="L90" t="s" s="2">
         <v>136</v>
       </c>
-      <c r="L90" t="s" s="2">
-        <v>274</v>
-      </c>
       <c r="M90" t="s" s="2">
-        <v>275</v>
+        <v>137</v>
       </c>
       <c r="N90" s="2"/>
       <c r="O90" s="2"/>
@@ -12989,19 +13015,19 @@
         <v>80</v>
       </c>
       <c r="AB90" t="s" s="2">
-        <v>260</v>
+        <v>138</v>
       </c>
       <c r="AC90" t="s" s="2">
-        <v>261</v>
+        <v>158</v>
       </c>
       <c r="AD90" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AE90" t="s" s="2">
-        <v>262</v>
+        <v>139</v>
       </c>
       <c r="AF90" t="s" s="2">
-        <v>263</v>
+        <v>159</v>
       </c>
       <c r="AG90" t="s" s="2">
         <v>81</v>
@@ -13039,10 +13065,10 @@
     </row>
     <row r="91" hidden="true">
       <c r="A91" t="s" s="2">
-        <v>371</v>
+        <v>375</v>
       </c>
       <c r="B91" t="s" s="2">
-        <v>283</v>
+        <v>376</v>
       </c>
       <c r="C91" s="2"/>
       <c r="D91" t="s" s="2">
@@ -13068,13 +13094,13 @@
         <v>104</v>
       </c>
       <c r="L91" t="s" s="2">
-        <v>284</v>
+        <v>168</v>
       </c>
       <c r="M91" t="s" s="2">
-        <v>285</v>
+        <v>169</v>
       </c>
       <c r="N91" t="s" s="2">
-        <v>286</v>
+        <v>170</v>
       </c>
       <c r="O91" s="2"/>
       <c r="P91" t="s" s="2">
@@ -13082,7 +13108,7 @@
       </c>
       <c r="Q91" s="2"/>
       <c r="R91" t="s" s="2">
-        <v>277</v>
+        <v>161</v>
       </c>
       <c r="S91" t="s" s="2">
         <v>80</v>
@@ -13124,7 +13150,7 @@
         <v>80</v>
       </c>
       <c r="AF91" t="s" s="2">
-        <v>287</v>
+        <v>171</v>
       </c>
       <c r="AG91" t="s" s="2">
         <v>90</v>
@@ -13162,10 +13188,10 @@
     </row>
     <row r="92" hidden="true">
       <c r="A92" t="s" s="2">
-        <v>372</v>
+        <v>377</v>
       </c>
       <c r="B92" t="s" s="2">
-        <v>289</v>
+        <v>378</v>
       </c>
       <c r="C92" s="2"/>
       <c r="D92" t="s" s="2">
@@ -13191,10 +13217,10 @@
         <v>110</v>
       </c>
       <c r="L92" t="s" s="2">
-        <v>290</v>
+        <v>174</v>
       </c>
       <c r="M92" t="s" s="2">
-        <v>291</v>
+        <v>175</v>
       </c>
       <c r="N92" s="2"/>
       <c r="O92" s="2"/>
@@ -13206,7 +13232,7 @@
         <v>80</v>
       </c>
       <c r="S92" t="s" s="2">
-        <v>373</v>
+        <v>379</v>
       </c>
       <c r="T92" t="s" s="2">
         <v>80</v>
@@ -13225,7 +13251,7 @@
       </c>
       <c r="Y92" s="2"/>
       <c r="Z92" t="s" s="2">
-        <v>293</v>
+        <v>178</v>
       </c>
       <c r="AA92" t="s" s="2">
         <v>80</v>
@@ -13243,7 +13269,7 @@
         <v>80</v>
       </c>
       <c r="AF92" t="s" s="2">
-        <v>294</v>
+        <v>179</v>
       </c>
       <c r="AG92" t="s" s="2">
         <v>81</v>
@@ -13281,13 +13307,13 @@
     </row>
     <row r="93" hidden="true">
       <c r="A93" t="s" s="2">
-        <v>374</v>
+        <v>380</v>
       </c>
       <c r="B93" t="s" s="2">
-        <v>272</v>
+        <v>369</v>
       </c>
       <c r="C93" t="s" s="2">
-        <v>296</v>
+        <v>181</v>
       </c>
       <c r="D93" t="s" s="2">
         <v>80</v>
@@ -13309,13 +13335,13 @@
         <v>80</v>
       </c>
       <c r="K93" t="s" s="2">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="L93" t="s" s="2">
-        <v>297</v>
+        <v>182</v>
       </c>
       <c r="M93" t="s" s="2">
-        <v>275</v>
+        <v>137</v>
       </c>
       <c r="N93" s="2"/>
       <c r="O93" s="2"/>
@@ -13366,7 +13392,7 @@
         <v>80</v>
       </c>
       <c r="AF93" t="s" s="2">
-        <v>263</v>
+        <v>159</v>
       </c>
       <c r="AG93" t="s" s="2">
         <v>81</v>
@@ -13404,10 +13430,10 @@
     </row>
     <row r="94" hidden="true">
       <c r="A94" t="s" s="2">
-        <v>375</v>
+        <v>381</v>
       </c>
       <c r="B94" t="s" s="2">
-        <v>279</v>
+        <v>372</v>
       </c>
       <c r="C94" s="2"/>
       <c r="D94" t="s" s="2">
@@ -13430,13 +13456,13 @@
         <v>80</v>
       </c>
       <c r="K94" t="s" s="2">
-        <v>253</v>
+        <v>150</v>
       </c>
       <c r="L94" t="s" s="2">
-        <v>254</v>
+        <v>151</v>
       </c>
       <c r="M94" t="s" s="2">
-        <v>255</v>
+        <v>152</v>
       </c>
       <c r="N94" s="2"/>
       <c r="O94" s="2"/>
@@ -13487,7 +13513,7 @@
         <v>80</v>
       </c>
       <c r="AF94" t="s" s="2">
-        <v>256</v>
+        <v>153</v>
       </c>
       <c r="AG94" t="s" s="2">
         <v>81</v>
@@ -13505,7 +13531,7 @@
         <v>80</v>
       </c>
       <c r="AL94" t="s" s="2">
-        <v>257</v>
+        <v>154</v>
       </c>
       <c r="AM94" t="s" s="2">
         <v>80</v>
@@ -13525,10 +13551,10 @@
     </row>
     <row r="95" hidden="true">
       <c r="A95" t="s" s="2">
-        <v>376</v>
+        <v>382</v>
       </c>
       <c r="B95" t="s" s="2">
-        <v>281</v>
+        <v>374</v>
       </c>
       <c r="C95" s="2"/>
       <c r="D95" t="s" s="2">
@@ -13551,13 +13577,13 @@
         <v>80</v>
       </c>
       <c r="K95" t="s" s="2">
+        <v>135</v>
+      </c>
+      <c r="L95" t="s" s="2">
         <v>136</v>
       </c>
-      <c r="L95" t="s" s="2">
-        <v>274</v>
-      </c>
       <c r="M95" t="s" s="2">
-        <v>275</v>
+        <v>137</v>
       </c>
       <c r="N95" s="2"/>
       <c r="O95" s="2"/>
@@ -13596,19 +13622,19 @@
         <v>80</v>
       </c>
       <c r="AB95" t="s" s="2">
-        <v>260</v>
+        <v>138</v>
       </c>
       <c r="AC95" t="s" s="2">
-        <v>261</v>
+        <v>158</v>
       </c>
       <c r="AD95" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AE95" t="s" s="2">
-        <v>262</v>
+        <v>139</v>
       </c>
       <c r="AF95" t="s" s="2">
-        <v>263</v>
+        <v>159</v>
       </c>
       <c r="AG95" t="s" s="2">
         <v>81</v>
@@ -13646,10 +13672,10 @@
     </row>
     <row r="96" hidden="true">
       <c r="A96" t="s" s="2">
-        <v>377</v>
+        <v>383</v>
       </c>
       <c r="B96" t="s" s="2">
-        <v>283</v>
+        <v>376</v>
       </c>
       <c r="C96" s="2"/>
       <c r="D96" t="s" s="2">
@@ -13675,13 +13701,13 @@
         <v>104</v>
       </c>
       <c r="L96" t="s" s="2">
-        <v>284</v>
+        <v>168</v>
       </c>
       <c r="M96" t="s" s="2">
-        <v>285</v>
+        <v>169</v>
       </c>
       <c r="N96" t="s" s="2">
-        <v>286</v>
+        <v>170</v>
       </c>
       <c r="O96" s="2"/>
       <c r="P96" t="s" s="2">
@@ -13689,7 +13715,7 @@
       </c>
       <c r="Q96" s="2"/>
       <c r="R96" t="s" s="2">
-        <v>296</v>
+        <v>181</v>
       </c>
       <c r="S96" t="s" s="2">
         <v>80</v>
@@ -13731,7 +13757,7 @@
         <v>80</v>
       </c>
       <c r="AF96" t="s" s="2">
-        <v>287</v>
+        <v>171</v>
       </c>
       <c r="AG96" t="s" s="2">
         <v>90</v>
@@ -13769,10 +13795,10 @@
     </row>
     <row r="97" hidden="true">
       <c r="A97" t="s" s="2">
+        <v>384</v>
+      </c>
+      <c r="B97" t="s" s="2">
         <v>378</v>
-      </c>
-      <c r="B97" t="s" s="2">
-        <v>289</v>
       </c>
       <c r="C97" s="2"/>
       <c r="D97" t="s" s="2">
@@ -13795,13 +13821,13 @@
         <v>80</v>
       </c>
       <c r="K97" t="s" s="2">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="L97" t="s" s="2">
-        <v>290</v>
+        <v>174</v>
       </c>
       <c r="M97" t="s" s="2">
-        <v>291</v>
+        <v>175</v>
       </c>
       <c r="N97" s="2"/>
       <c r="O97" s="2"/>
@@ -13852,7 +13878,7 @@
         <v>80</v>
       </c>
       <c r="AF97" t="s" s="2">
-        <v>294</v>
+        <v>179</v>
       </c>
       <c r="AG97" t="s" s="2">
         <v>81</v>
@@ -13890,13 +13916,13 @@
     </row>
     <row r="98" hidden="true">
       <c r="A98" t="s" s="2">
-        <v>379</v>
+        <v>385</v>
       </c>
       <c r="B98" t="s" s="2">
-        <v>272</v>
+        <v>369</v>
       </c>
       <c r="C98" t="s" s="2">
-        <v>303</v>
+        <v>189</v>
       </c>
       <c r="D98" t="s" s="2">
         <v>80</v>
@@ -13918,13 +13944,13 @@
         <v>80</v>
       </c>
       <c r="K98" t="s" s="2">
+        <v>135</v>
+      </c>
+      <c r="L98" t="s" s="2">
         <v>136</v>
       </c>
-      <c r="L98" t="s" s="2">
-        <v>304</v>
-      </c>
       <c r="M98" t="s" s="2">
-        <v>275</v>
+        <v>137</v>
       </c>
       <c r="N98" s="2"/>
       <c r="O98" s="2"/>
@@ -13975,7 +14001,7 @@
         <v>80</v>
       </c>
       <c r="AF98" t="s" s="2">
-        <v>263</v>
+        <v>159</v>
       </c>
       <c r="AG98" t="s" s="2">
         <v>81</v>
@@ -14013,10 +14039,10 @@
     </row>
     <row r="99" hidden="true">
       <c r="A99" t="s" s="2">
-        <v>380</v>
+        <v>386</v>
       </c>
       <c r="B99" t="s" s="2">
-        <v>279</v>
+        <v>372</v>
       </c>
       <c r="C99" s="2"/>
       <c r="D99" t="s" s="2">
@@ -14039,13 +14065,13 @@
         <v>80</v>
       </c>
       <c r="K99" t="s" s="2">
-        <v>253</v>
+        <v>150</v>
       </c>
       <c r="L99" t="s" s="2">
-        <v>254</v>
+        <v>151</v>
       </c>
       <c r="M99" t="s" s="2">
-        <v>255</v>
+        <v>152</v>
       </c>
       <c r="N99" s="2"/>
       <c r="O99" s="2"/>
@@ -14096,7 +14122,7 @@
         <v>80</v>
       </c>
       <c r="AF99" t="s" s="2">
-        <v>256</v>
+        <v>153</v>
       </c>
       <c r="AG99" t="s" s="2">
         <v>81</v>
@@ -14114,7 +14140,7 @@
         <v>80</v>
       </c>
       <c r="AL99" t="s" s="2">
-        <v>257</v>
+        <v>154</v>
       </c>
       <c r="AM99" t="s" s="2">
         <v>80</v>
@@ -14134,10 +14160,10 @@
     </row>
     <row r="100" hidden="true">
       <c r="A100" t="s" s="2">
-        <v>381</v>
+        <v>387</v>
       </c>
       <c r="B100" t="s" s="2">
-        <v>281</v>
+        <v>374</v>
       </c>
       <c r="C100" s="2"/>
       <c r="D100" t="s" s="2">
@@ -14160,13 +14186,13 @@
         <v>80</v>
       </c>
       <c r="K100" t="s" s="2">
+        <v>135</v>
+      </c>
+      <c r="L100" t="s" s="2">
         <v>136</v>
       </c>
-      <c r="L100" t="s" s="2">
-        <v>274</v>
-      </c>
       <c r="M100" t="s" s="2">
-        <v>275</v>
+        <v>137</v>
       </c>
       <c r="N100" s="2"/>
       <c r="O100" s="2"/>
@@ -14205,19 +14231,19 @@
         <v>80</v>
       </c>
       <c r="AB100" t="s" s="2">
-        <v>260</v>
+        <v>138</v>
       </c>
       <c r="AC100" t="s" s="2">
-        <v>261</v>
+        <v>158</v>
       </c>
       <c r="AD100" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AE100" t="s" s="2">
-        <v>262</v>
+        <v>139</v>
       </c>
       <c r="AF100" t="s" s="2">
-        <v>263</v>
+        <v>159</v>
       </c>
       <c r="AG100" t="s" s="2">
         <v>81</v>
@@ -14255,10 +14281,10 @@
     </row>
     <row r="101" hidden="true">
       <c r="A101" t="s" s="2">
-        <v>382</v>
+        <v>388</v>
       </c>
       <c r="B101" t="s" s="2">
-        <v>283</v>
+        <v>376</v>
       </c>
       <c r="C101" s="2"/>
       <c r="D101" t="s" s="2">
@@ -14284,13 +14310,13 @@
         <v>104</v>
       </c>
       <c r="L101" t="s" s="2">
-        <v>284</v>
+        <v>168</v>
       </c>
       <c r="M101" t="s" s="2">
-        <v>285</v>
+        <v>169</v>
       </c>
       <c r="N101" t="s" s="2">
-        <v>286</v>
+        <v>170</v>
       </c>
       <c r="O101" s="2"/>
       <c r="P101" t="s" s="2">
@@ -14298,7 +14324,7 @@
       </c>
       <c r="Q101" s="2"/>
       <c r="R101" t="s" s="2">
-        <v>303</v>
+        <v>189</v>
       </c>
       <c r="S101" t="s" s="2">
         <v>80</v>
@@ -14340,7 +14366,7 @@
         <v>80</v>
       </c>
       <c r="AF101" t="s" s="2">
-        <v>287</v>
+        <v>171</v>
       </c>
       <c r="AG101" t="s" s="2">
         <v>90</v>
@@ -14378,10 +14404,10 @@
     </row>
     <row r="102" hidden="true">
       <c r="A102" t="s" s="2">
-        <v>383</v>
+        <v>389</v>
       </c>
       <c r="B102" t="s" s="2">
-        <v>289</v>
+        <v>378</v>
       </c>
       <c r="C102" s="2"/>
       <c r="D102" t="s" s="2">
@@ -14404,13 +14430,13 @@
         <v>80</v>
       </c>
       <c r="K102" t="s" s="2">
-        <v>309</v>
+        <v>390</v>
       </c>
       <c r="L102" t="s" s="2">
-        <v>290</v>
+        <v>174</v>
       </c>
       <c r="M102" t="s" s="2">
-        <v>291</v>
+        <v>175</v>
       </c>
       <c r="N102" s="2"/>
       <c r="O102" s="2"/>
@@ -14461,7 +14487,7 @@
         <v>80</v>
       </c>
       <c r="AF102" t="s" s="2">
-        <v>294</v>
+        <v>179</v>
       </c>
       <c r="AG102" t="s" s="2">
         <v>81</v>
@@ -14499,10 +14525,10 @@
     </row>
     <row r="103" hidden="true">
       <c r="A103" t="s" s="2">
-        <v>384</v>
+        <v>391</v>
       </c>
       <c r="B103" t="s" s="2">
-        <v>311</v>
+        <v>392</v>
       </c>
       <c r="C103" s="2"/>
       <c r="D103" t="s" s="2">
@@ -14528,13 +14554,13 @@
         <v>104</v>
       </c>
       <c r="L103" t="s" s="2">
-        <v>284</v>
+        <v>168</v>
       </c>
       <c r="M103" t="s" s="2">
-        <v>285</v>
+        <v>169</v>
       </c>
       <c r="N103" t="s" s="2">
-        <v>286</v>
+        <v>170</v>
       </c>
       <c r="O103" s="2"/>
       <c r="P103" t="s" s="2">
@@ -14542,7 +14568,7 @@
       </c>
       <c r="Q103" s="2"/>
       <c r="R103" t="s" s="2">
-        <v>312</v>
+        <v>197</v>
       </c>
       <c r="S103" t="s" s="2">
         <v>80</v>
@@ -14584,7 +14610,7 @@
         <v>80</v>
       </c>
       <c r="AF103" t="s" s="2">
-        <v>287</v>
+        <v>171</v>
       </c>
       <c r="AG103" t="s" s="2">
         <v>90</v>
@@ -14622,10 +14648,10 @@
     </row>
     <row r="104" hidden="true">
       <c r="A104" t="s" s="2">
-        <v>385</v>
+        <v>393</v>
       </c>
       <c r="B104" t="s" s="2">
-        <v>314</v>
+        <v>394</v>
       </c>
       <c r="C104" s="2"/>
       <c r="D104" t="s" s="2">
@@ -14648,13 +14674,13 @@
         <v>80</v>
       </c>
       <c r="K104" t="s" s="2">
-        <v>315</v>
+        <v>200</v>
       </c>
       <c r="L104" t="s" s="2">
-        <v>290</v>
+        <v>174</v>
       </c>
       <c r="M104" t="s" s="2">
-        <v>291</v>
+        <v>175</v>
       </c>
       <c r="N104" s="2"/>
       <c r="O104" s="2"/>
@@ -14705,7 +14731,7 @@
         <v>80</v>
       </c>
       <c r="AF104" t="s" s="2">
-        <v>294</v>
+        <v>179</v>
       </c>
       <c r="AG104" t="s" s="2">
         <v>81</v>
@@ -14743,10 +14769,10 @@
     </row>
     <row r="105" hidden="true">
       <c r="A105" t="s" s="2">
-        <v>386</v>
+        <v>395</v>
       </c>
       <c r="B105" t="s" s="2">
-        <v>386</v>
+        <v>395</v>
       </c>
       <c r="C105" s="2"/>
       <c r="D105" t="s" s="2">
@@ -14769,16 +14795,16 @@
         <v>91</v>
       </c>
       <c r="K105" t="s" s="2">
-        <v>253</v>
+        <v>150</v>
       </c>
       <c r="L105" t="s" s="2">
-        <v>387</v>
+        <v>396</v>
       </c>
       <c r="M105" t="s" s="2">
-        <v>388</v>
+        <v>397</v>
       </c>
       <c r="N105" t="s" s="2">
-        <v>389</v>
+        <v>398</v>
       </c>
       <c r="O105" s="2"/>
       <c r="P105" t="s" s="2">
@@ -14828,7 +14854,7 @@
         <v>80</v>
       </c>
       <c r="AF105" t="s" s="2">
-        <v>390</v>
+        <v>399</v>
       </c>
       <c r="AG105" t="s" s="2">
         <v>81</v>
@@ -14837,7 +14863,7 @@
         <v>90</v>
       </c>
       <c r="AI105" t="s" s="2">
-        <v>391</v>
+        <v>400</v>
       </c>
       <c r="AJ105" t="s" s="2">
         <v>102</v>
@@ -14866,10 +14892,10 @@
     </row>
     <row r="106" hidden="true">
       <c r="A106" t="s" s="2">
-        <v>392</v>
+        <v>401</v>
       </c>
       <c r="B106" t="s" s="2">
-        <v>392</v>
+        <v>401</v>
       </c>
       <c r="C106" s="2"/>
       <c r="D106" t="s" s="2">
@@ -14895,13 +14921,13 @@
         <v>104</v>
       </c>
       <c r="L106" t="s" s="2">
-        <v>393</v>
+        <v>402</v>
       </c>
       <c r="M106" t="s" s="2">
-        <v>394</v>
+        <v>403</v>
       </c>
       <c r="N106" t="s" s="2">
-        <v>395</v>
+        <v>404</v>
       </c>
       <c r="O106" s="2"/>
       <c r="P106" t="s" s="2">
@@ -14927,13 +14953,13 @@
         <v>80</v>
       </c>
       <c r="X106" t="s" s="2">
-        <v>189</v>
+        <v>296</v>
       </c>
       <c r="Y106" t="s" s="2">
-        <v>396</v>
+        <v>405</v>
       </c>
       <c r="Z106" t="s" s="2">
-        <v>397</v>
+        <v>406</v>
       </c>
       <c r="AA106" t="s" s="2">
         <v>80</v>
@@ -14951,7 +14977,7 @@
         <v>80</v>
       </c>
       <c r="AF106" t="s" s="2">
-        <v>398</v>
+        <v>407</v>
       </c>
       <c r="AG106" t="s" s="2">
         <v>81</v>
@@ -14989,10 +15015,10 @@
     </row>
     <row r="107" hidden="true">
       <c r="A107" t="s" s="2">
-        <v>399</v>
+        <v>408</v>
       </c>
       <c r="B107" t="s" s="2">
-        <v>399</v>
+        <v>408</v>
       </c>
       <c r="C107" s="2"/>
       <c r="D107" t="s" s="2">
@@ -15015,16 +15041,16 @@
         <v>91</v>
       </c>
       <c r="K107" t="s" s="2">
-        <v>148</v>
+        <v>257</v>
       </c>
       <c r="L107" t="s" s="2">
-        <v>400</v>
+        <v>409</v>
       </c>
       <c r="M107" t="s" s="2">
-        <v>401</v>
+        <v>410</v>
       </c>
       <c r="N107" t="s" s="2">
-        <v>402</v>
+        <v>411</v>
       </c>
       <c r="O107" s="2"/>
       <c r="P107" t="s" s="2">
@@ -15074,7 +15100,7 @@
         <v>80</v>
       </c>
       <c r="AF107" t="s" s="2">
-        <v>403</v>
+        <v>412</v>
       </c>
       <c r="AG107" t="s" s="2">
         <v>81</v>
@@ -15092,7 +15118,7 @@
         <v>80</v>
       </c>
       <c r="AL107" t="s" s="2">
-        <v>404</v>
+        <v>413</v>
       </c>
       <c r="AM107" t="s" s="2">
         <v>80</v>
@@ -15112,10 +15138,10 @@
     </row>
     <row r="108" hidden="true">
       <c r="A108" t="s" s="2">
-        <v>405</v>
+        <v>414</v>
       </c>
       <c r="B108" t="s" s="2">
-        <v>405</v>
+        <v>414</v>
       </c>
       <c r="C108" s="2"/>
       <c r="D108" t="s" s="2">
@@ -15138,16 +15164,16 @@
         <v>91</v>
       </c>
       <c r="K108" t="s" s="2">
-        <v>253</v>
+        <v>150</v>
       </c>
       <c r="L108" t="s" s="2">
-        <v>406</v>
+        <v>415</v>
       </c>
       <c r="M108" t="s" s="2">
-        <v>407</v>
+        <v>416</v>
       </c>
       <c r="N108" t="s" s="2">
-        <v>408</v>
+        <v>417</v>
       </c>
       <c r="O108" s="2"/>
       <c r="P108" t="s" s="2">
@@ -15197,7 +15223,7 @@
         <v>80</v>
       </c>
       <c r="AF108" t="s" s="2">
-        <v>409</v>
+        <v>418</v>
       </c>
       <c r="AG108" t="s" s="2">
         <v>81</v>
@@ -15235,10 +15261,10 @@
     </row>
     <row r="109">
       <c r="A109" t="s" s="2">
-        <v>410</v>
+        <v>419</v>
       </c>
       <c r="B109" t="s" s="2">
-        <v>410</v>
+        <v>419</v>
       </c>
       <c r="C109" s="2"/>
       <c r="D109" t="s" s="2">
@@ -15261,16 +15287,16 @@
         <v>91</v>
       </c>
       <c r="K109" t="s" s="2">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="L109" t="s" s="2">
-        <v>411</v>
+        <v>420</v>
       </c>
       <c r="M109" t="s" s="2">
-        <v>412</v>
+        <v>421</v>
       </c>
       <c r="N109" t="s" s="2">
-        <v>413</v>
+        <v>422</v>
       </c>
       <c r="O109" s="2"/>
       <c r="P109" t="s" s="2">
@@ -15296,13 +15322,13 @@
         <v>80</v>
       </c>
       <c r="X109" t="s" s="2">
-        <v>197</v>
+        <v>304</v>
       </c>
       <c r="Y109" t="s" s="2">
-        <v>414</v>
+        <v>423</v>
       </c>
       <c r="Z109" t="s" s="2">
-        <v>415</v>
+        <v>424</v>
       </c>
       <c r="AA109" t="s" s="2">
         <v>80</v>
@@ -15320,7 +15346,7 @@
         <v>80</v>
       </c>
       <c r="AF109" t="s" s="2">
-        <v>410</v>
+        <v>419</v>
       </c>
       <c r="AG109" t="s" s="2">
         <v>81</v>
@@ -15335,13 +15361,13 @@
         <v>102</v>
       </c>
       <c r="AK109" t="s" s="2">
-        <v>416</v>
+        <v>425</v>
       </c>
       <c r="AL109" t="s" s="2">
-        <v>417</v>
+        <v>426</v>
       </c>
       <c r="AM109" t="s" s="2">
-        <v>418</v>
+        <v>427</v>
       </c>
       <c r="AN109" t="s" s="2">
         <v>80</v>
@@ -15358,10 +15384,10 @@
     </row>
     <row r="110" hidden="true">
       <c r="A110" t="s" s="2">
-        <v>419</v>
+        <v>428</v>
       </c>
       <c r="B110" t="s" s="2">
-        <v>419</v>
+        <v>428</v>
       </c>
       <c r="C110" s="2"/>
       <c r="D110" t="s" s="2">
@@ -15384,16 +15410,16 @@
         <v>91</v>
       </c>
       <c r="K110" t="s" s="2">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="L110" t="s" s="2">
-        <v>420</v>
+        <v>429</v>
       </c>
       <c r="M110" t="s" s="2">
-        <v>421</v>
+        <v>430</v>
       </c>
       <c r="N110" t="s" s="2">
-        <v>422</v>
+        <v>431</v>
       </c>
       <c r="O110" s="2"/>
       <c r="P110" t="s" s="2">
@@ -15419,13 +15445,13 @@
         <v>80</v>
       </c>
       <c r="X110" t="s" s="2">
-        <v>197</v>
+        <v>304</v>
       </c>
       <c r="Y110" t="s" s="2">
-        <v>423</v>
+        <v>432</v>
       </c>
       <c r="Z110" t="s" s="2">
-        <v>424</v>
+        <v>433</v>
       </c>
       <c r="AA110" t="s" s="2">
         <v>80</v>
@@ -15443,7 +15469,7 @@
         <v>80</v>
       </c>
       <c r="AF110" t="s" s="2">
-        <v>419</v>
+        <v>428</v>
       </c>
       <c r="AG110" t="s" s="2">
         <v>81</v>
@@ -15461,7 +15487,7 @@
         <v>80</v>
       </c>
       <c r="AL110" t="s" s="2">
-        <v>425</v>
+        <v>434</v>
       </c>
       <c r="AM110" t="s" s="2">
         <v>80</v>
@@ -15473,18 +15499,18 @@
         <v>80</v>
       </c>
       <c r="AP110" t="s" s="2">
-        <v>426</v>
+        <v>435</v>
       </c>
       <c r="AQ110" t="s" s="2">
-        <v>427</v>
+        <v>436</v>
       </c>
     </row>
     <row r="111" hidden="true">
       <c r="A111" t="s" s="2">
-        <v>428</v>
+        <v>437</v>
       </c>
       <c r="B111" t="s" s="2">
-        <v>428</v>
+        <v>437</v>
       </c>
       <c r="C111" s="2"/>
       <c r="D111" t="s" s="2">
@@ -15507,13 +15533,13 @@
         <v>91</v>
       </c>
       <c r="K111" t="s" s="2">
-        <v>253</v>
+        <v>150</v>
       </c>
       <c r="L111" t="s" s="2">
-        <v>429</v>
+        <v>438</v>
       </c>
       <c r="M111" t="s" s="2">
-        <v>430</v>
+        <v>439</v>
       </c>
       <c r="N111" s="2"/>
       <c r="O111" s="2"/>
@@ -15564,7 +15590,7 @@
         <v>80</v>
       </c>
       <c r="AF111" t="s" s="2">
-        <v>428</v>
+        <v>437</v>
       </c>
       <c r="AG111" t="s" s="2">
         <v>81</v>
@@ -15582,13 +15608,13 @@
         <v>80</v>
       </c>
       <c r="AL111" t="s" s="2">
-        <v>431</v>
+        <v>440</v>
       </c>
       <c r="AM111" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AN111" t="s" s="2">
-        <v>432</v>
+        <v>441</v>
       </c>
       <c r="AO111" t="s" s="2">
         <v>80</v>
@@ -15602,10 +15628,10 @@
     </row>
     <row r="112" hidden="true">
       <c r="A112" t="s" s="2">
-        <v>433</v>
+        <v>442</v>
       </c>
       <c r="B112" t="s" s="2">
-        <v>433</v>
+        <v>442</v>
       </c>
       <c r="C112" s="2"/>
       <c r="D112" t="s" s="2">
@@ -15628,16 +15654,16 @@
         <v>91</v>
       </c>
       <c r="K112" t="s" s="2">
-        <v>434</v>
+        <v>443</v>
       </c>
       <c r="L112" t="s" s="2">
-        <v>435</v>
+        <v>444</v>
       </c>
       <c r="M112" t="s" s="2">
-        <v>436</v>
+        <v>445</v>
       </c>
       <c r="N112" t="s" s="2">
-        <v>437</v>
+        <v>446</v>
       </c>
       <c r="O112" s="2"/>
       <c r="P112" t="s" s="2">
@@ -15687,7 +15713,7 @@
         <v>80</v>
       </c>
       <c r="AF112" t="s" s="2">
-        <v>433</v>
+        <v>442</v>
       </c>
       <c r="AG112" t="s" s="2">
         <v>81</v>
@@ -15705,7 +15731,7 @@
         <v>80</v>
       </c>
       <c r="AL112" t="s" s="2">
-        <v>438</v>
+        <v>447</v>
       </c>
       <c r="AM112" t="s" s="2">
         <v>80</v>
@@ -15717,18 +15743,18 @@
         <v>80</v>
       </c>
       <c r="AP112" t="s" s="2">
-        <v>439</v>
+        <v>448</v>
       </c>
       <c r="AQ112" t="s" s="2">
-        <v>440</v>
+        <v>449</v>
       </c>
     </row>
     <row r="113" hidden="true">
       <c r="A113" t="s" s="2">
-        <v>441</v>
+        <v>450</v>
       </c>
       <c r="B113" t="s" s="2">
-        <v>441</v>
+        <v>450</v>
       </c>
       <c r="C113" s="2"/>
       <c r="D113" t="s" s="2">
@@ -15751,13 +15777,13 @@
         <v>91</v>
       </c>
       <c r="K113" t="s" s="2">
-        <v>442</v>
+        <v>451</v>
       </c>
       <c r="L113" t="s" s="2">
-        <v>443</v>
+        <v>452</v>
       </c>
       <c r="M113" t="s" s="2">
-        <v>444</v>
+        <v>453</v>
       </c>
       <c r="N113" s="2"/>
       <c r="O113" s="2"/>
@@ -15808,7 +15834,7 @@
         <v>80</v>
       </c>
       <c r="AF113" t="s" s="2">
-        <v>441</v>
+        <v>450</v>
       </c>
       <c r="AG113" t="s" s="2">
         <v>81</v>
@@ -15826,13 +15852,13 @@
         <v>80</v>
       </c>
       <c r="AL113" t="s" s="2">
-        <v>445</v>
+        <v>454</v>
       </c>
       <c r="AM113" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AN113" t="s" s="2">
-        <v>446</v>
+        <v>455</v>
       </c>
       <c r="AO113" t="s" s="2">
         <v>80</v>
@@ -15846,10 +15872,10 @@
     </row>
     <row r="114" hidden="true">
       <c r="A114" t="s" s="2">
-        <v>447</v>
+        <v>456</v>
       </c>
       <c r="B114" t="s" s="2">
-        <v>447</v>
+        <v>456</v>
       </c>
       <c r="C114" s="2"/>
       <c r="D114" t="s" s="2">
@@ -15872,13 +15898,13 @@
         <v>91</v>
       </c>
       <c r="K114" t="s" s="2">
-        <v>442</v>
+        <v>451</v>
       </c>
       <c r="L114" t="s" s="2">
-        <v>448</v>
+        <v>457</v>
       </c>
       <c r="M114" t="s" s="2">
-        <v>449</v>
+        <v>458</v>
       </c>
       <c r="N114" s="2"/>
       <c r="O114" s="2"/>
@@ -15929,7 +15955,7 @@
         <v>80</v>
       </c>
       <c r="AF114" t="s" s="2">
-        <v>447</v>
+        <v>456</v>
       </c>
       <c r="AG114" t="s" s="2">
         <v>81</v>
@@ -15947,13 +15973,13 @@
         <v>80</v>
       </c>
       <c r="AL114" t="s" s="2">
-        <v>445</v>
+        <v>454</v>
       </c>
       <c r="AM114" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AN114" t="s" s="2">
-        <v>450</v>
+        <v>459</v>
       </c>
       <c r="AO114" t="s" s="2">
         <v>80</v>
@@ -15967,10 +15993,10 @@
     </row>
     <row r="115" hidden="true">
       <c r="A115" t="s" s="2">
-        <v>451</v>
+        <v>460</v>
       </c>
       <c r="B115" t="s" s="2">
-        <v>451</v>
+        <v>460</v>
       </c>
       <c r="C115" s="2"/>
       <c r="D115" t="s" s="2">
@@ -15993,16 +16019,16 @@
         <v>91</v>
       </c>
       <c r="K115" t="s" s="2">
-        <v>442</v>
+        <v>451</v>
       </c>
       <c r="L115" t="s" s="2">
-        <v>452</v>
+        <v>461</v>
       </c>
       <c r="M115" t="s" s="2">
-        <v>453</v>
+        <v>462</v>
       </c>
       <c r="N115" t="s" s="2">
-        <v>454</v>
+        <v>463</v>
       </c>
       <c r="O115" s="2"/>
       <c r="P115" t="s" s="2">
@@ -16052,7 +16078,7 @@
         <v>80</v>
       </c>
       <c r="AF115" t="s" s="2">
-        <v>451</v>
+        <v>460</v>
       </c>
       <c r="AG115" t="s" s="2">
         <v>81</v>
@@ -16070,7 +16096,7 @@
         <v>80</v>
       </c>
       <c r="AL115" t="s" s="2">
-        <v>445</v>
+        <v>454</v>
       </c>
       <c r="AM115" t="s" s="2">
         <v>80</v>
@@ -16090,10 +16116,10 @@
     </row>
     <row r="116" hidden="true">
       <c r="A116" t="s" s="2">
-        <v>455</v>
+        <v>464</v>
       </c>
       <c r="B116" t="s" s="2">
-        <v>455</v>
+        <v>464</v>
       </c>
       <c r="C116" s="2"/>
       <c r="D116" t="s" s="2">
@@ -16116,16 +16142,16 @@
         <v>91</v>
       </c>
       <c r="K116" t="s" s="2">
-        <v>456</v>
+        <v>465</v>
       </c>
       <c r="L116" t="s" s="2">
-        <v>457</v>
+        <v>466</v>
       </c>
       <c r="M116" t="s" s="2">
-        <v>458</v>
+        <v>467</v>
       </c>
       <c r="N116" t="s" s="2">
-        <v>459</v>
+        <v>468</v>
       </c>
       <c r="O116" s="2"/>
       <c r="P116" t="s" s="2">
@@ -16175,7 +16201,7 @@
         <v>80</v>
       </c>
       <c r="AF116" t="s" s="2">
-        <v>455</v>
+        <v>464</v>
       </c>
       <c r="AG116" t="s" s="2">
         <v>81</v>
@@ -16193,13 +16219,13 @@
         <v>80</v>
       </c>
       <c r="AL116" t="s" s="2">
-        <v>445</v>
+        <v>454</v>
       </c>
       <c r="AM116" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AN116" t="s" s="2">
-        <v>460</v>
+        <v>469</v>
       </c>
       <c r="AO116" t="s" s="2">
         <v>80</v>
@@ -16213,10 +16239,10 @@
     </row>
     <row r="117">
       <c r="A117" t="s" s="2">
-        <v>461</v>
+        <v>470</v>
       </c>
       <c r="B117" t="s" s="2">
-        <v>461</v>
+        <v>470</v>
       </c>
       <c r="C117" s="2"/>
       <c r="D117" t="s" s="2">
@@ -16239,16 +16265,16 @@
         <v>91</v>
       </c>
       <c r="K117" t="s" s="2">
-        <v>462</v>
+        <v>471</v>
       </c>
       <c r="L117" t="s" s="2">
-        <v>463</v>
+        <v>472</v>
       </c>
       <c r="M117" t="s" s="2">
-        <v>464</v>
+        <v>473</v>
       </c>
       <c r="N117" t="s" s="2">
-        <v>465</v>
+        <v>474</v>
       </c>
       <c r="O117" s="2"/>
       <c r="P117" t="s" s="2">
@@ -16298,7 +16324,7 @@
         <v>80</v>
       </c>
       <c r="AF117" t="s" s="2">
-        <v>461</v>
+        <v>470</v>
       </c>
       <c r="AG117" t="s" s="2">
         <v>90</v>
@@ -16316,7 +16342,7 @@
         <v>80</v>
       </c>
       <c r="AL117" t="s" s="2">
-        <v>466</v>
+        <v>475</v>
       </c>
       <c r="AM117" t="s" s="2">
         <v>80</v>
@@ -16336,10 +16362,10 @@
     </row>
     <row r="118" hidden="true">
       <c r="A118" t="s" s="2">
-        <v>467</v>
+        <v>476</v>
       </c>
       <c r="B118" t="s" s="2">
-        <v>467</v>
+        <v>476</v>
       </c>
       <c r="C118" s="2"/>
       <c r="D118" t="s" s="2">
@@ -16362,13 +16388,13 @@
         <v>80</v>
       </c>
       <c r="K118" t="s" s="2">
-        <v>253</v>
+        <v>150</v>
       </c>
       <c r="L118" t="s" s="2">
-        <v>254</v>
+        <v>151</v>
       </c>
       <c r="M118" t="s" s="2">
-        <v>255</v>
+        <v>152</v>
       </c>
       <c r="N118" s="2"/>
       <c r="O118" s="2"/>
@@ -16419,7 +16445,7 @@
         <v>80</v>
       </c>
       <c r="AF118" t="s" s="2">
-        <v>256</v>
+        <v>153</v>
       </c>
       <c r="AG118" t="s" s="2">
         <v>81</v>
@@ -16437,7 +16463,7 @@
         <v>80</v>
       </c>
       <c r="AL118" t="s" s="2">
-        <v>257</v>
+        <v>154</v>
       </c>
       <c r="AM118" t="s" s="2">
         <v>80</v>
@@ -16457,14 +16483,14 @@
     </row>
     <row r="119" hidden="true">
       <c r="A119" t="s" s="2">
-        <v>468</v>
+        <v>477</v>
       </c>
       <c r="B119" t="s" s="2">
-        <v>468</v>
+        <v>477</v>
       </c>
       <c r="C119" s="2"/>
       <c r="D119" t="s" s="2">
-        <v>135</v>
+        <v>250</v>
       </c>
       <c r="E119" s="2"/>
       <c r="F119" t="s" s="2">
@@ -16483,16 +16509,16 @@
         <v>80</v>
       </c>
       <c r="K119" t="s" s="2">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="L119" t="s" s="2">
-        <v>137</v>
+        <v>361</v>
       </c>
       <c r="M119" t="s" s="2">
-        <v>259</v>
+        <v>362</v>
       </c>
       <c r="N119" t="s" s="2">
-        <v>139</v>
+        <v>253</v>
       </c>
       <c r="O119" s="2"/>
       <c r="P119" t="s" s="2">
@@ -16530,19 +16556,19 @@
         <v>80</v>
       </c>
       <c r="AB119" t="s" s="2">
-        <v>260</v>
+        <v>138</v>
       </c>
       <c r="AC119" t="s" s="2">
-        <v>261</v>
+        <v>158</v>
       </c>
       <c r="AD119" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AE119" t="s" s="2">
-        <v>262</v>
+        <v>139</v>
       </c>
       <c r="AF119" t="s" s="2">
-        <v>263</v>
+        <v>159</v>
       </c>
       <c r="AG119" t="s" s="2">
         <v>81</v>
@@ -16560,7 +16586,7 @@
         <v>80</v>
       </c>
       <c r="AL119" t="s" s="2">
-        <v>257</v>
+        <v>154</v>
       </c>
       <c r="AM119" t="s" s="2">
         <v>80</v>
@@ -16580,10 +16606,10 @@
     </row>
     <row r="120">
       <c r="A120" t="s" s="2">
-        <v>469</v>
+        <v>478</v>
       </c>
       <c r="B120" t="s" s="2">
-        <v>469</v>
+        <v>478</v>
       </c>
       <c r="C120" s="2"/>
       <c r="D120" t="s" s="2">
@@ -16609,14 +16635,14 @@
         <v>110</v>
       </c>
       <c r="L120" t="s" s="2">
-        <v>470</v>
+        <v>479</v>
       </c>
       <c r="M120" t="s" s="2">
-        <v>471</v>
+        <v>480</v>
       </c>
       <c r="N120" s="2"/>
       <c r="O120" t="s" s="2">
-        <v>472</v>
+        <v>481</v>
       </c>
       <c r="P120" t="s" s="2">
         <v>80</v>
@@ -16629,7 +16655,7 @@
         <v>80</v>
       </c>
       <c r="T120" t="s" s="2">
-        <v>473</v>
+        <v>482</v>
       </c>
       <c r="U120" t="s" s="2">
         <v>80</v>
@@ -16644,10 +16670,10 @@
         <v>177</v>
       </c>
       <c r="Y120" t="s" s="2">
-        <v>474</v>
+        <v>483</v>
       </c>
       <c r="Z120" t="s" s="2">
-        <v>475</v>
+        <v>484</v>
       </c>
       <c r="AA120" t="s" s="2">
         <v>80</v>
@@ -16665,7 +16691,7 @@
         <v>80</v>
       </c>
       <c r="AF120" t="s" s="2">
-        <v>476</v>
+        <v>485</v>
       </c>
       <c r="AG120" t="s" s="2">
         <v>81</v>
@@ -16683,7 +16709,7 @@
         <v>80</v>
       </c>
       <c r="AL120" t="s" s="2">
-        <v>477</v>
+        <v>486</v>
       </c>
       <c r="AM120" t="s" s="2">
         <v>80</v>
@@ -16692,7 +16718,7 @@
         <v>80</v>
       </c>
       <c r="AO120" t="s" s="2">
-        <v>478</v>
+        <v>487</v>
       </c>
       <c r="AP120" t="s" s="2">
         <v>80</v>
@@ -16703,10 +16729,10 @@
     </row>
     <row r="121">
       <c r="A121" t="s" s="2">
-        <v>479</v>
+        <v>488</v>
       </c>
       <c r="B121" t="s" s="2">
-        <v>479</v>
+        <v>488</v>
       </c>
       <c r="C121" s="2"/>
       <c r="D121" t="s" s="2">
@@ -16732,14 +16758,14 @@
         <v>110</v>
       </c>
       <c r="L121" t="s" s="2">
-        <v>480</v>
+        <v>489</v>
       </c>
       <c r="M121" t="s" s="2">
-        <v>481</v>
+        <v>490</v>
       </c>
       <c r="N121" s="2"/>
       <c r="O121" t="s" s="2">
-        <v>482</v>
+        <v>491</v>
       </c>
       <c r="P121" t="s" s="2">
         <v>80</v>
@@ -16752,7 +16778,7 @@
         <v>80</v>
       </c>
       <c r="T121" t="s" s="2">
-        <v>483</v>
+        <v>492</v>
       </c>
       <c r="U121" t="s" s="2">
         <v>80</v>
@@ -16788,7 +16814,7 @@
         <v>80</v>
       </c>
       <c r="AF121" t="s" s="2">
-        <v>484</v>
+        <v>493</v>
       </c>
       <c r="AG121" t="s" s="2">
         <v>81</v>
@@ -16806,7 +16832,7 @@
         <v>80</v>
       </c>
       <c r="AL121" t="s" s="2">
-        <v>485</v>
+        <v>494</v>
       </c>
       <c r="AM121" t="s" s="2">
         <v>80</v>
@@ -16826,10 +16852,10 @@
     </row>
     <row r="122">
       <c r="A122" t="s" s="2">
-        <v>486</v>
+        <v>495</v>
       </c>
       <c r="B122" t="s" s="2">
-        <v>486</v>
+        <v>495</v>
       </c>
       <c r="C122" s="2"/>
       <c r="D122" t="s" s="2">
@@ -16852,19 +16878,19 @@
         <v>80</v>
       </c>
       <c r="K122" t="s" s="2">
-        <v>487</v>
+        <v>496</v>
       </c>
       <c r="L122" t="s" s="2">
-        <v>488</v>
+        <v>497</v>
       </c>
       <c r="M122" t="s" s="2">
-        <v>489</v>
+        <v>498</v>
       </c>
       <c r="N122" t="s" s="2">
-        <v>490</v>
+        <v>499</v>
       </c>
       <c r="O122" t="s" s="2">
-        <v>491</v>
+        <v>500</v>
       </c>
       <c r="P122" t="s" s="2">
         <v>80</v>
@@ -16913,7 +16939,7 @@
         <v>80</v>
       </c>
       <c r="AF122" t="s" s="2">
-        <v>492</v>
+        <v>501</v>
       </c>
       <c r="AG122" t="s" s="2">
         <v>81</v>
@@ -16931,7 +16957,7 @@
         <v>80</v>
       </c>
       <c r="AL122" t="s" s="2">
-        <v>493</v>
+        <v>502</v>
       </c>
       <c r="AM122" t="s" s="2">
         <v>80</v>
@@ -16940,7 +16966,7 @@
         <v>80</v>
       </c>
       <c r="AO122" t="s" s="2">
-        <v>494</v>
+        <v>503</v>
       </c>
       <c r="AP122" t="s" s="2">
         <v>80</v>
@@ -16951,10 +16977,10 @@
     </row>
     <row r="123" hidden="true">
       <c r="A123" t="s" s="2">
-        <v>495</v>
+        <v>504</v>
       </c>
       <c r="B123" t="s" s="2">
-        <v>495</v>
+        <v>504</v>
       </c>
       <c r="C123" s="2"/>
       <c r="D123" t="s" s="2">
@@ -16977,19 +17003,19 @@
         <v>91</v>
       </c>
       <c r="K123" t="s" s="2">
-        <v>496</v>
+        <v>505</v>
       </c>
       <c r="L123" t="s" s="2">
-        <v>497</v>
+        <v>506</v>
       </c>
       <c r="M123" t="s" s="2">
-        <v>498</v>
+        <v>507</v>
       </c>
       <c r="N123" t="s" s="2">
-        <v>499</v>
+        <v>508</v>
       </c>
       <c r="O123" t="s" s="2">
-        <v>500</v>
+        <v>509</v>
       </c>
       <c r="P123" t="s" s="2">
         <v>80</v>
@@ -17002,7 +17028,7 @@
         <v>80</v>
       </c>
       <c r="T123" t="s" s="2">
-        <v>501</v>
+        <v>510</v>
       </c>
       <c r="U123" t="s" s="2">
         <v>80</v>
@@ -17038,7 +17064,7 @@
         <v>80</v>
       </c>
       <c r="AF123" t="s" s="2">
-        <v>502</v>
+        <v>511</v>
       </c>
       <c r="AG123" t="s" s="2">
         <v>81</v>
@@ -17056,7 +17082,7 @@
         <v>80</v>
       </c>
       <c r="AL123" t="s" s="2">
-        <v>503</v>
+        <v>512</v>
       </c>
       <c r="AM123" t="s" s="2">
         <v>80</v>
@@ -17065,7 +17091,7 @@
         <v>80</v>
       </c>
       <c r="AO123" t="s" s="2">
-        <v>504</v>
+        <v>513</v>
       </c>
       <c r="AP123" t="s" s="2">
         <v>80</v>
@@ -17076,10 +17102,10 @@
     </row>
     <row r="124" hidden="true">
       <c r="A124" t="s" s="2">
-        <v>505</v>
+        <v>514</v>
       </c>
       <c r="B124" t="s" s="2">
-        <v>505</v>
+        <v>514</v>
       </c>
       <c r="C124" s="2"/>
       <c r="D124" t="s" s="2">
@@ -17102,19 +17128,19 @@
         <v>91</v>
       </c>
       <c r="K124" t="s" s="2">
-        <v>506</v>
+        <v>515</v>
       </c>
       <c r="L124" t="s" s="2">
-        <v>507</v>
+        <v>516</v>
       </c>
       <c r="M124" t="s" s="2">
-        <v>508</v>
+        <v>517</v>
       </c>
       <c r="N124" t="s" s="2">
-        <v>509</v>
+        <v>518</v>
       </c>
       <c r="O124" t="s" s="2">
-        <v>510</v>
+        <v>519</v>
       </c>
       <c r="P124" t="s" s="2">
         <v>80</v>
@@ -17163,7 +17189,7 @@
         <v>80</v>
       </c>
       <c r="AF124" t="s" s="2">
-        <v>511</v>
+        <v>520</v>
       </c>
       <c r="AG124" t="s" s="2">
         <v>81</v>
@@ -17181,7 +17207,7 @@
         <v>80</v>
       </c>
       <c r="AL124" t="s" s="2">
-        <v>512</v>
+        <v>521</v>
       </c>
       <c r="AM124" t="s" s="2">
         <v>80</v>
@@ -17201,10 +17227,10 @@
     </row>
     <row r="125" hidden="true">
       <c r="A125" t="s" s="2">
-        <v>513</v>
+        <v>522</v>
       </c>
       <c r="B125" t="s" s="2">
-        <v>513</v>
+        <v>522</v>
       </c>
       <c r="C125" s="2"/>
       <c r="D125" t="s" s="2">
@@ -17227,19 +17253,19 @@
         <v>91</v>
       </c>
       <c r="K125" t="s" s="2">
-        <v>487</v>
+        <v>496</v>
       </c>
       <c r="L125" t="s" s="2">
-        <v>514</v>
+        <v>523</v>
       </c>
       <c r="M125" t="s" s="2">
-        <v>515</v>
+        <v>524</v>
       </c>
       <c r="N125" t="s" s="2">
-        <v>516</v>
+        <v>525</v>
       </c>
       <c r="O125" t="s" s="2">
-        <v>517</v>
+        <v>526</v>
       </c>
       <c r="P125" t="s" s="2">
         <v>80</v>
@@ -17288,7 +17314,7 @@
         <v>80</v>
       </c>
       <c r="AF125" t="s" s="2">
-        <v>518</v>
+        <v>527</v>
       </c>
       <c r="AG125" t="s" s="2">
         <v>81</v>
@@ -17306,7 +17332,7 @@
         <v>80</v>
       </c>
       <c r="AL125" t="s" s="2">
-        <v>519</v>
+        <v>528</v>
       </c>
       <c r="AM125" t="s" s="2">
         <v>80</v>
@@ -17326,10 +17352,10 @@
     </row>
     <row r="126" hidden="true">
       <c r="A126" t="s" s="2">
-        <v>520</v>
+        <v>529</v>
       </c>
       <c r="B126" t="s" s="2">
-        <v>520</v>
+        <v>529</v>
       </c>
       <c r="C126" s="2"/>
       <c r="D126" t="s" s="2">
@@ -17352,17 +17378,17 @@
         <v>91</v>
       </c>
       <c r="K126" t="s" s="2">
-        <v>253</v>
+        <v>150</v>
       </c>
       <c r="L126" t="s" s="2">
-        <v>521</v>
+        <v>530</v>
       </c>
       <c r="M126" t="s" s="2">
-        <v>522</v>
+        <v>531</v>
       </c>
       <c r="N126" s="2"/>
       <c r="O126" t="s" s="2">
-        <v>523</v>
+        <v>532</v>
       </c>
       <c r="P126" t="s" s="2">
         <v>80</v>
@@ -17375,7 +17401,7 @@
         <v>80</v>
       </c>
       <c r="T126" t="s" s="2">
-        <v>524</v>
+        <v>533</v>
       </c>
       <c r="U126" t="s" s="2">
         <v>80</v>
@@ -17411,7 +17437,7 @@
         <v>80</v>
       </c>
       <c r="AF126" t="s" s="2">
-        <v>525</v>
+        <v>534</v>
       </c>
       <c r="AG126" t="s" s="2">
         <v>81</v>
@@ -17429,7 +17455,7 @@
         <v>80</v>
       </c>
       <c r="AL126" t="s" s="2">
-        <v>526</v>
+        <v>535</v>
       </c>
       <c r="AM126" t="s" s="2">
         <v>80</v>
@@ -17449,10 +17475,10 @@
     </row>
     <row r="127" hidden="true">
       <c r="A127" t="s" s="2">
-        <v>527</v>
+        <v>536</v>
       </c>
       <c r="B127" t="s" s="2">
-        <v>527</v>
+        <v>536</v>
       </c>
       <c r="C127" s="2"/>
       <c r="D127" t="s" s="2">
@@ -17475,17 +17501,17 @@
         <v>91</v>
       </c>
       <c r="K127" t="s" s="2">
-        <v>528</v>
+        <v>537</v>
       </c>
       <c r="L127" t="s" s="2">
-        <v>529</v>
+        <v>538</v>
       </c>
       <c r="M127" t="s" s="2">
-        <v>530</v>
+        <v>539</v>
       </c>
       <c r="N127" s="2"/>
       <c r="O127" t="s" s="2">
-        <v>531</v>
+        <v>540</v>
       </c>
       <c r="P127" t="s" s="2">
         <v>80</v>
@@ -17534,7 +17560,7 @@
         <v>80</v>
       </c>
       <c r="AF127" t="s" s="2">
-        <v>532</v>
+        <v>541</v>
       </c>
       <c r="AG127" t="s" s="2">
         <v>81</v>
@@ -17552,7 +17578,7 @@
         <v>80</v>
       </c>
       <c r="AL127" t="s" s="2">
-        <v>512</v>
+        <v>521</v>
       </c>
       <c r="AM127" t="s" s="2">
         <v>80</v>
@@ -17572,10 +17598,10 @@
     </row>
     <row r="128" hidden="true">
       <c r="A128" t="s" s="2">
-        <v>533</v>
+        <v>542</v>
       </c>
       <c r="B128" t="s" s="2">
-        <v>533</v>
+        <v>542</v>
       </c>
       <c r="C128" s="2"/>
       <c r="D128" t="s" s="2">
@@ -17598,16 +17624,16 @@
         <v>80</v>
       </c>
       <c r="K128" t="s" s="2">
-        <v>534</v>
+        <v>543</v>
       </c>
       <c r="L128" t="s" s="2">
-        <v>535</v>
+        <v>544</v>
       </c>
       <c r="M128" t="s" s="2">
-        <v>536</v>
+        <v>545</v>
       </c>
       <c r="N128" t="s" s="2">
-        <v>537</v>
+        <v>546</v>
       </c>
       <c r="O128" s="2"/>
       <c r="P128" t="s" s="2">
@@ -17657,7 +17683,7 @@
         <v>80</v>
       </c>
       <c r="AF128" t="s" s="2">
-        <v>533</v>
+        <v>542</v>
       </c>
       <c r="AG128" t="s" s="2">
         <v>81</v>
@@ -17672,10 +17698,10 @@
         <v>102</v>
       </c>
       <c r="AK128" t="s" s="2">
-        <v>538</v>
+        <v>547</v>
       </c>
       <c r="AL128" t="s" s="2">
-        <v>539</v>
+        <v>548</v>
       </c>
       <c r="AM128" t="s" s="2">
         <v>80</v>
@@ -17684,7 +17710,7 @@
         <v>80</v>
       </c>
       <c r="AO128" t="s" s="2">
-        <v>540</v>
+        <v>549</v>
       </c>
       <c r="AP128" t="s" s="2">
         <v>80</v>

--- a/main/ig/StructureDefinition-fr-media-document.xlsx
+++ b/main/ig/StructureDefinition-fr-media-document.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-30T09:01:37+00:00</t>
+    <t>2026-06-30T09:56:22+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-media-document.xlsx
+++ b/main/ig/StructureDefinition-fr-media-document.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-30T09:56:22+00:00</t>
+    <t>2026-08-06T11:33:52+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
